--- a/database/event/2998/event_2998_evp_summary.xlsx
+++ b/database/event/2998/event_2998_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.7729</v>
+        <v>4.9663</v>
       </c>
       <c r="C2" t="n">
-        <v>1.4152</v>
+        <v>1.8628</v>
       </c>
       <c r="D2" t="n">
-        <v>1.1028</v>
+        <v>1.5347</v>
       </c>
       <c r="E2" t="n">
-        <v>3.7729</v>
+        <v>4.9663</v>
       </c>
       <c r="F2" t="n">
-        <v>3.4646</v>
+        <v>4.658</v>
       </c>
       <c r="G2" t="n">
         <v>0.3083</v>
       </c>
       <c r="H2" t="n">
-        <v>3.4646</v>
+        <v>5.0007</v>
       </c>
       <c r="I2" t="n">
-        <v>3.4807</v>
+        <v>5.0428</v>
       </c>
       <c r="J2" t="n">
         <v>0.3083</v>
@@ -529,7 +529,7 @@
         <v>86</v>
       </c>
       <c r="M2" t="n">
-        <v>3.789</v>
+        <v>5.3511</v>
       </c>
       <c r="N2" t="n">
         <v>206</v>
@@ -538,35 +538,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.2579</v>
+        <v>4.4159</v>
       </c>
       <c r="C3" t="n">
-        <v>1.222</v>
+        <v>1.6563</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8948</v>
+        <v>1.3154</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2579</v>
+        <v>4.4159</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.6677999999999999</v>
+        <v>4.1145</v>
       </c>
       <c r="G3" t="n">
-        <v>3.9257</v>
+        <v>0.3014</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.6677999999999999</v>
+        <v>4.1485</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.6677999999999999</v>
+        <v>4.1485</v>
       </c>
       <c r="J3" t="n">
-        <v>3.9257</v>
+        <v>0.3014</v>
       </c>
       <c r="K3" t="n">
         <v>115</v>
@@ -575,7 +575,7 @@
         <v>86</v>
       </c>
       <c r="M3" t="n">
-        <v>3.2579</v>
+        <v>4.4499</v>
       </c>
       <c r="N3" t="n">
         <v>201</v>
@@ -584,139 +584,139 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>dennis</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.0203</v>
+        <v>4.1112</v>
       </c>
       <c r="C4" t="n">
-        <v>1.1329</v>
+        <v>1.542</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7988</v>
+        <v>1.194</v>
       </c>
       <c r="E4" t="n">
-        <v>3.0203</v>
+        <v>4.1112</v>
       </c>
       <c r="F4" t="n">
-        <v>2.7189</v>
+        <v>4.3071</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3014</v>
+        <v>-0.1959</v>
       </c>
       <c r="H4" t="n">
-        <v>2.7189</v>
+        <v>4.4505</v>
       </c>
       <c r="I4" t="n">
-        <v>2.7189</v>
+        <v>4.488</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3014</v>
+        <v>-0.1959</v>
       </c>
       <c r="K4" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="L4" t="n">
         <v>86</v>
       </c>
       <c r="M4" t="n">
-        <v>3.0203</v>
+        <v>4.2921</v>
       </c>
       <c r="N4" t="n">
-        <v>201</v>
+        <v>206</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>boltz</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.7457</v>
+        <v>3.8703</v>
       </c>
       <c r="C5" t="n">
-        <v>1.0299</v>
+        <v>1.4517</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6878</v>
+        <v>1.098</v>
       </c>
       <c r="E5" t="n">
-        <v>2.7457</v>
+        <v>3.8703</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1285</v>
+        <v>3.8703</v>
       </c>
       <c r="G5" t="n">
-        <v>1.6172</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1.1285</v>
+        <v>3.8703</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1285</v>
+        <v>3.8703</v>
       </c>
       <c r="J5" t="n">
-        <v>1.6172</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="L5" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>2.7457</v>
+        <v>3.8703</v>
       </c>
       <c r="N5" t="n">
-        <v>201</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>dennis</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.4766</v>
+        <v>3.4577</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9288999999999999</v>
+        <v>1.2969</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5790999999999999</v>
+        <v>0.9336</v>
       </c>
       <c r="E6" t="n">
-        <v>2.4766</v>
+        <v>3.4577</v>
       </c>
       <c r="F6" t="n">
-        <v>2.6725</v>
+        <v>-0.468</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1959</v>
+        <v>3.9257</v>
       </c>
       <c r="H6" t="n">
-        <v>2.6725</v>
+        <v>-0.468</v>
       </c>
       <c r="I6" t="n">
-        <v>2.685</v>
+        <v>-0.468</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1959</v>
+        <v>3.9257</v>
       </c>
       <c r="K6" t="n">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="L6" t="n">
         <v>86</v>
       </c>
       <c r="M6" t="n">
-        <v>2.4891</v>
+        <v>3.4577</v>
       </c>
       <c r="N6" t="n">
-        <v>206</v>
+        <v>201</v>
       </c>
     </row>
     <row r="7">
@@ -726,28 +726,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.3944</v>
+        <v>3.3194</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8981</v>
+        <v>1.2451</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5459000000000001</v>
+        <v>0.8784999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>2.3944</v>
+        <v>3.3194</v>
       </c>
       <c r="F7" t="n">
-        <v>2.7856</v>
+        <v>3.7106</v>
       </c>
       <c r="G7" t="n">
         <v>-0.3912</v>
       </c>
       <c r="H7" t="n">
-        <v>2.7856</v>
+        <v>3.7106</v>
       </c>
       <c r="I7" t="n">
-        <v>2.7986</v>
+        <v>3.7418</v>
       </c>
       <c r="J7" t="n">
         <v>-0.3912</v>
@@ -759,7 +759,7 @@
         <v>86</v>
       </c>
       <c r="M7" t="n">
-        <v>2.4074</v>
+        <v>3.3506</v>
       </c>
       <c r="N7" t="n">
         <v>206</v>
@@ -768,47 +768,47 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>boltz</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.3393</v>
+        <v>3.3158</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8774</v>
+        <v>1.2437</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5237000000000001</v>
+        <v>0.8771</v>
       </c>
       <c r="E8" t="n">
-        <v>2.3393</v>
+        <v>3.3158</v>
       </c>
       <c r="F8" t="n">
-        <v>2.3393</v>
+        <v>1.6986</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1.6172</v>
       </c>
       <c r="H8" t="n">
-        <v>2.3393</v>
+        <v>1.6986</v>
       </c>
       <c r="I8" t="n">
-        <v>2.3393</v>
+        <v>1.6986</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1.6172</v>
       </c>
       <c r="K8" t="n">
-        <v>137</v>
+        <v>115</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="M8" t="n">
-        <v>2.3393</v>
+        <v>3.3158</v>
       </c>
       <c r="N8" t="n">
-        <v>137</v>
+        <v>201</v>
       </c>
     </row>
     <row r="9">
@@ -818,28 +818,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.1443</v>
+        <v>3.0744</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8043</v>
+        <v>1.1532</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4449</v>
+        <v>0.7809</v>
       </c>
       <c r="E9" t="n">
-        <v>2.1443</v>
+        <v>3.0744</v>
       </c>
       <c r="F9" t="n">
-        <v>2.1443</v>
+        <v>3.0744</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2.1443</v>
+        <v>3.0744</v>
       </c>
       <c r="I9" t="n">
-        <v>2.1443</v>
+        <v>3.0744</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.1443</v>
+        <v>3.0744</v>
       </c>
       <c r="N9" t="n">
         <v>137</v>
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.9493</v>
+        <v>1.9586</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7312</v>
+        <v>0.7346</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3661</v>
+        <v>0.3364</v>
       </c>
       <c r="E10" t="n">
-        <v>1.9493</v>
+        <v>1.9586</v>
       </c>
       <c r="F10" t="n">
-        <v>1.9493</v>
+        <v>1.9586</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1.9493</v>
+        <v>1.9586</v>
       </c>
       <c r="I10" t="n">
-        <v>1.9493</v>
+        <v>1.9586</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1.9493</v>
+        <v>1.9586</v>
       </c>
       <c r="N10" t="n">
         <v>137</v>
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.5254</v>
+        <v>1.9165</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5722</v>
+        <v>0.7188</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1949</v>
+        <v>0.3196</v>
       </c>
       <c r="E11" t="n">
-        <v>1.5254</v>
+        <v>1.9165</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5254</v>
+        <v>1.9165</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1.5254</v>
+        <v>1.9165</v>
       </c>
       <c r="I11" t="n">
-        <v>1.5254</v>
+        <v>1.9165</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1.5254</v>
+        <v>1.9165</v>
       </c>
       <c r="N11" t="n">
         <v>112</v>
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9502</v>
+        <v>1.3016</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3564</v>
+        <v>0.4882</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.0375</v>
+        <v>0.0746</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9502</v>
+        <v>1.3016</v>
       </c>
       <c r="F12" t="n">
-        <v>1.2158</v>
+        <v>1.5672</v>
       </c>
       <c r="G12" t="n">
         <v>-0.2656</v>
       </c>
       <c r="H12" t="n">
-        <v>1.2158</v>
+        <v>1.5672</v>
       </c>
       <c r="I12" t="n">
-        <v>1.2215</v>
+        <v>1.5804</v>
       </c>
       <c r="J12" t="n">
         <v>-0.2656</v>
@@ -989,7 +989,7 @@
         <v>86</v>
       </c>
       <c r="M12" t="n">
-        <v>0.9559</v>
+        <v>1.3148</v>
       </c>
       <c r="N12" t="n">
         <v>206</v>
@@ -1002,28 +1002,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7775</v>
+        <v>0.9049</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2916</v>
+        <v>0.3394</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1073</v>
+        <v>-0.0834</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7775</v>
+        <v>0.9049</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7775</v>
+        <v>0.9049</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7775</v>
+        <v>0.9049</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7775</v>
+        <v>0.9049</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0.7775</v>
+        <v>0.9049</v>
       </c>
       <c r="N13" t="n">
         <v>137</v>
@@ -1044,139 +1044,139 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5379</v>
+        <v>0.7852</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2018</v>
+        <v>0.2945</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.2041</v>
+        <v>-0.1311</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5379</v>
+        <v>0.7852</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5379</v>
+        <v>0.7852</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5379</v>
+        <v>0.7852</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5379</v>
+        <v>0.7852</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.5379</v>
+        <v>0.7852</v>
       </c>
       <c r="N14" t="n">
-        <v>135</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4944</v>
+        <v>0.6252</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1854</v>
+        <v>0.2345</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2216</v>
+        <v>-0.1948</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4944</v>
+        <v>0.6252</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4944</v>
+        <v>0.6252</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4944</v>
+        <v>0.6252</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4944</v>
+        <v>0.6252</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4944</v>
+        <v>0.6252</v>
       </c>
       <c r="N15" t="n">
-        <v>121</v>
+        <v>135</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>valde</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.3267</v>
+        <v>0.5589</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1225</v>
+        <v>0.2096</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2894</v>
+        <v>-0.2212</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3267</v>
+        <v>0.5589</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3267</v>
+        <v>1.1103</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>-0.5514</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3267</v>
+        <v>1.1103</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3267</v>
+        <v>1.1103</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>-0.5514</v>
       </c>
       <c r="K16" t="n">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="M16" t="n">
-        <v>0.3267</v>
+        <v>0.5589000000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>135</v>
+        <v>201</v>
       </c>
     </row>
     <row r="17">
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.0517</v>
+        <v>0.4464</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.0194</v>
+        <v>0.1674</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4422</v>
+        <v>-0.2661</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0517</v>
+        <v>0.4464</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0517</v>
+        <v>0.4464</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0517</v>
+        <v>0.4464</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0517</v>
+        <v>0.4464</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.0517</v>
+        <v>0.4464</v>
       </c>
       <c r="N17" t="n">
         <v>121</v>
@@ -1228,124 +1228,124 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>valde</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.0565</v>
+        <v>0.3267</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.0212</v>
+        <v>0.1225</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4442</v>
+        <v>-0.3138</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0565</v>
+        <v>0.3267</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0565</v>
+        <v>0.3267</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0565</v>
+        <v>0.3267</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0565</v>
+        <v>0.3267</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0565</v>
+        <v>0.3267</v>
       </c>
       <c r="N18" t="n">
-        <v>121</v>
+        <v>135</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.1189</v>
+        <v>0.2513</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.0446</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4694</v>
+        <v>-0.3438</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1189</v>
+        <v>0.2513</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4325</v>
+        <v>0.2513</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5514</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4325</v>
+        <v>0.2513</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4325</v>
+        <v>0.2513</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5514</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="L19" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1189</v>
+        <v>0.2513</v>
       </c>
       <c r="N19" t="n">
-        <v>201</v>
+        <v>121</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Xizt</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.5642</v>
+        <v>-0.1426</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.2116</v>
+        <v>-0.0535</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6493</v>
+        <v>-0.5007</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5642</v>
+        <v>-0.1426</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5642</v>
+        <v>-0.1426</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5642</v>
+        <v>-0.1426</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5642</v>
+        <v>-0.1426</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.5642</v>
+        <v>-0.1426</v>
       </c>
       <c r="N20" t="n">
         <v>112</v>
@@ -1366,93 +1366,93 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.6019</v>
+        <v>-0.1768</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.2258</v>
+        <v>-0.0663</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.6645</v>
+        <v>-0.5143</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6019</v>
+        <v>-0.1768</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6019</v>
+        <v>0.3147</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>-0.4915</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.6019</v>
+        <v>0.3147</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6019</v>
+        <v>0.3147</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>-0.4915</v>
       </c>
       <c r="K21" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.6019</v>
+        <v>-0.1768</v>
       </c>
       <c r="N21" t="n">
-        <v>112</v>
+        <v>201</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.605</v>
+        <v>-0.284</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.2269</v>
+        <v>-0.1065</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.6657999999999999</v>
+        <v>-0.5571</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.605</v>
+        <v>-0.284</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1135</v>
+        <v>-0.284</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.4915</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.1135</v>
+        <v>-0.284</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1135</v>
+        <v>-0.284</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.4915</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="L22" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.605</v>
+        <v>-0.284</v>
       </c>
       <c r="N22" t="n">
-        <v>201</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23">
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.6932</v>
+        <v>-0.5505</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.26</v>
+        <v>-0.2065</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.7014</v>
+        <v>-0.6632</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.6932</v>
+        <v>-0.5505</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.6932</v>
+        <v>-0.5505</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.6932</v>
+        <v>-0.5505</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.6932</v>
+        <v>-0.5505</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.6932</v>
+        <v>-0.5505</v>
       </c>
       <c r="N23" t="n">
         <v>112</v>
@@ -1504,185 +1504,185 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>Xizt</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.7374000000000001</v>
+        <v>-0.5642</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.2766</v>
+        <v>-0.2116</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.7193000000000001</v>
+        <v>-0.6687</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.7374000000000001</v>
+        <v>-0.5642</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.7374000000000001</v>
+        <v>-0.5642</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.7374000000000001</v>
+        <v>-0.5642</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.7374000000000001</v>
+        <v>-0.5642</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.7374000000000001</v>
+        <v>-0.5642</v>
       </c>
       <c r="N24" t="n">
-        <v>135</v>
+        <v>112</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.8313</v>
+        <v>-0.7374000000000001</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.3118</v>
+        <v>-0.2766</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.7572</v>
+        <v>-0.7377</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.8313</v>
+        <v>-0.7374000000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.8313</v>
+        <v>-0.7374000000000001</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.8313</v>
+        <v>-0.7374000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.8313</v>
+        <v>-0.7374000000000001</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.8313</v>
+        <v>-0.7374000000000001</v>
       </c>
       <c r="N25" t="n">
-        <v>121</v>
+        <v>135</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.8336</v>
+        <v>-0.8117</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.3127</v>
+        <v>-0.3045</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.7581</v>
+        <v>-0.7673</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.8336</v>
+        <v>-0.8117</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.8336</v>
+        <v>-0.0184</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>-0.7933</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.8336</v>
+        <v>-0.0184</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.8336</v>
+        <v>-0.0186</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>-0.7933</v>
       </c>
       <c r="K26" t="n">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.8336</v>
+        <v>-0.8119</v>
       </c>
       <c r="N26" t="n">
-        <v>112</v>
+        <v>206</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.8875999999999999</v>
+        <v>-0.8313</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.3329</v>
+        <v>-0.3118</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.7799</v>
+        <v>-0.7751</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.8875999999999999</v>
+        <v>-0.8313</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.09429999999999999</v>
+        <v>-0.8313</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.7933</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.09429999999999999</v>
+        <v>-0.8313</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.09470000000000001</v>
+        <v>-0.8313</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.7933</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L27" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.888</v>
+        <v>-0.8313</v>
       </c>
       <c r="N27" t="n">
-        <v>206</v>
+        <v>121</v>
       </c>
     </row>
     <row r="28">
@@ -1698,7 +1698,7 @@
         <v>-0.3827</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.8335</v>
+        <v>-0.8504</v>
       </c>
       <c r="E28" t="n">
         <v>-1.0203</v>
@@ -1744,7 +1744,7 @@
         <v>-0.4203</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.874</v>
+        <v>-0.8903</v>
       </c>
       <c r="E29" t="n">
         <v>-1.1205</v>
@@ -1790,7 +1790,7 @@
         <v>-0.6313</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.1013</v>
+        <v>-1.1145</v>
       </c>
       <c r="E30" t="n">
         <v>-1.6832</v>
@@ -1836,7 +1836,7 @@
         <v>-0.8653999999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.3534</v>
+        <v>-1.3631</v>
       </c>
       <c r="E31" t="n">
         <v>-2.3072</v>

--- a/database/event/2998/event_2998_evp_summary.xlsx
+++ b/database/event/2998/event_2998_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.9663</v>
+        <v>4.0124</v>
       </c>
       <c r="C2" t="n">
-        <v>1.8628</v>
+        <v>1.505</v>
       </c>
       <c r="D2" t="n">
-        <v>1.5347</v>
+        <v>1.1734</v>
       </c>
       <c r="E2" t="n">
-        <v>4.9663</v>
+        <v>4.0124</v>
       </c>
       <c r="F2" t="n">
-        <v>4.658</v>
+        <v>3.6437</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3083</v>
+        <v>0.3687</v>
       </c>
       <c r="H2" t="n">
-        <v>5.0007</v>
+        <v>4.6411</v>
       </c>
       <c r="I2" t="n">
-        <v>5.0428</v>
+        <v>4.832</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3083</v>
+        <v>0.3687</v>
       </c>
       <c r="K2" t="n">
         <v>120</v>
@@ -529,7 +529,7 @@
         <v>86</v>
       </c>
       <c r="M2" t="n">
-        <v>5.3511</v>
+        <v>5.200699999999999</v>
       </c>
       <c r="N2" t="n">
         <v>206</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.4159</v>
+        <v>3.9435</v>
       </c>
       <c r="C3" t="n">
-        <v>1.6563</v>
+        <v>1.4791</v>
       </c>
       <c r="D3" t="n">
-        <v>1.3154</v>
+        <v>1.1423</v>
       </c>
       <c r="E3" t="n">
-        <v>4.4159</v>
+        <v>3.9435</v>
       </c>
       <c r="F3" t="n">
-        <v>4.1145</v>
+        <v>3.3924</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3014</v>
+        <v>0.5511</v>
       </c>
       <c r="H3" t="n">
-        <v>4.1485</v>
+        <v>4.0894</v>
       </c>
       <c r="I3" t="n">
-        <v>4.1485</v>
+        <v>4.0894</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3014</v>
+        <v>0.5511</v>
       </c>
       <c r="K3" t="n">
         <v>115</v>
@@ -575,7 +575,7 @@
         <v>86</v>
       </c>
       <c r="M3" t="n">
-        <v>4.4499</v>
+        <v>4.6405</v>
       </c>
       <c r="N3" t="n">
         <v>201</v>
@@ -584,231 +584,231 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>dennis</t>
+          <t>boltz</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.1112</v>
+        <v>3.8359</v>
       </c>
       <c r="C4" t="n">
-        <v>1.542</v>
+        <v>1.4388</v>
       </c>
       <c r="D4" t="n">
-        <v>1.194</v>
+        <v>1.0937</v>
       </c>
       <c r="E4" t="n">
-        <v>4.1112</v>
+        <v>3.8359</v>
       </c>
       <c r="F4" t="n">
-        <v>4.3071</v>
+        <v>2.1114</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1959</v>
+        <v>1.7245</v>
       </c>
       <c r="H4" t="n">
-        <v>4.4505</v>
+        <v>2.1114</v>
       </c>
       <c r="I4" t="n">
-        <v>4.488</v>
+        <v>2.1114</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.1959</v>
+        <v>1.7245</v>
       </c>
       <c r="K4" t="n">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="L4" t="n">
         <v>86</v>
       </c>
       <c r="M4" t="n">
-        <v>4.2921</v>
+        <v>3.8359</v>
       </c>
       <c r="N4" t="n">
-        <v>206</v>
+        <v>201</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.8703</v>
+        <v>3.6438</v>
       </c>
       <c r="C5" t="n">
-        <v>1.4517</v>
+        <v>1.3667</v>
       </c>
       <c r="D5" t="n">
-        <v>1.098</v>
+        <v>1.007</v>
       </c>
       <c r="E5" t="n">
-        <v>3.8703</v>
+        <v>3.6438</v>
       </c>
       <c r="F5" t="n">
-        <v>3.8703</v>
+        <v>0.1954</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>3.4484</v>
       </c>
       <c r="H5" t="n">
-        <v>3.8703</v>
+        <v>0.1954</v>
       </c>
       <c r="I5" t="n">
-        <v>3.8703</v>
+        <v>0.1954</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>3.4484</v>
       </c>
       <c r="K5" t="n">
-        <v>137</v>
+        <v>115</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="M5" t="n">
-        <v>3.8703</v>
+        <v>3.6438</v>
       </c>
       <c r="N5" t="n">
-        <v>137</v>
+        <v>201</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>dennis</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.4577</v>
+        <v>3.2891</v>
       </c>
       <c r="C6" t="n">
-        <v>1.2969</v>
+        <v>1.2337</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9336</v>
+        <v>0.8469</v>
       </c>
       <c r="E6" t="n">
-        <v>3.4577</v>
+        <v>3.2891</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.468</v>
+        <v>3.3715</v>
       </c>
       <c r="G6" t="n">
-        <v>3.9257</v>
+        <v>-0.0824</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.468</v>
+        <v>4.0434</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.468</v>
+        <v>4.2097</v>
       </c>
       <c r="J6" t="n">
-        <v>3.9257</v>
+        <v>-0.0824</v>
       </c>
       <c r="K6" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="L6" t="n">
         <v>86</v>
       </c>
       <c r="M6" t="n">
-        <v>3.4577</v>
+        <v>4.1273</v>
       </c>
       <c r="N6" t="n">
-        <v>201</v>
+        <v>206</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.3194</v>
+        <v>3.2138</v>
       </c>
       <c r="C7" t="n">
-        <v>1.2451</v>
+        <v>1.2054</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8784999999999999</v>
+        <v>0.8129</v>
       </c>
       <c r="E7" t="n">
-        <v>3.3194</v>
+        <v>3.2138</v>
       </c>
       <c r="F7" t="n">
-        <v>3.7106</v>
+        <v>3.2138</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3912</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>3.7106</v>
+        <v>3.6972</v>
       </c>
       <c r="I7" t="n">
-        <v>3.7418</v>
+        <v>3.6972</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.3912</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="L7" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.3506</v>
+        <v>3.6972</v>
       </c>
       <c r="N7" t="n">
-        <v>206</v>
+        <v>137</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>boltz</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.3158</v>
+        <v>3.0665</v>
       </c>
       <c r="C8" t="n">
-        <v>1.2437</v>
+        <v>1.1502</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8771</v>
+        <v>0.7464</v>
       </c>
       <c r="E8" t="n">
-        <v>3.3158</v>
+        <v>3.0665</v>
       </c>
       <c r="F8" t="n">
-        <v>1.6986</v>
+        <v>3.2112</v>
       </c>
       <c r="G8" t="n">
-        <v>1.6172</v>
+        <v>-0.1447</v>
       </c>
       <c r="H8" t="n">
-        <v>1.6986</v>
+        <v>3.6915</v>
       </c>
       <c r="I8" t="n">
-        <v>1.6986</v>
+        <v>3.8433</v>
       </c>
       <c r="J8" t="n">
-        <v>1.6172</v>
+        <v>-0.1447</v>
       </c>
       <c r="K8" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="L8" t="n">
         <v>86</v>
       </c>
       <c r="M8" t="n">
-        <v>3.3158</v>
+        <v>3.6986</v>
       </c>
       <c r="N8" t="n">
-        <v>201</v>
+        <v>206</v>
       </c>
     </row>
     <row r="9">
@@ -818,28 +818,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.0744</v>
+        <v>2.919</v>
       </c>
       <c r="C9" t="n">
-        <v>1.1532</v>
+        <v>1.0949</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7809</v>
+        <v>0.6798</v>
       </c>
       <c r="E9" t="n">
-        <v>3.0744</v>
+        <v>2.919</v>
       </c>
       <c r="F9" t="n">
-        <v>3.0744</v>
+        <v>2.919</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>3.0744</v>
+        <v>3.0499</v>
       </c>
       <c r="I9" t="n">
-        <v>3.0744</v>
+        <v>3.0499</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.0744</v>
+        <v>3.0499</v>
       </c>
       <c r="N9" t="n">
         <v>137</v>
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.9586</v>
+        <v>2.3076</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7346</v>
+        <v>0.8655</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3364</v>
+        <v>0.4038</v>
       </c>
       <c r="E10" t="n">
-        <v>1.9586</v>
+        <v>2.3076</v>
       </c>
       <c r="F10" t="n">
-        <v>1.9586</v>
+        <v>2.3076</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1.9586</v>
+        <v>2.3076</v>
       </c>
       <c r="I10" t="n">
-        <v>1.9586</v>
+        <v>2.3076</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1.9586</v>
+        <v>2.3076</v>
       </c>
       <c r="N10" t="n">
         <v>137</v>
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.9165</v>
+        <v>1.9632</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7188</v>
+        <v>0.7364000000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3196</v>
+        <v>0.2483</v>
       </c>
       <c r="E11" t="n">
-        <v>1.9165</v>
+        <v>1.9632</v>
       </c>
       <c r="F11" t="n">
-        <v>1.9165</v>
+        <v>1.9632</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1.9165</v>
+        <v>1.9632</v>
       </c>
       <c r="I11" t="n">
-        <v>1.9165</v>
+        <v>1.9632</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1.9165</v>
+        <v>1.9632</v>
       </c>
       <c r="N11" t="n">
         <v>112</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.3016</v>
+        <v>1.6608</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4882</v>
+        <v>0.6229</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0746</v>
+        <v>0.1118</v>
       </c>
       <c r="E12" t="n">
-        <v>1.3016</v>
+        <v>1.6608</v>
       </c>
       <c r="F12" t="n">
-        <v>1.5672</v>
+        <v>1.7315</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.2656</v>
+        <v>-0.0707</v>
       </c>
       <c r="H12" t="n">
-        <v>1.5672</v>
+        <v>1.7315</v>
       </c>
       <c r="I12" t="n">
-        <v>1.5804</v>
+        <v>1.8027</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.2656</v>
+        <v>-0.0707</v>
       </c>
       <c r="K12" t="n">
         <v>120</v>
@@ -989,7 +989,7 @@
         <v>86</v>
       </c>
       <c r="M12" t="n">
-        <v>1.3148</v>
+        <v>1.732</v>
       </c>
       <c r="N12" t="n">
         <v>206</v>
@@ -1002,28 +1002,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9049</v>
+        <v>1.2876</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3394</v>
+        <v>0.483</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0834</v>
+        <v>-0.0567</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9049</v>
+        <v>1.2876</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9049</v>
+        <v>1.2876</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9049</v>
+        <v>1.2876</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9049</v>
+        <v>1.2876</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0.9049</v>
+        <v>1.2876</v>
       </c>
       <c r="N13" t="n">
         <v>137</v>
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7852</v>
+        <v>1.0361</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2945</v>
+        <v>0.3886</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1311</v>
+        <v>-0.1703</v>
       </c>
       <c r="E14" t="n">
-        <v>0.7852</v>
+        <v>1.0361</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7852</v>
+        <v>1.0361</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7852</v>
+        <v>1.0361</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7852</v>
+        <v>1.0361</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.7852</v>
+        <v>1.0361</v>
       </c>
       <c r="N14" t="n">
         <v>121</v>
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6252</v>
+        <v>0.9308999999999999</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2345</v>
+        <v>0.3492</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1948</v>
+        <v>-0.2178</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6252</v>
+        <v>0.9308999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6252</v>
+        <v>0.9308999999999999</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6252</v>
+        <v>0.9308999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6252</v>
+        <v>0.9308999999999999</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.6252</v>
+        <v>0.9308999999999999</v>
       </c>
       <c r="N15" t="n">
         <v>135</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5589</v>
+        <v>0.8643</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2096</v>
+        <v>0.3242</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2212</v>
+        <v>-0.2478</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5589</v>
+        <v>0.8643</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1103</v>
+        <v>1.1763</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.5514</v>
+        <v>-0.312</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1103</v>
+        <v>1.1763</v>
       </c>
       <c r="I16" t="n">
-        <v>1.1103</v>
+        <v>1.1763</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.5514</v>
+        <v>-0.312</v>
       </c>
       <c r="K16" t="n">
         <v>115</v>
@@ -1173,7 +1173,7 @@
         <v>86</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5589000000000001</v>
+        <v>0.8642999999999998</v>
       </c>
       <c r="N16" t="n">
         <v>201</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.4464</v>
+        <v>0.8373</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1674</v>
+        <v>0.3141</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2661</v>
+        <v>-0.26</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4464</v>
+        <v>0.8373</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4464</v>
+        <v>0.8373</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4464</v>
+        <v>0.8373</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4464</v>
+        <v>0.8373</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.4464</v>
+        <v>0.8373</v>
       </c>
       <c r="N17" t="n">
         <v>121</v>
@@ -1228,185 +1228,185 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>valde</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.3267</v>
+        <v>0.6524</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1225</v>
+        <v>0.2447</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3138</v>
+        <v>-0.3435</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3267</v>
+        <v>0.6524</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3267</v>
+        <v>0.6524</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3267</v>
+        <v>0.6524</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3267</v>
+        <v>0.6524</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3267</v>
+        <v>0.6524</v>
       </c>
       <c r="N18" t="n">
-        <v>135</v>
+        <v>121</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>valde</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.2513</v>
+        <v>0.5693</v>
       </c>
       <c r="C19" t="n">
-        <v>0.09429999999999999</v>
+        <v>0.2135</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3438</v>
+        <v>-0.381</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2513</v>
+        <v>0.5693</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2513</v>
+        <v>0.5693</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2513</v>
+        <v>0.5693</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2513</v>
+        <v>0.5693</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2513</v>
+        <v>0.5693</v>
       </c>
       <c r="N19" t="n">
-        <v>121</v>
+        <v>135</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.1426</v>
+        <v>0.5151</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.0535</v>
+        <v>0.1932</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5007</v>
+        <v>-0.4055</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1426</v>
+        <v>0.5151</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1426</v>
+        <v>0.7766</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-0.2615</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1426</v>
+        <v>0.7766</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1426</v>
+        <v>0.7766</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-0.2615</v>
       </c>
       <c r="K20" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1426</v>
+        <v>0.5150999999999999</v>
       </c>
       <c r="N20" t="n">
-        <v>112</v>
+        <v>201</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.1768</v>
+        <v>0.2275</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.0663</v>
+        <v>0.0853</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5143</v>
+        <v>-0.5353</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.1768</v>
+        <v>0.2275</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3147</v>
+        <v>0.2275</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.4915</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3147</v>
+        <v>0.2275</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3147</v>
+        <v>0.2275</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.4915</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="L21" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1768</v>
+        <v>0.2275</v>
       </c>
       <c r="N21" t="n">
-        <v>201</v>
+        <v>112</v>
       </c>
     </row>
     <row r="22">
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.284</v>
+        <v>0.1682</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.1065</v>
+        <v>0.0631</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5571</v>
+        <v>-0.5621</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.284</v>
+        <v>0.1682</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.284</v>
+        <v>0.1682</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.284</v>
+        <v>0.1682</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.284</v>
+        <v>0.1682</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.284</v>
+        <v>0.1682</v>
       </c>
       <c r="N22" t="n">
         <v>112</v>
@@ -1458,78 +1458,78 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.5505</v>
+        <v>0.1065</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.2065</v>
+        <v>0.0399</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.6632</v>
+        <v>-0.5899</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.5505</v>
+        <v>0.1065</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.5505</v>
+        <v>0.5499000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>-0.4434</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.5505</v>
+        <v>0.5499000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.5505</v>
+        <v>0.5725</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>-0.4434</v>
       </c>
       <c r="K23" t="n">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.5505</v>
+        <v>0.1291</v>
       </c>
       <c r="N23" t="n">
-        <v>112</v>
+        <v>206</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Xizt</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.5642</v>
+        <v>0.0696</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.2116</v>
+        <v>0.0261</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.6687</v>
+        <v>-0.6066</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.5642</v>
+        <v>0.0696</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.5642</v>
+        <v>0.0696</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.5642</v>
+        <v>0.0696</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.5642</v>
+        <v>0.0696</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.5642</v>
+        <v>0.0696</v>
       </c>
       <c r="N24" t="n">
         <v>112</v>
@@ -1550,93 +1550,93 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>Xizt</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.7374000000000001</v>
+        <v>-0.1161</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.2766</v>
+        <v>-0.0435</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.7377</v>
+        <v>-0.6904</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.7374000000000001</v>
+        <v>-0.1161</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.7374000000000001</v>
+        <v>-0.1161</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.7374000000000001</v>
+        <v>-0.1161</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.7374000000000001</v>
+        <v>-0.1161</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.7374000000000001</v>
+        <v>-0.1161</v>
       </c>
       <c r="N25" t="n">
-        <v>135</v>
+        <v>112</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.8117</v>
+        <v>-0.2741</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.3045</v>
+        <v>-0.1028</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.7673</v>
+        <v>-0.7618</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.8117</v>
+        <v>-0.2741</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.0184</v>
+        <v>-0.2741</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.7933</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.0184</v>
+        <v>-0.2741</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.0186</v>
+        <v>-0.2741</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.7933</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="L26" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.8119</v>
+        <v>-0.2741</v>
       </c>
       <c r="N26" t="n">
-        <v>206</v>
+        <v>135</v>
       </c>
     </row>
     <row r="27">
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.8313</v>
+        <v>-0.3645</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.3118</v>
+        <v>-0.1367</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.7751</v>
+        <v>-0.8026</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.8313</v>
+        <v>-0.3645</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.8313</v>
+        <v>-0.3645</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.8313</v>
+        <v>-0.3645</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.8313</v>
+        <v>-0.3645</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.8313</v>
+        <v>-0.3645</v>
       </c>
       <c r="N27" t="n">
         <v>121</v>
@@ -1688,32 +1688,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>MSL</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-1.0203</v>
+        <v>-0.4786</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.3827</v>
+        <v>-0.1795</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.8504</v>
+        <v>-0.8541</v>
       </c>
       <c r="E28" t="n">
-        <v>-1.0203</v>
+        <v>-0.4786</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.0203</v>
+        <v>-0.4786</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.0203</v>
+        <v>-0.4786</v>
       </c>
       <c r="I28" t="n">
-        <v>-1.0203</v>
+        <v>-0.4786</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-1.0203</v>
+        <v>-0.4786</v>
       </c>
       <c r="N28" t="n">
         <v>135</v>
@@ -1734,32 +1734,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MSL</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-1.1205</v>
+        <v>-0.7044</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.4203</v>
+        <v>-0.2642</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.8903</v>
+        <v>-0.956</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.1205</v>
+        <v>-0.7044</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.1205</v>
+        <v>-0.7044</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-1.1205</v>
+        <v>-0.7044</v>
       </c>
       <c r="I29" t="n">
-        <v>-1.1205</v>
+        <v>-0.7044</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-1.1205</v>
+        <v>-0.7044</v>
       </c>
       <c r="N29" t="n">
         <v>135</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-1.6832</v>
+        <v>-1.0433</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.6313</v>
+        <v>-0.3913</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.1145</v>
+        <v>-1.109</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.6832</v>
+        <v>-1.0433</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.6832</v>
+        <v>-1.0433</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-1.6832</v>
+        <v>-1.0433</v>
       </c>
       <c r="I30" t="n">
-        <v>-1.6832</v>
+        <v>-1.0433</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-1.6832</v>
+        <v>-1.0433</v>
       </c>
       <c r="N30" t="n">
         <v>121</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-2.3072</v>
+        <v>-1.8563</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.8653999999999999</v>
+        <v>-0.6963</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.3631</v>
+        <v>-1.476</v>
       </c>
       <c r="E31" t="n">
-        <v>-2.3072</v>
+        <v>-1.8563</v>
       </c>
       <c r="F31" t="n">
-        <v>-2.3072</v>
+        <v>-1.8563</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-2.3072</v>
+        <v>-1.8563</v>
       </c>
       <c r="I31" t="n">
-        <v>-2.3072</v>
+        <v>-1.8563</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-2.3072</v>
+        <v>-1.8563</v>
       </c>
       <c r="N31" t="n">
         <v>137</v>
@@ -1969,10 +1969,10 @@
         <v>1.42</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6193</v>
+        <v>0.5427</v>
       </c>
       <c r="J2" t="n">
-        <v>16.7211</v>
+        <v>14.6529</v>
       </c>
     </row>
     <row r="3">
@@ -2009,10 +2009,10 @@
         <v>1.35</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5327</v>
+        <v>0.4629</v>
       </c>
       <c r="J3" t="n">
-        <v>14.3829</v>
+        <v>12.4983</v>
       </c>
     </row>
     <row r="4">
@@ -2049,10 +2049,10 @@
         <v>1.3</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4676</v>
+        <v>0.4048</v>
       </c>
       <c r="J4" t="n">
-        <v>12.6252</v>
+        <v>10.9296</v>
       </c>
     </row>
     <row r="5">
@@ -2089,10 +2089,10 @@
         <v>1.04</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0383</v>
+        <v>0.06469999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>1.0341</v>
+        <v>1.7469</v>
       </c>
     </row>
     <row r="6">
@@ -2129,10 +2129,10 @@
         <v>0.7</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5446</v>
+        <v>-0.3525</v>
       </c>
       <c r="J6" t="n">
-        <v>-14.7042</v>
+        <v>-9.5175</v>
       </c>
     </row>
     <row r="7">
@@ -2169,10 +2169,10 @@
         <v>1.42</v>
       </c>
       <c r="I7" t="n">
-        <v>0.67</v>
+        <v>0.6284</v>
       </c>
       <c r="J7" t="n">
-        <v>18.09</v>
+        <v>16.9668</v>
       </c>
     </row>
     <row r="8">
@@ -2209,10 +2209,10 @@
         <v>0.92</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1927</v>
+        <v>-0.1117</v>
       </c>
       <c r="J8" t="n">
-        <v>-5.2029</v>
+        <v>-3.0159</v>
       </c>
     </row>
     <row r="9">
@@ -2249,10 +2249,10 @@
         <v>0.9</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2279</v>
+        <v>-0.1342</v>
       </c>
       <c r="J9" t="n">
-        <v>-6.1533</v>
+        <v>-3.6234</v>
       </c>
     </row>
     <row r="10">
@@ -2289,10 +2289,10 @@
         <v>0.89</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2448</v>
+        <v>-0.1453</v>
       </c>
       <c r="J10" t="n">
-        <v>-6.6096</v>
+        <v>-3.9231</v>
       </c>
     </row>
     <row r="11">
@@ -2329,10 +2329,10 @@
         <v>0.87</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2775</v>
+        <v>-0.1669</v>
       </c>
       <c r="J11" t="n">
-        <v>-7.4925</v>
+        <v>-4.5063</v>
       </c>
     </row>
     <row r="12">
@@ -2369,10 +2369,10 @@
         <v>1.06</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2292</v>
+        <v>0.223</v>
       </c>
       <c r="J12" t="n">
-        <v>5.5008</v>
+        <v>5.352</v>
       </c>
     </row>
     <row r="13">
@@ -2409,10 +2409,10 @@
         <v>1.01</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1226</v>
+        <v>0.09</v>
       </c>
       <c r="J13" t="n">
-        <v>2.9424</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="14">
@@ -2449,10 +2449,10 @@
         <v>0.76</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3852</v>
+        <v>-0.2554</v>
       </c>
       <c r="J14" t="n">
-        <v>-9.2448</v>
+        <v>-6.1296</v>
       </c>
     </row>
     <row r="15">
@@ -2489,10 +2489,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4896</v>
+        <v>-0.3223</v>
       </c>
       <c r="J15" t="n">
-        <v>-11.7504</v>
+        <v>-7.7352</v>
       </c>
     </row>
     <row r="16">
@@ -2529,10 +2529,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.663</v>
+        <v>-0.4442</v>
       </c>
       <c r="J16" t="n">
-        <v>-15.912</v>
+        <v>-10.6608</v>
       </c>
     </row>
     <row r="17">
@@ -2569,10 +2569,10 @@
         <v>1.67</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5312</v>
+        <v>1.3449</v>
       </c>
       <c r="J17" t="n">
-        <v>36.7488</v>
+        <v>32.2776</v>
       </c>
     </row>
     <row r="18">
@@ -2609,10 +2609,10 @@
         <v>1.43</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0607</v>
+        <v>1.0424</v>
       </c>
       <c r="J18" t="n">
-        <v>25.4568</v>
+        <v>25.0176</v>
       </c>
     </row>
     <row r="19">
@@ -2649,10 +2649,10 @@
         <v>1.12</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2758</v>
+        <v>0.3496</v>
       </c>
       <c r="J19" t="n">
-        <v>6.6192</v>
+        <v>8.3904</v>
       </c>
     </row>
     <row r="20">
@@ -2689,10 +2689,10 @@
         <v>1.09</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1909</v>
+        <v>0.2654</v>
       </c>
       <c r="J20" t="n">
-        <v>4.5816</v>
+        <v>6.3696</v>
       </c>
     </row>
     <row r="21">
@@ -2729,10 +2729,10 @@
         <v>0.87</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5662</v>
+        <v>-0.4971</v>
       </c>
       <c r="J21" t="n">
-        <v>-13.5888</v>
+        <v>-11.9304</v>
       </c>
     </row>
     <row r="22">
@@ -2769,10 +2769,10 @@
         <v>1.06</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2259</v>
+        <v>0.2193</v>
       </c>
       <c r="J22" t="n">
-        <v>7.9065</v>
+        <v>7.6755</v>
       </c>
     </row>
     <row r="23">
@@ -2809,10 +2809,10 @@
         <v>0.85</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2219</v>
+        <v>-0.1692</v>
       </c>
       <c r="J23" t="n">
-        <v>-7.7665</v>
+        <v>-5.922</v>
       </c>
     </row>
     <row r="24">
@@ -2849,10 +2849,10 @@
         <v>0.78</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.3568</v>
+        <v>-0.2371</v>
       </c>
       <c r="J24" t="n">
-        <v>-12.488</v>
+        <v>-8.298500000000001</v>
       </c>
     </row>
     <row r="25">
@@ -2889,10 +2889,10 @@
         <v>0.73</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.4343</v>
+        <v>-0.2853</v>
       </c>
       <c r="J25" t="n">
-        <v>-15.2005</v>
+        <v>-9.9855</v>
       </c>
     </row>
     <row r="26">
@@ -2929,10 +2929,10 @@
         <v>0.7</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4779</v>
+        <v>-0.3139</v>
       </c>
       <c r="J26" t="n">
-        <v>-16.7265</v>
+        <v>-10.9865</v>
       </c>
     </row>
     <row r="27">
@@ -2969,10 +2969,10 @@
         <v>1.78</v>
       </c>
       <c r="I27" t="n">
-        <v>1.7245</v>
+        <v>1.4751</v>
       </c>
       <c r="J27" t="n">
-        <v>60.3575</v>
+        <v>51.6285</v>
       </c>
     </row>
     <row r="28">
@@ -3009,10 +3009,10 @@
         <v>1.33</v>
       </c>
       <c r="I28" t="n">
-        <v>0.834</v>
+        <v>0.849</v>
       </c>
       <c r="J28" t="n">
-        <v>29.19</v>
+        <v>29.715</v>
       </c>
     </row>
     <row r="29">
@@ -3049,10 +3049,10 @@
         <v>1.12</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2704</v>
+        <v>0.3468</v>
       </c>
       <c r="J29" t="n">
-        <v>9.464</v>
+        <v>12.138</v>
       </c>
     </row>
     <row r="30">
@@ -3089,10 +3089,10 @@
         <v>1.11</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2427</v>
+        <v>0.3193</v>
       </c>
       <c r="J30" t="n">
-        <v>8.4945</v>
+        <v>11.1755</v>
       </c>
     </row>
     <row r="31">
@@ -3129,10 +3129,10 @@
         <v>0.9</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4897</v>
+        <v>-0.4152</v>
       </c>
       <c r="J31" t="n">
-        <v>-17.1395</v>
+        <v>-14.532</v>
       </c>
     </row>
     <row r="32">
@@ -3169,10 +3169,10 @@
         <v>1.33</v>
       </c>
       <c r="I32" t="n">
-        <v>0.926</v>
+        <v>0.9056</v>
       </c>
       <c r="J32" t="n">
-        <v>27.78</v>
+        <v>27.168</v>
       </c>
     </row>
     <row r="33">
@@ -3209,10 +3209,10 @@
         <v>1.06</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1839</v>
+        <v>0.2118</v>
       </c>
       <c r="J33" t="n">
-        <v>5.517</v>
+        <v>6.354</v>
       </c>
     </row>
     <row r="34">
@@ -3249,10 +3249,10 @@
         <v>1.02</v>
       </c>
       <c r="I34" t="n">
-        <v>0.0344</v>
+        <v>0.0771</v>
       </c>
       <c r="J34" t="n">
-        <v>1.032</v>
+        <v>2.313</v>
       </c>
     </row>
     <row r="35">
@@ -3289,10 +3289,10 @@
         <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.0183</v>
       </c>
       <c r="J35" t="n">
-        <v>-2.1</v>
+        <v>-0.549</v>
       </c>
     </row>
     <row r="36">
@@ -3329,10 +3329,10 @@
         <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.0183</v>
       </c>
       <c r="J36" t="n">
-        <v>-2.1</v>
+        <v>-0.549</v>
       </c>
     </row>
     <row r="37">
@@ -3369,10 +3369,10 @@
         <v>1.11</v>
       </c>
       <c r="I37" t="n">
-        <v>0.2471</v>
+        <v>0.2682</v>
       </c>
       <c r="J37" t="n">
-        <v>7.413</v>
+        <v>8.045999999999999</v>
       </c>
     </row>
     <row r="38">
@@ -3409,10 +3409,10 @@
         <v>1.08</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1951</v>
+        <v>0.2063</v>
       </c>
       <c r="J38" t="n">
-        <v>5.853</v>
+        <v>6.189</v>
       </c>
     </row>
     <row r="39">
@@ -3449,10 +3449,10 @@
         <v>1.03</v>
       </c>
       <c r="I39" t="n">
-        <v>0.0953</v>
+        <v>0.0929</v>
       </c>
       <c r="J39" t="n">
-        <v>2.859</v>
+        <v>2.787</v>
       </c>
     </row>
     <row r="40">
@@ -3489,10 +3489,10 @@
         <v>0.88</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.2595</v>
+        <v>-0.1554</v>
       </c>
       <c r="J40" t="n">
-        <v>-7.785</v>
+        <v>-4.662</v>
       </c>
     </row>
     <row r="41">
@@ -3529,10 +3529,10 @@
         <v>0.87</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.2758</v>
+        <v>-0.1662</v>
       </c>
       <c r="J41" t="n">
-        <v>-8.273999999999999</v>
+        <v>-4.986</v>
       </c>
     </row>
     <row r="42">
@@ -3569,10 +3569,10 @@
         <v>1.52</v>
       </c>
       <c r="I42" t="n">
-        <v>0.8055</v>
+        <v>1.002</v>
       </c>
       <c r="J42" t="n">
-        <v>22.554</v>
+        <v>28.056</v>
       </c>
     </row>
     <row r="43">
@@ -3609,10 +3609,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.128</v>
+        <v>-0.0832</v>
       </c>
       <c r="J43" t="n">
-        <v>-3.584</v>
+        <v>-2.3296</v>
       </c>
     </row>
     <row r="44">
@@ -3649,10 +3649,10 @@
         <v>0.88</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.2433</v>
+        <v>-0.15</v>
       </c>
       <c r="J44" t="n">
-        <v>-6.8124</v>
+        <v>-4.2</v>
       </c>
     </row>
     <row r="45">
@@ -3689,10 +3689,10 @@
         <v>0.8</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.3699</v>
+        <v>-0.2326</v>
       </c>
       <c r="J45" t="n">
-        <v>-10.3572</v>
+        <v>-6.5128</v>
       </c>
     </row>
     <row r="46">
@@ -3729,10 +3729,10 @@
         <v>0.59</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6498</v>
+        <v>-0.4326</v>
       </c>
       <c r="J46" t="n">
-        <v>-18.1944</v>
+        <v>-12.1128</v>
       </c>
     </row>
     <row r="47">
@@ -3769,10 +3769,10 @@
         <v>1.53</v>
       </c>
       <c r="I47" t="n">
-        <v>1.3057</v>
+        <v>1.1928</v>
       </c>
       <c r="J47" t="n">
-        <v>36.5596</v>
+        <v>33.3984</v>
       </c>
     </row>
     <row r="48">
@@ -3809,10 +3809,10 @@
         <v>1.42</v>
       </c>
       <c r="I48" t="n">
-        <v>1.0827</v>
+        <v>1.0485</v>
       </c>
       <c r="J48" t="n">
-        <v>30.3156</v>
+        <v>29.358</v>
       </c>
     </row>
     <row r="49">
@@ -3849,10 +3849,10 @@
         <v>1.09</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2325</v>
+        <v>0.2852</v>
       </c>
       <c r="J49" t="n">
-        <v>6.51</v>
+        <v>7.9856</v>
       </c>
     </row>
     <row r="50">
@@ -3889,10 +3889,10 @@
         <v>0.98</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.2055</v>
+        <v>-0.1324</v>
       </c>
       <c r="J50" t="n">
-        <v>-5.754</v>
+        <v>-3.7072</v>
       </c>
     </row>
     <row r="51">
@@ -3929,10 +3929,10 @@
         <v>0.74</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.8567</v>
+        <v>-0.8153</v>
       </c>
       <c r="J51" t="n">
-        <v>-23.9876</v>
+        <v>-22.8284</v>
       </c>
     </row>
     <row r="52">
@@ -3969,10 +3969,10 @@
         <v>1.59</v>
       </c>
       <c r="I52" t="n">
-        <v>1.3335</v>
+        <v>1.2234</v>
       </c>
       <c r="J52" t="n">
-        <v>30.6705</v>
+        <v>28.1382</v>
       </c>
     </row>
     <row r="53">
@@ -4009,10 +4009,10 @@
         <v>1.48</v>
       </c>
       <c r="I53" t="n">
-        <v>1.114</v>
+        <v>1.0887</v>
       </c>
       <c r="J53" t="n">
-        <v>25.622</v>
+        <v>25.0401</v>
       </c>
     </row>
     <row r="54">
@@ -4049,10 +4049,10 @@
         <v>1.47</v>
       </c>
       <c r="I54" t="n">
-        <v>1.0931</v>
+        <v>1.0763</v>
       </c>
       <c r="J54" t="n">
-        <v>25.1413</v>
+        <v>24.7549</v>
       </c>
     </row>
     <row r="55">
@@ -4089,10 +4089,10 @@
         <v>1.19</v>
       </c>
       <c r="I55" t="n">
-        <v>0.4149</v>
+        <v>0.5086000000000001</v>
       </c>
       <c r="J55" t="n">
-        <v>9.5427</v>
+        <v>11.6978</v>
       </c>
     </row>
     <row r="56">
@@ -4129,10 +4129,10 @@
         <v>0.96</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3353</v>
+        <v>-0.2497</v>
       </c>
       <c r="J56" t="n">
-        <v>-7.7119</v>
+        <v>-5.7431</v>
       </c>
     </row>
     <row r="57">
@@ -4169,10 +4169,10 @@
         <v>0.99</v>
       </c>
       <c r="I57" t="n">
-        <v>0.0384</v>
+        <v>-0.0019</v>
       </c>
       <c r="J57" t="n">
-        <v>0.8832</v>
+        <v>-0.0437</v>
       </c>
     </row>
     <row r="58">
@@ -4209,10 +4209,10 @@
         <v>0.92</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.1092</v>
+        <v>-0.09660000000000001</v>
       </c>
       <c r="J58" t="n">
-        <v>-2.5116</v>
+        <v>-2.2218</v>
       </c>
     </row>
     <row r="59">
@@ -4249,10 +4249,10 @@
         <v>0.85</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2466</v>
+        <v>-0.1716</v>
       </c>
       <c r="J59" t="n">
-        <v>-5.6718</v>
+        <v>-3.9468</v>
       </c>
     </row>
     <row r="60">
@@ -4289,10 +4289,10 @@
         <v>0.78</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.369</v>
+        <v>-0.2406</v>
       </c>
       <c r="J60" t="n">
-        <v>-8.487</v>
+        <v>-5.5338</v>
       </c>
     </row>
     <row r="61">
@@ -4329,10 +4329,10 @@
         <v>0.72</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4583</v>
+        <v>-0.2987</v>
       </c>
       <c r="J61" t="n">
-        <v>-10.5409</v>
+        <v>-6.8701</v>
       </c>
     </row>
     <row r="62">
@@ -4369,10 +4369,10 @@
         <v>0.99</v>
       </c>
       <c r="I62" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.0353</v>
       </c>
       <c r="J62" t="n">
-        <v>1.8672</v>
+        <v>0.8472</v>
       </c>
     </row>
     <row r="63">
@@ -4409,10 +4409,10 @@
         <v>0.93</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.0488</v>
+        <v>-0.0667</v>
       </c>
       <c r="J63" t="n">
-        <v>-1.1712</v>
+        <v>-1.6008</v>
       </c>
     </row>
     <row r="64">
@@ -4449,10 +4449,10 @@
         <v>0.87</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.1542</v>
+        <v>-0.1374</v>
       </c>
       <c r="J64" t="n">
-        <v>-3.7008</v>
+        <v>-3.2976</v>
       </c>
     </row>
     <row r="65">
@@ -4489,10 +4489,10 @@
         <v>0.54</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.6757</v>
+        <v>-0.4548</v>
       </c>
       <c r="J65" t="n">
-        <v>-16.2168</v>
+        <v>-10.9152</v>
       </c>
     </row>
     <row r="66">
@@ -4529,10 +4529,10 @@
         <v>0.47</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.7637</v>
+        <v>-0.5197000000000001</v>
       </c>
       <c r="J66" t="n">
-        <v>-18.3288</v>
+        <v>-12.4728</v>
       </c>
     </row>
     <row r="67">
@@ -4569,10 +4569,10 @@
         <v>1.93</v>
       </c>
       <c r="I67" t="n">
-        <v>1.913</v>
+        <v>1.613</v>
       </c>
       <c r="J67" t="n">
-        <v>45.912</v>
+        <v>38.712</v>
       </c>
     </row>
     <row r="68">
@@ -4609,10 +4609,10 @@
         <v>1.69</v>
       </c>
       <c r="I68" t="n">
-        <v>1.5023</v>
+        <v>1.3342</v>
       </c>
       <c r="J68" t="n">
-        <v>36.0552</v>
+        <v>32.0208</v>
       </c>
     </row>
     <row r="69">
@@ -4649,10 +4649,10 @@
         <v>1.31</v>
       </c>
       <c r="I69" t="n">
-        <v>0.6817</v>
+        <v>0.7819</v>
       </c>
       <c r="J69" t="n">
-        <v>16.3608</v>
+        <v>18.7656</v>
       </c>
     </row>
     <row r="70">
@@ -4689,10 +4689,10 @@
         <v>1.07</v>
       </c>
       <c r="I70" t="n">
-        <v>0.0838</v>
+        <v>0.1725</v>
       </c>
       <c r="J70" t="n">
-        <v>2.0112</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="71">
@@ -4729,10 +4729,10 @@
         <v>0.91</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.4938</v>
+        <v>-0.4156</v>
       </c>
       <c r="J71" t="n">
-        <v>-11.8512</v>
+        <v>-9.974399999999999</v>
       </c>
     </row>
     <row r="72">
@@ -4769,10 +4769,10 @@
         <v>1.68</v>
       </c>
       <c r="I72" t="n">
-        <v>1.4743</v>
+        <v>1.3181</v>
       </c>
       <c r="J72" t="n">
-        <v>29.486</v>
+        <v>26.362</v>
       </c>
     </row>
     <row r="73">
@@ -4809,10 +4809,10 @@
         <v>1.51</v>
       </c>
       <c r="I73" t="n">
-        <v>1.1429</v>
+        <v>1.1156</v>
       </c>
       <c r="J73" t="n">
-        <v>22.858</v>
+        <v>22.312</v>
       </c>
     </row>
     <row r="74">
@@ -4849,10 +4849,10 @@
         <v>1.47</v>
       </c>
       <c r="I74" t="n">
-        <v>1.0582</v>
+        <v>1.0673</v>
       </c>
       <c r="J74" t="n">
-        <v>21.164</v>
+        <v>21.346</v>
       </c>
     </row>
     <row r="75">
@@ -4889,10 +4889,10 @@
         <v>1.22</v>
       </c>
       <c r="I75" t="n">
-        <v>0.4627</v>
+        <v>0.5682</v>
       </c>
       <c r="J75" t="n">
-        <v>9.254</v>
+        <v>11.364</v>
       </c>
     </row>
     <row r="76">
@@ -4929,10 +4929,10 @@
         <v>1.14</v>
       </c>
       <c r="I76" t="n">
-        <v>0.2673</v>
+        <v>0.3656</v>
       </c>
       <c r="J76" t="n">
-        <v>5.346</v>
+        <v>7.312</v>
       </c>
     </row>
     <row r="77">
@@ -4969,10 +4969,10 @@
         <v>1.17</v>
       </c>
       <c r="I77" t="n">
-        <v>0.4247</v>
+        <v>0.4833</v>
       </c>
       <c r="J77" t="n">
-        <v>8.494</v>
+        <v>9.666</v>
       </c>
     </row>
     <row r="78">
@@ -5009,10 +5009,10 @@
         <v>0.78</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.322</v>
+        <v>-0.2324</v>
       </c>
       <c r="J78" t="n">
-        <v>-6.44</v>
+        <v>-4.648</v>
       </c>
     </row>
     <row r="79">
@@ -5049,10 +5049,10 @@
         <v>0.67</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.5052</v>
+        <v>-0.3357</v>
       </c>
       <c r="J79" t="n">
-        <v>-10.104</v>
+        <v>-6.714</v>
       </c>
     </row>
     <row r="80">
@@ -5089,10 +5089,10 @@
         <v>0.67</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.5052</v>
+        <v>-0.3357</v>
       </c>
       <c r="J80" t="n">
-        <v>-10.104</v>
+        <v>-6.714</v>
       </c>
     </row>
     <row r="81">
@@ -5129,10 +5129,10 @@
         <v>0.6</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.6018</v>
+        <v>-0.4015</v>
       </c>
       <c r="J81" t="n">
-        <v>-12.036</v>
+        <v>-8.029999999999999</v>
       </c>
     </row>
     <row r="82">
@@ -5169,10 +5169,10 @@
         <v>1.74</v>
       </c>
       <c r="I82" t="n">
-        <v>1.5404</v>
+        <v>1.3695</v>
       </c>
       <c r="J82" t="n">
-        <v>27.7272</v>
+        <v>24.651</v>
       </c>
     </row>
     <row r="83">
@@ -5209,10 +5209,10 @@
         <v>1.57</v>
       </c>
       <c r="I83" t="n">
-        <v>1.2129</v>
+        <v>1.174</v>
       </c>
       <c r="J83" t="n">
-        <v>21.8322</v>
+        <v>21.132</v>
       </c>
     </row>
     <row r="84">
@@ -5249,10 +5249,10 @@
         <v>1.53</v>
       </c>
       <c r="I84" t="n">
-        <v>1.1264</v>
+        <v>1.1278</v>
       </c>
       <c r="J84" t="n">
-        <v>20.2752</v>
+        <v>20.3004</v>
       </c>
     </row>
     <row r="85">
@@ -5289,10 +5289,10 @@
         <v>1.43</v>
       </c>
       <c r="I85" t="n">
-        <v>0.8895</v>
+        <v>1.0033</v>
       </c>
       <c r="J85" t="n">
-        <v>16.011</v>
+        <v>18.0594</v>
       </c>
     </row>
     <row r="86">
@@ -5329,10 +5329,10 @@
         <v>1.27</v>
       </c>
       <c r="I86" t="n">
-        <v>0.5433</v>
+        <v>0.6655</v>
       </c>
       <c r="J86" t="n">
-        <v>9.779400000000001</v>
+        <v>11.979</v>
       </c>
     </row>
     <row r="87">
@@ -5369,10 +5369,10 @@
         <v>1.15</v>
       </c>
       <c r="I87" t="n">
-        <v>0.4446</v>
+        <v>0.5228</v>
       </c>
       <c r="J87" t="n">
-        <v>8.002800000000001</v>
+        <v>9.410399999999999</v>
       </c>
     </row>
     <row r="88">
@@ -5409,10 +5409,10 @@
         <v>0.85</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.1444</v>
+        <v>-0.1383</v>
       </c>
       <c r="J88" t="n">
-        <v>-2.5992</v>
+        <v>-2.4894</v>
       </c>
     </row>
     <row r="89">
@@ -5449,10 +5449,10 @@
         <v>0.78</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.2565</v>
+        <v>-0.2146</v>
       </c>
       <c r="J89" t="n">
-        <v>-4.617</v>
+        <v>-3.8628</v>
       </c>
     </row>
     <row r="90">
@@ -5489,10 +5489,10 @@
         <v>0.33</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.9171</v>
+        <v>-0.6377</v>
       </c>
       <c r="J90" t="n">
-        <v>-16.5078</v>
+        <v>-11.4786</v>
       </c>
     </row>
     <row r="91">
@@ -5529,10 +5529,10 @@
         <v>0.25</v>
       </c>
       <c r="I91" t="n">
-        <v>-1.0109</v>
+        <v>-0.7128</v>
       </c>
       <c r="J91" t="n">
-        <v>-18.1962</v>
+        <v>-12.8304</v>
       </c>
     </row>
     <row r="92">
@@ -5569,10 +5569,10 @@
         <v>1.35</v>
       </c>
       <c r="I92" t="n">
-        <v>0.5544</v>
+        <v>0.67</v>
       </c>
       <c r="J92" t="n">
-        <v>16.632</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="93">
@@ -5609,10 +5609,10 @@
         <v>1.21</v>
       </c>
       <c r="I93" t="n">
-        <v>0.3661</v>
+        <v>0.4313</v>
       </c>
       <c r="J93" t="n">
-        <v>10.983</v>
+        <v>12.939</v>
       </c>
     </row>
     <row r="94">
@@ -5649,10 +5649,10 @@
         <v>1.2</v>
       </c>
       <c r="I94" t="n">
-        <v>0.3515</v>
+        <v>0.4136</v>
       </c>
       <c r="J94" t="n">
-        <v>10.545</v>
+        <v>12.408</v>
       </c>
     </row>
     <row r="95">
@@ -5689,10 +5689,10 @@
         <v>1.13</v>
       </c>
       <c r="I95" t="n">
-        <v>0.2412</v>
+        <v>0.2859</v>
       </c>
       <c r="J95" t="n">
-        <v>7.236</v>
+        <v>8.577</v>
       </c>
     </row>
     <row r="96">
@@ -5729,10 +5729,10 @@
         <v>0.57</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.6929999999999999</v>
+        <v>-0.465</v>
       </c>
       <c r="J96" t="n">
-        <v>-20.79</v>
+        <v>-13.95</v>
       </c>
     </row>
     <row r="97">
@@ -5769,10 +5769,10 @@
         <v>1.23</v>
       </c>
       <c r="I97" t="n">
-        <v>0.4261</v>
+        <v>0.4933</v>
       </c>
       <c r="J97" t="n">
-        <v>12.783</v>
+        <v>14.799</v>
       </c>
     </row>
     <row r="98">
@@ -5809,10 +5809,10 @@
         <v>1.03</v>
       </c>
       <c r="I98" t="n">
-        <v>0.09229999999999999</v>
+        <v>0.09180000000000001</v>
       </c>
       <c r="J98" t="n">
-        <v>2.769</v>
+        <v>2.754</v>
       </c>
     </row>
     <row r="99">
@@ -5849,10 +5849,10 @@
         <v>1.01</v>
       </c>
       <c r="I99" t="n">
-        <v>0.0404</v>
+        <v>0.0377</v>
       </c>
       <c r="J99" t="n">
-        <v>1.212</v>
+        <v>1.131</v>
       </c>
     </row>
     <row r="100">
@@ -5889,10 +5889,10 @@
         <v>0.92</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.1927</v>
+        <v>-0.1117</v>
       </c>
       <c r="J100" t="n">
-        <v>-5.781</v>
+        <v>-3.351</v>
       </c>
     </row>
     <row r="101">
@@ -5929,10 +5929,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.3691</v>
+        <v>-0.229</v>
       </c>
       <c r="J101" t="n">
-        <v>-11.073</v>
+        <v>-6.87</v>
       </c>
     </row>
     <row r="102">
@@ -5969,10 +5969,10 @@
         <v>1.03</v>
       </c>
       <c r="I102" t="n">
-        <v>0.1851</v>
+        <v>0.165</v>
       </c>
       <c r="J102" t="n">
-        <v>4.4424</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="103">
@@ -6009,10 +6009,10 @@
         <v>0.89</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.1294</v>
+        <v>-0.1189</v>
       </c>
       <c r="J103" t="n">
-        <v>-3.1056</v>
+        <v>-2.8536</v>
       </c>
     </row>
     <row r="104">
@@ -6049,10 +6049,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.2665</v>
+        <v>-0.2039</v>
       </c>
       <c r="J104" t="n">
-        <v>-6.396</v>
+        <v>-4.8936</v>
       </c>
     </row>
     <row r="105">
@@ -6089,10 +6089,10 @@
         <v>0.68</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.4915</v>
+        <v>-0.3266</v>
       </c>
       <c r="J105" t="n">
-        <v>-11.796</v>
+        <v>-7.8384</v>
       </c>
     </row>
     <row r="106">
@@ -6129,10 +6129,10 @@
         <v>0.49</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.743</v>
+        <v>-0.5039</v>
       </c>
       <c r="J106" t="n">
-        <v>-17.832</v>
+        <v>-12.0936</v>
       </c>
     </row>
     <row r="107">
@@ -6169,10 +6169,10 @@
         <v>1.85</v>
       </c>
       <c r="I107" t="n">
-        <v>1.8353</v>
+        <v>1.5514</v>
       </c>
       <c r="J107" t="n">
-        <v>44.0472</v>
+        <v>37.2336</v>
       </c>
     </row>
     <row r="108">
@@ -6209,10 +6209,10 @@
         <v>1.35</v>
       </c>
       <c r="I108" t="n">
-        <v>0.8662</v>
+        <v>0.8875999999999999</v>
       </c>
       <c r="J108" t="n">
-        <v>20.7888</v>
+        <v>21.3024</v>
       </c>
     </row>
     <row r="109">
@@ -6249,10 +6249,10 @@
         <v>1.29</v>
       </c>
       <c r="I109" t="n">
-        <v>0.7197</v>
+        <v>0.7547</v>
       </c>
       <c r="J109" t="n">
-        <v>17.2728</v>
+        <v>18.1128</v>
       </c>
     </row>
     <row r="110">
@@ -6289,10 +6289,10 @@
         <v>1.2</v>
       </c>
       <c r="I110" t="n">
-        <v>0.4702</v>
+        <v>0.5475</v>
       </c>
       <c r="J110" t="n">
-        <v>11.2848</v>
+        <v>13.14</v>
       </c>
     </row>
     <row r="111">
@@ -6329,10 +6329,10 @@
         <v>0.67</v>
       </c>
       <c r="I111" t="n">
-        <v>-1.0321</v>
+        <v>-1.0113</v>
       </c>
       <c r="J111" t="n">
-        <v>-24.7704</v>
+        <v>-24.2712</v>
       </c>
     </row>
     <row r="112">
@@ -6369,10 +6369,10 @@
         <v>0.83</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.155</v>
+        <v>-0.1478</v>
       </c>
       <c r="J112" t="n">
-        <v>-3.1</v>
+        <v>-2.956</v>
       </c>
     </row>
     <row r="113">
@@ -6409,10 +6409,10 @@
         <v>0.68</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.3912</v>
+        <v>-0.3056</v>
       </c>
       <c r="J113" t="n">
-        <v>-7.824</v>
+        <v>-6.112</v>
       </c>
     </row>
     <row r="114">
@@ -6449,10 +6449,10 @@
         <v>0.67</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.4076</v>
+        <v>-0.3152</v>
       </c>
       <c r="J114" t="n">
-        <v>-8.151999999999999</v>
+        <v>-6.304</v>
       </c>
     </row>
     <row r="115">
@@ -6489,10 +6489,10 @@
         <v>0.49</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.7039</v>
+        <v>-0.48</v>
       </c>
       <c r="J115" t="n">
-        <v>-14.078</v>
+        <v>-9.6</v>
       </c>
     </row>
     <row r="116">
@@ -6529,10 +6529,10 @@
         <v>0.48</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.7175</v>
+        <v>-0.4895</v>
       </c>
       <c r="J116" t="n">
-        <v>-14.35</v>
+        <v>-9.789999999999999</v>
       </c>
     </row>
     <row r="117">
@@ -6569,10 +6569,10 @@
         <v>2.24</v>
       </c>
       <c r="I117" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J117" t="n">
-        <v>41.186</v>
+        <v>36.676</v>
       </c>
     </row>
     <row r="118">
@@ -6609,10 +6609,10 @@
         <v>1.6</v>
       </c>
       <c r="I118" t="n">
-        <v>1.2554</v>
+        <v>1.2048</v>
       </c>
       <c r="J118" t="n">
-        <v>25.108</v>
+        <v>24.096</v>
       </c>
     </row>
     <row r="119">
@@ -6649,10 +6649,10 @@
         <v>1.54</v>
       </c>
       <c r="I119" t="n">
-        <v>1.1146</v>
+        <v>1.137</v>
       </c>
       <c r="J119" t="n">
-        <v>22.292</v>
+        <v>22.74</v>
       </c>
     </row>
     <row r="120">
@@ -6689,10 +6689,10 @@
         <v>1.33</v>
       </c>
       <c r="I120" t="n">
-        <v>0.6629</v>
+        <v>0.7951</v>
       </c>
       <c r="J120" t="n">
-        <v>13.258</v>
+        <v>15.902</v>
       </c>
     </row>
     <row r="121">
@@ -6729,10 +6729,10 @@
         <v>1.01</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.1544</v>
+        <v>-0.0684</v>
       </c>
       <c r="J121" t="n">
-        <v>-3.088</v>
+        <v>-1.368</v>
       </c>
     </row>
     <row r="122">
@@ -6769,10 +6769,10 @@
         <v>1.33</v>
       </c>
       <c r="I122" t="n">
-        <v>0.5177</v>
+        <v>0.6264</v>
       </c>
       <c r="J122" t="n">
-        <v>15.0133</v>
+        <v>18.1656</v>
       </c>
     </row>
     <row r="123">
@@ -6809,10 +6809,10 @@
         <v>1.29</v>
       </c>
       <c r="I123" t="n">
-        <v>0.4653</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J123" t="n">
-        <v>13.4937</v>
+        <v>16.24</v>
       </c>
     </row>
     <row r="124">
@@ -6849,10 +6849,10 @@
         <v>1.05</v>
       </c>
       <c r="I124" t="n">
-        <v>0.0679</v>
+        <v>0.1201</v>
       </c>
       <c r="J124" t="n">
-        <v>1.9691</v>
+        <v>3.4829</v>
       </c>
     </row>
     <row r="125">
@@ -6889,10 +6889,10 @@
         <v>1.04</v>
       </c>
       <c r="I125" t="n">
-        <v>0.0481</v>
+        <v>0.0968</v>
       </c>
       <c r="J125" t="n">
-        <v>1.3949</v>
+        <v>2.8072</v>
       </c>
     </row>
     <row r="126">
@@ -6929,10 +6929,10 @@
         <v>0.93</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.2099</v>
+        <v>-0.1136</v>
       </c>
       <c r="J126" t="n">
-        <v>-6.0871</v>
+        <v>-3.2944</v>
       </c>
     </row>
     <row r="127">
@@ -6969,10 +6969,10 @@
         <v>1.1</v>
       </c>
       <c r="I127" t="n">
-        <v>0.38</v>
+        <v>0.3409</v>
       </c>
       <c r="J127" t="n">
-        <v>11.02</v>
+        <v>9.886100000000001</v>
       </c>
     </row>
     <row r="128">
@@ -7009,10 +7009,10 @@
         <v>1.07</v>
       </c>
       <c r="I128" t="n">
-        <v>0.2853</v>
+        <v>0.2529</v>
       </c>
       <c r="J128" t="n">
-        <v>8.2737</v>
+        <v>7.3341</v>
       </c>
     </row>
     <row r="129">
@@ -7049,10 +7049,10 @@
         <v>1.06</v>
       </c>
       <c r="I129" t="n">
-        <v>0.2513</v>
+        <v>0.2224</v>
       </c>
       <c r="J129" t="n">
-        <v>7.2877</v>
+        <v>6.4496</v>
       </c>
     </row>
     <row r="130">
@@ -7089,10 +7089,10 @@
         <v>0.95</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2513</v>
+        <v>-0.2036</v>
       </c>
       <c r="J130" t="n">
-        <v>-7.2877</v>
+        <v>-5.9044</v>
       </c>
     </row>
     <row r="131">
@@ -7129,10 +7129,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.2851</v>
+        <v>-0.2355</v>
       </c>
       <c r="J131" t="n">
-        <v>-8.267899999999999</v>
+        <v>-6.8295</v>
       </c>
     </row>
     <row r="132">
@@ -7169,10 +7169,10 @@
         <v>1.85</v>
       </c>
       <c r="I132" t="n">
-        <v>1.7884</v>
+        <v>1.5215</v>
       </c>
       <c r="J132" t="n">
-        <v>37.5564</v>
+        <v>31.9515</v>
       </c>
     </row>
     <row r="133">
@@ -7209,10 +7209,10 @@
         <v>1.52</v>
       </c>
       <c r="I133" t="n">
-        <v>1.1754</v>
+        <v>1.1312</v>
       </c>
       <c r="J133" t="n">
-        <v>24.6834</v>
+        <v>23.7552</v>
       </c>
     </row>
     <row r="134">
@@ -7249,10 +7249,10 @@
         <v>1.3</v>
       </c>
       <c r="I134" t="n">
-        <v>0.6593</v>
+        <v>0.7599</v>
       </c>
       <c r="J134" t="n">
-        <v>13.8453</v>
+        <v>15.9579</v>
       </c>
     </row>
     <row r="135">
@@ -7289,10 +7289,10 @@
         <v>1.26</v>
       </c>
       <c r="I135" t="n">
-        <v>0.5659</v>
+        <v>0.6683</v>
       </c>
       <c r="J135" t="n">
-        <v>11.8839</v>
+        <v>14.0343</v>
       </c>
     </row>
     <row r="136">
@@ -7329,10 +7329,10 @@
         <v>0.97</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3115</v>
+        <v>-0.2238</v>
       </c>
       <c r="J136" t="n">
-        <v>-6.5415</v>
+        <v>-4.6998</v>
       </c>
     </row>
     <row r="137">
@@ -7369,10 +7369,10 @@
         <v>1.03</v>
       </c>
       <c r="I137" t="n">
-        <v>0.1894</v>
+        <v>0.1702</v>
       </c>
       <c r="J137" t="n">
-        <v>3.9774</v>
+        <v>3.5742</v>
       </c>
     </row>
     <row r="138">
@@ -7409,10 +7409,10 @@
         <v>0.77</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.3367</v>
+        <v>-0.2409</v>
       </c>
       <c r="J138" t="n">
-        <v>-7.0707</v>
+        <v>-5.0589</v>
       </c>
     </row>
     <row r="139">
@@ -7449,10 +7449,10 @@
         <v>0.76</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.3591</v>
+        <v>-0.2499</v>
       </c>
       <c r="J139" t="n">
-        <v>-7.5411</v>
+        <v>-5.2479</v>
       </c>
     </row>
     <row r="140">
@@ -7489,10 +7489,10 @@
         <v>0.74</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.3945</v>
+        <v>-0.2686</v>
       </c>
       <c r="J140" t="n">
-        <v>-8.2845</v>
+        <v>-5.6406</v>
       </c>
     </row>
     <row r="141">
@@ -7529,10 +7529,10 @@
         <v>0.55</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.6652</v>
+        <v>-0.4469</v>
       </c>
       <c r="J141" t="n">
-        <v>-13.9692</v>
+        <v>-9.3849</v>
       </c>
     </row>
     <row r="142">
@@ -7569,10 +7569,10 @@
         <v>1.53</v>
       </c>
       <c r="I142" t="n">
-        <v>1.1879</v>
+        <v>1.1409</v>
       </c>
       <c r="J142" t="n">
-        <v>28.5096</v>
+        <v>27.3816</v>
       </c>
     </row>
     <row r="143">
@@ -7609,10 +7609,10 @@
         <v>1.44</v>
       </c>
       <c r="I143" t="n">
-        <v>0.9965000000000001</v>
+        <v>1.0294</v>
       </c>
       <c r="J143" t="n">
-        <v>23.916</v>
+        <v>24.7056</v>
       </c>
     </row>
     <row r="144">
@@ -7649,10 +7649,10 @@
         <v>1.43</v>
       </c>
       <c r="I144" t="n">
-        <v>0.9736</v>
+        <v>1.015</v>
       </c>
       <c r="J144" t="n">
-        <v>23.3664</v>
+        <v>24.36</v>
       </c>
     </row>
     <row r="145">
@@ -7689,10 +7689,10 @@
         <v>1.37</v>
       </c>
       <c r="I145" t="n">
-        <v>0.8154</v>
+        <v>0.9094</v>
       </c>
       <c r="J145" t="n">
-        <v>19.5696</v>
+        <v>21.8256</v>
       </c>
     </row>
     <row r="146">
@@ -7729,10 +7729,10 @@
         <v>1.21</v>
       </c>
       <c r="I146" t="n">
-        <v>0.4418</v>
+        <v>0.5455</v>
       </c>
       <c r="J146" t="n">
-        <v>10.6032</v>
+        <v>13.092</v>
       </c>
     </row>
     <row r="147">
@@ -7769,10 +7769,10 @@
         <v>0.76</v>
       </c>
       <c r="I147" t="n">
-        <v>-0.3181</v>
+        <v>-0.245</v>
       </c>
       <c r="J147" t="n">
-        <v>-7.6344</v>
+        <v>-5.88</v>
       </c>
     </row>
     <row r="148">
@@ -7809,10 +7809,10 @@
         <v>0.76</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.3181</v>
+        <v>-0.245</v>
       </c>
       <c r="J148" t="n">
-        <v>-7.6344</v>
+        <v>-5.88</v>
       </c>
     </row>
     <row r="149">
@@ -7849,10 +7849,10 @@
         <v>0.71</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.4167</v>
+        <v>-0.2908</v>
       </c>
       <c r="J149" t="n">
-        <v>-10.0008</v>
+        <v>-6.9792</v>
       </c>
     </row>
     <row r="150">
@@ -7889,10 +7889,10 @@
         <v>0.7</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.4343</v>
+        <v>-0.3</v>
       </c>
       <c r="J150" t="n">
-        <v>-10.4232</v>
+        <v>-7.2</v>
       </c>
     </row>
     <row r="151">
@@ -7929,10 +7929,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.451</v>
+        <v>-0.3092</v>
       </c>
       <c r="J151" t="n">
-        <v>-10.824</v>
+        <v>-7.4208</v>
       </c>
     </row>
     <row r="152">
@@ -7969,10 +7969,10 @@
         <v>1.16</v>
       </c>
       <c r="I152" t="n">
-        <v>0.3186</v>
+        <v>0.3595</v>
       </c>
       <c r="J152" t="n">
-        <v>9.558</v>
+        <v>10.785</v>
       </c>
     </row>
     <row r="153">
@@ -8009,10 +8009,10 @@
         <v>1.13</v>
       </c>
       <c r="I153" t="n">
-        <v>0.2716</v>
+        <v>0.302</v>
       </c>
       <c r="J153" t="n">
-        <v>8.148</v>
+        <v>9.06</v>
       </c>
     </row>
     <row r="154">
@@ -8049,10 +8049,10 @@
         <v>1.05</v>
       </c>
       <c r="I154" t="n">
-        <v>0.1279</v>
+        <v>0.1363</v>
       </c>
       <c r="J154" t="n">
-        <v>3.837</v>
+        <v>4.089</v>
       </c>
     </row>
     <row r="155">
@@ -8089,10 +8089,10 @@
         <v>0.89</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.2495</v>
+        <v>-0.1471</v>
       </c>
       <c r="J155" t="n">
-        <v>-7.485</v>
+        <v>-4.413</v>
       </c>
     </row>
     <row r="156">
@@ -8129,10 +8129,10 @@
         <v>0.85</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.3132</v>
+        <v>-0.1898</v>
       </c>
       <c r="J156" t="n">
-        <v>-9.396000000000001</v>
+        <v>-5.694</v>
       </c>
     </row>
     <row r="157">
@@ -8169,10 +8169,10 @@
         <v>1.19</v>
       </c>
       <c r="I157" t="n">
-        <v>0.36</v>
+        <v>0.4125</v>
       </c>
       <c r="J157" t="n">
-        <v>10.8</v>
+        <v>12.375</v>
       </c>
     </row>
     <row r="158">
@@ -8209,10 +8209,10 @@
         <v>1.17</v>
       </c>
       <c r="I158" t="n">
-        <v>0.3303</v>
+        <v>0.3755</v>
       </c>
       <c r="J158" t="n">
-        <v>9.909000000000001</v>
+        <v>11.265</v>
       </c>
     </row>
     <row r="159">
@@ -8249,10 +8249,10 @@
         <v>1.16</v>
       </c>
       <c r="I159" t="n">
-        <v>0.315</v>
+        <v>0.3568</v>
       </c>
       <c r="J159" t="n">
-        <v>9.449999999999999</v>
+        <v>10.704</v>
       </c>
     </row>
     <row r="160">
@@ -8289,10 +8289,10 @@
         <v>0.82</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.3605</v>
+        <v>-0.2218</v>
       </c>
       <c r="J160" t="n">
-        <v>-10.815</v>
+        <v>-6.654</v>
       </c>
     </row>
     <row r="161">
@@ -8329,10 +8329,10 @@
         <v>0.79</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.4036</v>
+        <v>-0.252</v>
       </c>
       <c r="J161" t="n">
-        <v>-12.108</v>
+        <v>-7.56</v>
       </c>
     </row>
     <row r="162">
@@ -8369,10 +8369,10 @@
         <v>1.33</v>
       </c>
       <c r="I162" t="n">
-        <v>0.5437</v>
+        <v>0.6518</v>
       </c>
       <c r="J162" t="n">
-        <v>16.311</v>
+        <v>19.554</v>
       </c>
     </row>
     <row r="163">
@@ -8409,10 +8409,10 @@
         <v>1.24</v>
       </c>
       <c r="I163" t="n">
-        <v>0.4243</v>
+        <v>0.4965</v>
       </c>
       <c r="J163" t="n">
-        <v>12.729</v>
+        <v>14.895</v>
       </c>
     </row>
     <row r="164">
@@ -8449,10 +8449,10 @@
         <v>1.02</v>
       </c>
       <c r="I164" t="n">
-        <v>0.0346</v>
+        <v>0.0603</v>
       </c>
       <c r="J164" t="n">
-        <v>1.038</v>
+        <v>1.809</v>
       </c>
     </row>
     <row r="165">
@@ -8489,10 +8489,10 @@
         <v>0.96</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.1317</v>
+        <v>-0.0678</v>
       </c>
       <c r="J165" t="n">
-        <v>-3.951</v>
+        <v>-2.034</v>
       </c>
     </row>
     <row r="166">
@@ -8529,10 +8529,10 @@
         <v>0.68</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.5536</v>
+        <v>-0.36</v>
       </c>
       <c r="J166" t="n">
-        <v>-16.608</v>
+        <v>-10.8</v>
       </c>
     </row>
     <row r="167">
@@ -8569,10 +8569,10 @@
         <v>1.4</v>
       </c>
       <c r="I167" t="n">
-        <v>0.6308</v>
+        <v>0.7687</v>
       </c>
       <c r="J167" t="n">
-        <v>18.924</v>
+        <v>23.061</v>
       </c>
     </row>
     <row r="168">
@@ -8609,10 +8609,10 @@
         <v>1.03</v>
       </c>
       <c r="I168" t="n">
-        <v>0.0589</v>
+        <v>0.0859</v>
       </c>
       <c r="J168" t="n">
-        <v>1.767</v>
+        <v>2.577</v>
       </c>
     </row>
     <row r="169">
@@ -8649,10 +8649,10 @@
         <v>0.97</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.1106</v>
+        <v>-0.0545</v>
       </c>
       <c r="J169" t="n">
-        <v>-3.318</v>
+        <v>-1.635</v>
       </c>
     </row>
     <row r="170">
@@ -8689,10 +8689,10 @@
         <v>0.93</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.1892</v>
+        <v>-0.1049</v>
       </c>
       <c r="J170" t="n">
-        <v>-5.676</v>
+        <v>-3.147</v>
       </c>
     </row>
     <row r="171">
@@ -8729,10 +8729,10 @@
         <v>0.9</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.2412</v>
+        <v>-0.1393</v>
       </c>
       <c r="J171" t="n">
-        <v>-7.236</v>
+        <v>-4.179</v>
       </c>
     </row>
     <row r="172">
@@ -8769,10 +8769,10 @@
         <v>1.78</v>
       </c>
       <c r="I172" t="n">
-        <v>1.6192</v>
+        <v>1.4177</v>
       </c>
       <c r="J172" t="n">
-        <v>30.7648</v>
+        <v>26.9363</v>
       </c>
     </row>
     <row r="173">
@@ -8809,10 +8809,10 @@
         <v>1.73</v>
       </c>
       <c r="I173" t="n">
-        <v>1.5289</v>
+        <v>1.3606</v>
       </c>
       <c r="J173" t="n">
-        <v>29.0491</v>
+        <v>25.8514</v>
       </c>
     </row>
     <row r="174">
@@ -8849,10 +8849,10 @@
         <v>1.69</v>
       </c>
       <c r="I174" t="n">
-        <v>1.455</v>
+        <v>1.3147</v>
       </c>
       <c r="J174" t="n">
-        <v>27.645</v>
+        <v>24.9793</v>
       </c>
     </row>
     <row r="175">
@@ -8889,10 +8889,10 @@
         <v>1.38</v>
       </c>
       <c r="I175" t="n">
-        <v>0.7886</v>
+        <v>0.914</v>
       </c>
       <c r="J175" t="n">
-        <v>14.9834</v>
+        <v>17.366</v>
       </c>
     </row>
     <row r="176">
@@ -8929,10 +8929,10 @@
         <v>0.88</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.5931</v>
+        <v>-0.5221</v>
       </c>
       <c r="J176" t="n">
-        <v>-11.2689</v>
+        <v>-9.9199</v>
       </c>
     </row>
     <row r="177">
@@ -8969,10 +8969,10 @@
         <v>1.06</v>
       </c>
       <c r="I177" t="n">
-        <v>0.3256</v>
+        <v>0.3655</v>
       </c>
       <c r="J177" t="n">
-        <v>6.1864</v>
+        <v>6.9445</v>
       </c>
     </row>
     <row r="178">
@@ -9009,10 +9009,10 @@
         <v>0.66</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.4133</v>
+        <v>-0.3216</v>
       </c>
       <c r="J178" t="n">
-        <v>-7.8527</v>
+        <v>-6.1104</v>
       </c>
     </row>
     <row r="179">
@@ -9049,10 +9049,10 @@
         <v>0.66</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.4133</v>
+        <v>-0.3216</v>
       </c>
       <c r="J179" t="n">
-        <v>-7.8527</v>
+        <v>-6.1104</v>
       </c>
     </row>
     <row r="180">
@@ -9089,10 +9089,10 @@
         <v>0.38</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.844</v>
+        <v>-0.5816</v>
       </c>
       <c r="J180" t="n">
-        <v>-16.036</v>
+        <v>-11.0504</v>
       </c>
     </row>
     <row r="181">
@@ -9129,10 +9129,10 @@
         <v>0.31</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.9312</v>
+        <v>-0.6485</v>
       </c>
       <c r="J181" t="n">
-        <v>-17.6928</v>
+        <v>-12.3215</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2998/event_2998_evp_summary.xlsx
+++ b/database/event/2998/event_2998_evp_summary.xlsx
@@ -492,127 +492,127 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.0124</v>
+        <v>3.823</v>
       </c>
       <c r="C2" t="n">
-        <v>1.505</v>
+        <v>1.4339</v>
       </c>
       <c r="D2" t="n">
-        <v>1.1734</v>
+        <v>1.1161</v>
       </c>
       <c r="E2" t="n">
-        <v>4.0124</v>
+        <v>3.823</v>
       </c>
       <c r="F2" t="n">
-        <v>3.6437</v>
+        <v>0.1791</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3687</v>
+        <v>3.6439</v>
       </c>
       <c r="H2" t="n">
-        <v>4.6411</v>
+        <v>0.1791</v>
       </c>
       <c r="I2" t="n">
-        <v>4.832</v>
+        <v>0.1791</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3687</v>
+        <v>3.6439</v>
       </c>
       <c r="K2" t="n">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="L2" t="n">
         <v>86</v>
       </c>
       <c r="M2" t="n">
-        <v>5.200699999999999</v>
+        <v>3.823</v>
       </c>
       <c r="N2" t="n">
-        <v>206</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.9435</v>
+        <v>3.7022</v>
       </c>
       <c r="C3" t="n">
-        <v>1.4791</v>
+        <v>1.3886</v>
       </c>
       <c r="D3" t="n">
-        <v>1.1423</v>
+        <v>1.0611</v>
       </c>
       <c r="E3" t="n">
-        <v>3.9435</v>
+        <v>3.7022</v>
       </c>
       <c r="F3" t="n">
-        <v>3.3924</v>
+        <v>3.3459</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5511</v>
+        <v>0.3563</v>
       </c>
       <c r="H3" t="n">
-        <v>4.0894</v>
+        <v>4.5982</v>
       </c>
       <c r="I3" t="n">
-        <v>4.0894</v>
+        <v>4.7167</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5511</v>
+        <v>0.3563</v>
       </c>
       <c r="K3" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="L3" t="n">
         <v>86</v>
       </c>
       <c r="M3" t="n">
-        <v>4.6405</v>
+        <v>5.073</v>
       </c>
       <c r="N3" t="n">
-        <v>201</v>
+        <v>206</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>boltz</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.8359</v>
+        <v>3.6901</v>
       </c>
       <c r="C4" t="n">
-        <v>1.4388</v>
+        <v>1.3841</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0937</v>
+        <v>1.0556</v>
       </c>
       <c r="E4" t="n">
-        <v>3.8359</v>
+        <v>3.6901</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1114</v>
+        <v>3.1393</v>
       </c>
       <c r="G4" t="n">
-        <v>1.7245</v>
+        <v>0.5508</v>
       </c>
       <c r="H4" t="n">
-        <v>2.1114</v>
+        <v>4.1459</v>
       </c>
       <c r="I4" t="n">
-        <v>2.1114</v>
+        <v>4.1459</v>
       </c>
       <c r="J4" t="n">
-        <v>1.7245</v>
+        <v>0.5508</v>
       </c>
       <c r="K4" t="n">
         <v>115</v>
@@ -621,7 +621,7 @@
         <v>86</v>
       </c>
       <c r="M4" t="n">
-        <v>3.8359</v>
+        <v>4.6967</v>
       </c>
       <c r="N4" t="n">
         <v>201</v>
@@ -630,35 +630,35 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>boltz</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.6438</v>
+        <v>3.6021</v>
       </c>
       <c r="C5" t="n">
-        <v>1.3667</v>
+        <v>1.3511</v>
       </c>
       <c r="D5" t="n">
-        <v>1.007</v>
+        <v>1.0155</v>
       </c>
       <c r="E5" t="n">
-        <v>3.6438</v>
+        <v>3.6021</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1954</v>
+        <v>1.9793</v>
       </c>
       <c r="G5" t="n">
-        <v>3.4484</v>
+        <v>1.6228</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1954</v>
+        <v>1.9793</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1954</v>
+        <v>1.9793</v>
       </c>
       <c r="J5" t="n">
-        <v>3.4484</v>
+        <v>1.6228</v>
       </c>
       <c r="K5" t="n">
         <v>115</v>
@@ -667,7 +667,7 @@
         <v>86</v>
       </c>
       <c r="M5" t="n">
-        <v>3.6438</v>
+        <v>3.6021</v>
       </c>
       <c r="N5" t="n">
         <v>201</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.2891</v>
+        <v>3.0132</v>
       </c>
       <c r="C6" t="n">
-        <v>1.2337</v>
+        <v>1.1302</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8469</v>
+        <v>0.7475000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>3.2891</v>
+        <v>3.0132</v>
       </c>
       <c r="F6" t="n">
-        <v>3.3715</v>
+        <v>3.1078</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0824</v>
+        <v>-0.0946</v>
       </c>
       <c r="H6" t="n">
-        <v>4.0434</v>
+        <v>4.0771</v>
       </c>
       <c r="I6" t="n">
-        <v>4.2097</v>
+        <v>4.1822</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.0824</v>
+        <v>-0.0946</v>
       </c>
       <c r="K6" t="n">
         <v>120</v>
@@ -713,7 +713,7 @@
         <v>86</v>
       </c>
       <c r="M6" t="n">
-        <v>4.1273</v>
+        <v>4.0876</v>
       </c>
       <c r="N6" t="n">
         <v>206</v>
@@ -726,28 +726,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.2138</v>
+        <v>2.9216</v>
       </c>
       <c r="C7" t="n">
-        <v>1.2054</v>
+        <v>1.0958</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8129</v>
+        <v>0.7058</v>
       </c>
       <c r="E7" t="n">
-        <v>3.2138</v>
+        <v>2.9216</v>
       </c>
       <c r="F7" t="n">
-        <v>3.2138</v>
+        <v>2.9216</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>3.6972</v>
+        <v>3.6695</v>
       </c>
       <c r="I7" t="n">
-        <v>3.6972</v>
+        <v>3.6695</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -759,7 +759,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.6972</v>
+        <v>3.6695</v>
       </c>
       <c r="N7" t="n">
         <v>137</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.0665</v>
+        <v>2.7546</v>
       </c>
       <c r="C8" t="n">
-        <v>1.1502</v>
+        <v>1.0332</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7464</v>
+        <v>0.6297</v>
       </c>
       <c r="E8" t="n">
-        <v>3.0665</v>
+        <v>2.7546</v>
       </c>
       <c r="F8" t="n">
-        <v>3.2112</v>
+        <v>2.9227</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1447</v>
+        <v>-0.1681</v>
       </c>
       <c r="H8" t="n">
-        <v>3.6915</v>
+        <v>3.6719</v>
       </c>
       <c r="I8" t="n">
-        <v>3.8433</v>
+        <v>3.7665</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1447</v>
+        <v>-0.1681</v>
       </c>
       <c r="K8" t="n">
         <v>120</v>
@@ -805,7 +805,7 @@
         <v>86</v>
       </c>
       <c r="M8" t="n">
-        <v>3.6986</v>
+        <v>3.5984</v>
       </c>
       <c r="N8" t="n">
         <v>206</v>
@@ -818,28 +818,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.919</v>
+        <v>2.6412</v>
       </c>
       <c r="C9" t="n">
-        <v>1.0949</v>
+        <v>0.9907</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6798</v>
+        <v>0.5780999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>2.919</v>
+        <v>2.6412</v>
       </c>
       <c r="F9" t="n">
-        <v>2.919</v>
+        <v>2.6412</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>3.0499</v>
+        <v>3.0558</v>
       </c>
       <c r="I9" t="n">
-        <v>3.0499</v>
+        <v>3.0558</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.0499</v>
+        <v>3.0558</v>
       </c>
       <c r="N9" t="n">
         <v>137</v>
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.3076</v>
+        <v>2.2654</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8655</v>
+        <v>0.8497</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4038</v>
+        <v>0.4071</v>
       </c>
       <c r="E10" t="n">
-        <v>2.3076</v>
+        <v>2.2654</v>
       </c>
       <c r="F10" t="n">
-        <v>2.3076</v>
+        <v>2.2654</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2.3076</v>
+        <v>2.2654</v>
       </c>
       <c r="I10" t="n">
-        <v>2.3076</v>
+        <v>2.2654</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.3076</v>
+        <v>2.2654</v>
       </c>
       <c r="N10" t="n">
         <v>137</v>
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.9632</v>
+        <v>1.8584</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7364000000000001</v>
+        <v>0.6971000000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2483</v>
+        <v>0.2218</v>
       </c>
       <c r="E11" t="n">
-        <v>1.9632</v>
+        <v>1.8584</v>
       </c>
       <c r="F11" t="n">
-        <v>1.9632</v>
+        <v>1.8584</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1.9632</v>
+        <v>1.8584</v>
       </c>
       <c r="I11" t="n">
-        <v>1.9632</v>
+        <v>1.8584</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1.9632</v>
+        <v>1.8584</v>
       </c>
       <c r="N11" t="n">
         <v>112</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.6608</v>
+        <v>1.6797</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6229</v>
+        <v>0.63</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1118</v>
+        <v>0.1404</v>
       </c>
       <c r="E12" t="n">
-        <v>1.6608</v>
+        <v>1.6797</v>
       </c>
       <c r="F12" t="n">
-        <v>1.7315</v>
+        <v>1.7737</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.0707</v>
+        <v>-0.094</v>
       </c>
       <c r="H12" t="n">
-        <v>1.7315</v>
+        <v>1.7737</v>
       </c>
       <c r="I12" t="n">
-        <v>1.8027</v>
+        <v>1.8194</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.0707</v>
+        <v>-0.094</v>
       </c>
       <c r="K12" t="n">
         <v>120</v>
@@ -989,7 +989,7 @@
         <v>86</v>
       </c>
       <c r="M12" t="n">
-        <v>1.732</v>
+        <v>1.7254</v>
       </c>
       <c r="N12" t="n">
         <v>206</v>
@@ -1002,28 +1002,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.2876</v>
+        <v>1.2372</v>
       </c>
       <c r="C13" t="n">
-        <v>0.483</v>
+        <v>0.4641</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0567</v>
+        <v>-0.061</v>
       </c>
       <c r="E13" t="n">
-        <v>1.2876</v>
+        <v>1.2372</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2876</v>
+        <v>1.2372</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1.2876</v>
+        <v>1.2372</v>
       </c>
       <c r="I13" t="n">
-        <v>1.2876</v>
+        <v>1.2372</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.2876</v>
+        <v>1.2372</v>
       </c>
       <c r="N13" t="n">
         <v>137</v>
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.0361</v>
+        <v>0.9496</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3886</v>
+        <v>0.3562</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1703</v>
+        <v>-0.1919</v>
       </c>
       <c r="E14" t="n">
-        <v>1.0361</v>
+        <v>0.9496</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0361</v>
+        <v>0.9496</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1.0361</v>
+        <v>0.9496</v>
       </c>
       <c r="I14" t="n">
-        <v>1.0361</v>
+        <v>0.9496</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.0361</v>
+        <v>0.9496</v>
       </c>
       <c r="N14" t="n">
         <v>121</v>
@@ -1090,93 +1090,93 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9308999999999999</v>
+        <v>0.8541</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3492</v>
+        <v>0.3204</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2178</v>
+        <v>-0.2354</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9308999999999999</v>
+        <v>0.8541</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9308999999999999</v>
+        <v>1.1365</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>-0.2824</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9308999999999999</v>
+        <v>1.1365</v>
       </c>
       <c r="I15" t="n">
-        <v>0.9308999999999999</v>
+        <v>1.1365</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>-0.2824</v>
       </c>
       <c r="K15" t="n">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9308999999999999</v>
+        <v>0.8541000000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>135</v>
+        <v>201</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8643</v>
+        <v>0.8486</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3242</v>
+        <v>0.3183</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2478</v>
+        <v>-0.2379</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8643</v>
+        <v>0.8486</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1763</v>
+        <v>0.8486</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.312</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1763</v>
+        <v>0.8486</v>
       </c>
       <c r="I16" t="n">
-        <v>1.1763</v>
+        <v>0.8486</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.312</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="L16" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.8642999999999998</v>
+        <v>0.8486</v>
       </c>
       <c r="N16" t="n">
-        <v>201</v>
+        <v>135</v>
       </c>
     </row>
     <row r="17">
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8373</v>
+        <v>0.7348</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3141</v>
+        <v>0.2756</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.26</v>
+        <v>-0.2897</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8373</v>
+        <v>0.7348</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8373</v>
+        <v>0.7348</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8373</v>
+        <v>0.7348</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8373</v>
+        <v>0.7348</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.8373</v>
+        <v>0.7348</v>
       </c>
       <c r="N17" t="n">
         <v>121</v>
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6524</v>
+        <v>0.5588</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2447</v>
+        <v>0.2096</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3435</v>
+        <v>-0.3698</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6524</v>
+        <v>0.5588</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6524</v>
+        <v>0.5588</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6524</v>
+        <v>0.5588</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6524</v>
+        <v>0.5588</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.6524</v>
+        <v>0.5588</v>
       </c>
       <c r="N18" t="n">
         <v>121</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.5693</v>
+        <v>0.5115</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2135</v>
+        <v>0.1919</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.381</v>
+        <v>-0.3914</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5693</v>
+        <v>0.5115</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5693</v>
+        <v>0.5115</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5693</v>
+        <v>0.5115</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5693</v>
+        <v>0.5115</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5693</v>
+        <v>0.5115</v>
       </c>
       <c r="N19" t="n">
         <v>135</v>
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5151</v>
+        <v>0.4932</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1932</v>
+        <v>0.185</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4055</v>
+        <v>-0.3997</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5151</v>
+        <v>0.4932</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7766</v>
+        <v>0.7272</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.2615</v>
+        <v>-0.234</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7766</v>
+        <v>0.7272</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7766</v>
+        <v>0.7272</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.2615</v>
+        <v>-0.234</v>
       </c>
       <c r="K20" t="n">
         <v>115</v>
@@ -1357,7 +1357,7 @@
         <v>86</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5150999999999999</v>
+        <v>0.4932</v>
       </c>
       <c r="N20" t="n">
         <v>201</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2275</v>
+        <v>0.1551</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0853</v>
+        <v>0.0582</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5353</v>
+        <v>-0.5536</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2275</v>
+        <v>0.1551</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2275</v>
+        <v>0.1551</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2275</v>
+        <v>0.1551</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2275</v>
+        <v>0.1551</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2275</v>
+        <v>0.1551</v>
       </c>
       <c r="N21" t="n">
         <v>112</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.1682</v>
+        <v>0.0828</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0631</v>
+        <v>0.0311</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5621</v>
+        <v>-0.5865</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1682</v>
+        <v>0.0828</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1682</v>
+        <v>0.0828</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1682</v>
+        <v>0.0828</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1682</v>
+        <v>0.0828</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1682</v>
+        <v>0.0828</v>
       </c>
       <c r="N22" t="n">
         <v>112</v>
@@ -1462,31 +1462,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1065</v>
+        <v>0.0747</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0399</v>
+        <v>0.028</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.5899</v>
+        <v>-0.5901999999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1065</v>
+        <v>0.0747</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5499000000000001</v>
+        <v>0.5505</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.4434</v>
+        <v>-0.4758</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5499000000000001</v>
+        <v>0.5505</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5725</v>
+        <v>0.5647</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.4434</v>
+        <v>-0.4758</v>
       </c>
       <c r="K23" t="n">
         <v>120</v>
@@ -1495,7 +1495,7 @@
         <v>86</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1291</v>
+        <v>0.08889999999999998</v>
       </c>
       <c r="N23" t="n">
         <v>206</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.0696</v>
+        <v>-0.0143</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0261</v>
+        <v>-0.0054</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.6066</v>
+        <v>-0.6307</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0696</v>
+        <v>-0.0143</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0696</v>
+        <v>-0.0143</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0696</v>
+        <v>-0.0143</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0696</v>
+        <v>-0.0143</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.0696</v>
+        <v>-0.0143</v>
       </c>
       <c r="N24" t="n">
         <v>112</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.1161</v>
+        <v>-0.1959</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.0435</v>
+        <v>-0.0735</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.6904</v>
+        <v>-0.7134</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.1161</v>
+        <v>-0.1959</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.1161</v>
+        <v>-0.1959</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.1161</v>
+        <v>-0.1959</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1161</v>
+        <v>-0.1959</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.1161</v>
+        <v>-0.1959</v>
       </c>
       <c r="N25" t="n">
         <v>112</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.2741</v>
+        <v>-0.2983</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.1028</v>
+        <v>-0.1119</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.7618</v>
+        <v>-0.76</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.2741</v>
+        <v>-0.2983</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.2741</v>
+        <v>-0.2983</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.2741</v>
+        <v>-0.2983</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.2741</v>
+        <v>-0.2983</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.2741</v>
+        <v>-0.2983</v>
       </c>
       <c r="N26" t="n">
         <v>135</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.3645</v>
+        <v>-0.4391</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.1367</v>
+        <v>-0.1647</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.8026</v>
+        <v>-0.8241000000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.3645</v>
+        <v>-0.4391</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.3645</v>
+        <v>-0.4391</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.3645</v>
+        <v>-0.4391</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.3645</v>
+        <v>-0.4391</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.3645</v>
+        <v>-0.4391</v>
       </c>
       <c r="N27" t="n">
         <v>121</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.4786</v>
+        <v>-0.4937</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.1795</v>
+        <v>-0.1852</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.8541</v>
+        <v>-0.8489</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.4786</v>
+        <v>-0.4937</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.4786</v>
+        <v>-0.4937</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.4786</v>
+        <v>-0.4937</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.4786</v>
+        <v>-0.4937</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.4786</v>
+        <v>-0.4937</v>
       </c>
       <c r="N28" t="n">
         <v>135</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.7044</v>
+        <v>-0.7482</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.2642</v>
+        <v>-0.2806</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.956</v>
+        <v>-0.9648</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.7044</v>
+        <v>-0.7482</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.7044</v>
+        <v>-0.7482</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.7044</v>
+        <v>-0.7482</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.7044</v>
+        <v>-0.7482</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.7044</v>
+        <v>-0.7482</v>
       </c>
       <c r="N29" t="n">
         <v>135</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-1.0433</v>
+        <v>-1.0624</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.3913</v>
+        <v>-0.3985</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.109</v>
+        <v>-1.1078</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.0433</v>
+        <v>-1.0624</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.0433</v>
+        <v>-1.0624</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-1.0433</v>
+        <v>-1.0624</v>
       </c>
       <c r="I30" t="n">
-        <v>-1.0433</v>
+        <v>-1.0624</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-1.0433</v>
+        <v>-1.0624</v>
       </c>
       <c r="N30" t="n">
         <v>121</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-1.8563</v>
+        <v>-1.7389</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.6963</v>
+        <v>-0.6522</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.476</v>
+        <v>-1.4158</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.8563</v>
+        <v>-1.7389</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.8563</v>
+        <v>-1.7389</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-1.8563</v>
+        <v>-1.7389</v>
       </c>
       <c r="I31" t="n">
-        <v>-1.8563</v>
+        <v>-1.7389</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-1.8563</v>
+        <v>-1.7389</v>
       </c>
       <c r="N31" t="n">
         <v>137</v>
@@ -1969,10 +1969,10 @@
         <v>1.42</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5427</v>
+        <v>0.5481</v>
       </c>
       <c r="J2" t="n">
-        <v>14.6529</v>
+        <v>14.7987</v>
       </c>
     </row>
     <row r="3">
@@ -2009,10 +2009,10 @@
         <v>1.35</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4629</v>
+        <v>0.4728</v>
       </c>
       <c r="J3" t="n">
-        <v>12.4983</v>
+        <v>12.7656</v>
       </c>
     </row>
     <row r="4">
@@ -2049,10 +2049,10 @@
         <v>1.3</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4048</v>
+        <v>0.4174</v>
       </c>
       <c r="J4" t="n">
-        <v>10.9296</v>
+        <v>11.2698</v>
       </c>
     </row>
     <row r="5">
@@ -2089,10 +2089,10 @@
         <v>1.04</v>
       </c>
       <c r="I5" t="n">
-        <v>0.06469999999999999</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>1.7469</v>
+        <v>2.1384</v>
       </c>
     </row>
     <row r="6">
@@ -2129,10 +2129,10 @@
         <v>0.7</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3525</v>
+        <v>-0.3605</v>
       </c>
       <c r="J6" t="n">
-        <v>-9.5175</v>
+        <v>-9.733499999999999</v>
       </c>
     </row>
     <row r="7">
@@ -2169,10 +2169,10 @@
         <v>1.42</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6284</v>
+        <v>0.6118</v>
       </c>
       <c r="J7" t="n">
-        <v>16.9668</v>
+        <v>16.5186</v>
       </c>
     </row>
     <row r="8">
@@ -2209,10 +2209,10 @@
         <v>0.92</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1117</v>
+        <v>-0.1236</v>
       </c>
       <c r="J8" t="n">
-        <v>-3.0159</v>
+        <v>-3.3372</v>
       </c>
     </row>
     <row r="9">
@@ -2249,10 +2249,10 @@
         <v>0.9</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1342</v>
+        <v>-0.1469</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.6234</v>
+        <v>-3.9663</v>
       </c>
     </row>
     <row r="10">
@@ -2289,10 +2289,10 @@
         <v>0.89</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1453</v>
+        <v>-0.1582</v>
       </c>
       <c r="J10" t="n">
-        <v>-3.9231</v>
+        <v>-4.2714</v>
       </c>
     </row>
     <row r="11">
@@ -2329,10 +2329,10 @@
         <v>0.87</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1669</v>
+        <v>-0.1802</v>
       </c>
       <c r="J11" t="n">
-        <v>-4.5063</v>
+        <v>-4.8654</v>
       </c>
     </row>
     <row r="12">
@@ -2369,10 +2369,10 @@
         <v>1.06</v>
       </c>
       <c r="I12" t="n">
-        <v>0.223</v>
+        <v>0.2149</v>
       </c>
       <c r="J12" t="n">
-        <v>5.352</v>
+        <v>5.1576</v>
       </c>
     </row>
     <row r="13">
@@ -2409,10 +2409,10 @@
         <v>1.01</v>
       </c>
       <c r="I13" t="n">
-        <v>0.09</v>
+        <v>0.0813</v>
       </c>
       <c r="J13" t="n">
-        <v>2.16</v>
+        <v>1.9512</v>
       </c>
     </row>
     <row r="14">
@@ -2449,10 +2449,10 @@
         <v>0.76</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2554</v>
+        <v>-0.2733</v>
       </c>
       <c r="J14" t="n">
-        <v>-6.1296</v>
+        <v>-6.5592</v>
       </c>
     </row>
     <row r="15">
@@ -2489,10 +2489,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3223</v>
+        <v>-0.3385</v>
       </c>
       <c r="J15" t="n">
-        <v>-7.7352</v>
+        <v>-8.124000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -2529,10 +2529,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4442</v>
+        <v>-0.455</v>
       </c>
       <c r="J16" t="n">
-        <v>-10.6608</v>
+        <v>-10.92</v>
       </c>
     </row>
     <row r="17">
@@ -2569,10 +2569,10 @@
         <v>1.67</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3449</v>
+        <v>1.4338</v>
       </c>
       <c r="J17" t="n">
-        <v>32.2776</v>
+        <v>34.4112</v>
       </c>
     </row>
     <row r="18">
@@ -2609,10 +2609,10 @@
         <v>1.43</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0424</v>
+        <v>0.9989</v>
       </c>
       <c r="J18" t="n">
-        <v>25.0176</v>
+        <v>23.9736</v>
       </c>
     </row>
     <row r="19">
@@ -2649,10 +2649,10 @@
         <v>1.12</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3496</v>
+        <v>0.3555</v>
       </c>
       <c r="J19" t="n">
-        <v>8.3904</v>
+        <v>8.532</v>
       </c>
     </row>
     <row r="20">
@@ -2689,10 +2689,10 @@
         <v>1.09</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2654</v>
+        <v>0.2779</v>
       </c>
       <c r="J20" t="n">
-        <v>6.3696</v>
+        <v>6.6696</v>
       </c>
     </row>
     <row r="21">
@@ -2729,10 +2729,10 @@
         <v>0.87</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4971</v>
+        <v>-0.4638</v>
       </c>
       <c r="J21" t="n">
-        <v>-11.9304</v>
+        <v>-11.1312</v>
       </c>
     </row>
     <row r="22">
@@ -2769,10 +2769,10 @@
         <v>1.06</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2193</v>
+        <v>0.2122</v>
       </c>
       <c r="J22" t="n">
-        <v>7.6755</v>
+        <v>7.427</v>
       </c>
     </row>
     <row r="23">
@@ -2809,10 +2809,10 @@
         <v>0.85</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1692</v>
+        <v>-0.1871</v>
       </c>
       <c r="J23" t="n">
-        <v>-5.922</v>
+        <v>-6.5485</v>
       </c>
     </row>
     <row r="24">
@@ -2849,10 +2849,10 @@
         <v>0.78</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2371</v>
+        <v>-0.2551</v>
       </c>
       <c r="J24" t="n">
-        <v>-8.298500000000001</v>
+        <v>-8.9285</v>
       </c>
     </row>
     <row r="25">
@@ -2889,10 +2889,10 @@
         <v>0.73</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2853</v>
+        <v>-0.3024</v>
       </c>
       <c r="J25" t="n">
-        <v>-9.9855</v>
+        <v>-10.584</v>
       </c>
     </row>
     <row r="26">
@@ -2929,10 +2929,10 @@
         <v>0.7</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3139</v>
+        <v>-0.3302</v>
       </c>
       <c r="J26" t="n">
-        <v>-10.9865</v>
+        <v>-11.557</v>
       </c>
     </row>
     <row r="27">
@@ -2969,10 +2969,10 @@
         <v>1.78</v>
       </c>
       <c r="I27" t="n">
-        <v>1.4751</v>
+        <v>1.5983</v>
       </c>
       <c r="J27" t="n">
-        <v>51.6285</v>
+        <v>55.9405</v>
       </c>
     </row>
     <row r="28">
@@ -3009,10 +3009,10 @@
         <v>1.33</v>
       </c>
       <c r="I28" t="n">
-        <v>0.849</v>
+        <v>0.8041</v>
       </c>
       <c r="J28" t="n">
-        <v>29.715</v>
+        <v>28.1435</v>
       </c>
     </row>
     <row r="29">
@@ -3049,10 +3049,10 @@
         <v>1.12</v>
       </c>
       <c r="I29" t="n">
-        <v>0.3468</v>
+        <v>0.3535</v>
       </c>
       <c r="J29" t="n">
-        <v>12.138</v>
+        <v>12.3725</v>
       </c>
     </row>
     <row r="30">
@@ -3089,10 +3089,10 @@
         <v>1.11</v>
       </c>
       <c r="I30" t="n">
-        <v>0.3193</v>
+        <v>0.3283</v>
       </c>
       <c r="J30" t="n">
-        <v>11.1755</v>
+        <v>11.4905</v>
       </c>
     </row>
     <row r="31">
@@ -3129,10 +3129,10 @@
         <v>0.9</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4152</v>
+        <v>-0.3883</v>
       </c>
       <c r="J31" t="n">
-        <v>-14.532</v>
+        <v>-13.5905</v>
       </c>
     </row>
     <row r="32">
@@ -3169,10 +3169,10 @@
         <v>1.33</v>
       </c>
       <c r="I32" t="n">
-        <v>0.9056</v>
+        <v>0.8437</v>
       </c>
       <c r="J32" t="n">
-        <v>27.168</v>
+        <v>25.311</v>
       </c>
     </row>
     <row r="33">
@@ -3209,10 +3209,10 @@
         <v>1.06</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2118</v>
+        <v>0.2187</v>
       </c>
       <c r="J33" t="n">
-        <v>6.354</v>
+        <v>6.561</v>
       </c>
     </row>
     <row r="34">
@@ -3249,10 +3249,10 @@
         <v>1.02</v>
       </c>
       <c r="I34" t="n">
-        <v>0.0771</v>
+        <v>0.0883</v>
       </c>
       <c r="J34" t="n">
-        <v>2.313</v>
+        <v>2.649</v>
       </c>
     </row>
     <row r="35">
@@ -3289,10 +3289,10 @@
         <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.0183</v>
+        <v>-0.0125</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.549</v>
+        <v>-0.375</v>
       </c>
     </row>
     <row r="36">
@@ -3329,10 +3329,10 @@
         <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.0183</v>
+        <v>-0.0125</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.549</v>
+        <v>-0.375</v>
       </c>
     </row>
     <row r="37">
@@ -3369,10 +3369,10 @@
         <v>1.11</v>
       </c>
       <c r="I37" t="n">
-        <v>0.2682</v>
+        <v>0.273</v>
       </c>
       <c r="J37" t="n">
-        <v>8.045999999999999</v>
+        <v>8.19</v>
       </c>
     </row>
     <row r="38">
@@ -3409,10 +3409,10 @@
         <v>1.08</v>
       </c>
       <c r="I38" t="n">
-        <v>0.2063</v>
+        <v>0.2134</v>
       </c>
       <c r="J38" t="n">
-        <v>6.189</v>
+        <v>6.402</v>
       </c>
     </row>
     <row r="39">
@@ -3449,10 +3449,10 @@
         <v>1.03</v>
       </c>
       <c r="I39" t="n">
-        <v>0.0929</v>
+        <v>0.1007</v>
       </c>
       <c r="J39" t="n">
-        <v>2.787</v>
+        <v>3.021</v>
       </c>
     </row>
     <row r="40">
@@ -3489,10 +3489,10 @@
         <v>0.88</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.1554</v>
+        <v>-0.1688</v>
       </c>
       <c r="J40" t="n">
-        <v>-4.662</v>
+        <v>-5.064</v>
       </c>
     </row>
     <row r="41">
@@ -3529,10 +3529,10 @@
         <v>0.87</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.1662</v>
+        <v>-0.1797</v>
       </c>
       <c r="J41" t="n">
-        <v>-4.986</v>
+        <v>-5.391</v>
       </c>
     </row>
     <row r="42">
@@ -3569,10 +3569,10 @@
         <v>1.52</v>
       </c>
       <c r="I42" t="n">
-        <v>1.002</v>
+        <v>0.9481000000000001</v>
       </c>
       <c r="J42" t="n">
-        <v>28.056</v>
+        <v>26.5468</v>
       </c>
     </row>
     <row r="43">
@@ -3609,10 +3609,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.0832</v>
+        <v>-0.0953</v>
       </c>
       <c r="J43" t="n">
-        <v>-2.3296</v>
+        <v>-2.6684</v>
       </c>
     </row>
     <row r="44">
@@ -3649,10 +3649,10 @@
         <v>0.88</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.15</v>
+        <v>-0.1646</v>
       </c>
       <c r="J44" t="n">
-        <v>-4.2</v>
+        <v>-4.6088</v>
       </c>
     </row>
     <row r="45">
@@ -3689,10 +3689,10 @@
         <v>0.8</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.2326</v>
+        <v>-0.2474</v>
       </c>
       <c r="J45" t="n">
-        <v>-6.5128</v>
+        <v>-6.9272</v>
       </c>
     </row>
     <row r="46">
@@ -3729,10 +3729,10 @@
         <v>0.59</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.4326</v>
+        <v>-0.4414</v>
       </c>
       <c r="J46" t="n">
-        <v>-12.1128</v>
+        <v>-12.3592</v>
       </c>
     </row>
     <row r="47">
@@ -3769,10 +3769,10 @@
         <v>1.53</v>
       </c>
       <c r="I47" t="n">
-        <v>1.1928</v>
+        <v>1.1568</v>
       </c>
       <c r="J47" t="n">
-        <v>33.3984</v>
+        <v>32.3904</v>
       </c>
     </row>
     <row r="48">
@@ -3809,10 +3809,10 @@
         <v>1.42</v>
       </c>
       <c r="I48" t="n">
-        <v>1.0485</v>
+        <v>0.9958</v>
       </c>
       <c r="J48" t="n">
-        <v>29.358</v>
+        <v>27.8824</v>
       </c>
     </row>
     <row r="49">
@@ -3849,10 +3849,10 @@
         <v>1.09</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2852</v>
+        <v>0.2915</v>
       </c>
       <c r="J49" t="n">
-        <v>7.9856</v>
+        <v>8.162000000000001</v>
       </c>
     </row>
     <row r="50">
@@ -3889,10 +3889,10 @@
         <v>0.98</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1324</v>
+        <v>-0.1263</v>
       </c>
       <c r="J50" t="n">
-        <v>-3.7072</v>
+        <v>-3.5364</v>
       </c>
     </row>
     <row r="51">
@@ -3929,10 +3929,10 @@
         <v>0.74</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.8153</v>
+        <v>-0.7513</v>
       </c>
       <c r="J51" t="n">
-        <v>-22.8284</v>
+        <v>-21.0364</v>
       </c>
     </row>
     <row r="52">
@@ -3969,10 +3969,10 @@
         <v>1.59</v>
       </c>
       <c r="I52" t="n">
-        <v>1.2234</v>
+        <v>1.1977</v>
       </c>
       <c r="J52" t="n">
-        <v>28.1382</v>
+        <v>27.5471</v>
       </c>
     </row>
     <row r="53">
@@ -4009,10 +4009,10 @@
         <v>1.48</v>
       </c>
       <c r="I53" t="n">
-        <v>1.0887</v>
+        <v>1.052</v>
       </c>
       <c r="J53" t="n">
-        <v>25.0401</v>
+        <v>24.196</v>
       </c>
     </row>
     <row r="54">
@@ -4049,10 +4049,10 @@
         <v>1.47</v>
       </c>
       <c r="I54" t="n">
-        <v>1.0763</v>
+        <v>1.0377</v>
       </c>
       <c r="J54" t="n">
-        <v>24.7549</v>
+        <v>23.8671</v>
       </c>
     </row>
     <row r="55">
@@ -4089,10 +4089,10 @@
         <v>1.19</v>
       </c>
       <c r="I55" t="n">
-        <v>0.5086000000000001</v>
+        <v>0.5046</v>
       </c>
       <c r="J55" t="n">
-        <v>11.6978</v>
+        <v>11.6058</v>
       </c>
     </row>
     <row r="56">
@@ -4129,10 +4129,10 @@
         <v>0.96</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.2497</v>
+        <v>-0.2283</v>
       </c>
       <c r="J56" t="n">
-        <v>-5.7431</v>
+        <v>-5.2509</v>
       </c>
     </row>
     <row r="57">
@@ -4169,10 +4169,10 @@
         <v>0.99</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.0019</v>
+        <v>-0.0109</v>
       </c>
       <c r="J57" t="n">
-        <v>-0.0437</v>
+        <v>-0.2507</v>
       </c>
     </row>
     <row r="58">
@@ -4209,10 +4209,10 @@
         <v>0.92</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.09660000000000001</v>
+        <v>-0.1122</v>
       </c>
       <c r="J58" t="n">
-        <v>-2.2218</v>
+        <v>-2.5806</v>
       </c>
     </row>
     <row r="59">
@@ -4249,10 +4249,10 @@
         <v>0.85</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1716</v>
+        <v>-0.1889</v>
       </c>
       <c r="J59" t="n">
-        <v>-3.9468</v>
+        <v>-4.3447</v>
       </c>
     </row>
     <row r="60">
@@ -4289,10 +4289,10 @@
         <v>0.78</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2406</v>
+        <v>-0.2578</v>
       </c>
       <c r="J60" t="n">
-        <v>-5.5338</v>
+        <v>-5.9294</v>
       </c>
     </row>
     <row r="61">
@@ -4329,10 +4329,10 @@
         <v>0.72</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.2987</v>
+        <v>-0.3147</v>
       </c>
       <c r="J61" t="n">
-        <v>-6.8701</v>
+        <v>-7.2381</v>
       </c>
     </row>
     <row r="62">
@@ -4369,10 +4369,10 @@
         <v>0.99</v>
       </c>
       <c r="I62" t="n">
-        <v>0.0353</v>
+        <v>0.0098</v>
       </c>
       <c r="J62" t="n">
-        <v>0.8472</v>
+        <v>0.2352</v>
       </c>
     </row>
     <row r="63">
@@ -4409,10 +4409,10 @@
         <v>0.93</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.0667</v>
+        <v>-0.0858</v>
       </c>
       <c r="J63" t="n">
-        <v>-1.6008</v>
+        <v>-2.0592</v>
       </c>
     </row>
     <row r="64">
@@ -4449,10 +4449,10 @@
         <v>0.87</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.1374</v>
+        <v>-0.1576</v>
       </c>
       <c r="J64" t="n">
-        <v>-3.2976</v>
+        <v>-3.7824</v>
       </c>
     </row>
     <row r="65">
@@ -4489,10 +4489,10 @@
         <v>0.54</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.4548</v>
+        <v>-0.4663</v>
       </c>
       <c r="J65" t="n">
-        <v>-10.9152</v>
+        <v>-11.1912</v>
       </c>
     </row>
     <row r="66">
@@ -4529,10 +4529,10 @@
         <v>0.47</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.5197000000000001</v>
+        <v>-0.5272</v>
       </c>
       <c r="J66" t="n">
-        <v>-12.4728</v>
+        <v>-12.6528</v>
       </c>
     </row>
     <row r="67">
@@ -4569,10 +4569,10 @@
         <v>1.93</v>
       </c>
       <c r="I67" t="n">
-        <v>1.613</v>
+        <v>1.6114</v>
       </c>
       <c r="J67" t="n">
-        <v>38.712</v>
+        <v>38.6736</v>
       </c>
     </row>
     <row r="68">
@@ -4609,10 +4609,10 @@
         <v>1.69</v>
       </c>
       <c r="I68" t="n">
-        <v>1.3342</v>
+        <v>1.3176</v>
       </c>
       <c r="J68" t="n">
-        <v>32.0208</v>
+        <v>31.6224</v>
       </c>
     </row>
     <row r="69">
@@ -4649,10 +4649,10 @@
         <v>1.31</v>
       </c>
       <c r="I69" t="n">
-        <v>0.7819</v>
+        <v>0.7495000000000001</v>
       </c>
       <c r="J69" t="n">
-        <v>18.7656</v>
+        <v>17.988</v>
       </c>
     </row>
     <row r="70">
@@ -4689,10 +4689,10 @@
         <v>1.07</v>
       </c>
       <c r="I70" t="n">
-        <v>0.1725</v>
+        <v>0.1991</v>
       </c>
       <c r="J70" t="n">
-        <v>4.14</v>
+        <v>4.7784</v>
       </c>
     </row>
     <row r="71">
@@ -4729,10 +4729,10 @@
         <v>0.91</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.4156</v>
+        <v>-0.3823</v>
       </c>
       <c r="J71" t="n">
-        <v>-9.974399999999999</v>
+        <v>-9.1752</v>
       </c>
     </row>
     <row r="72">
@@ -4769,10 +4769,10 @@
         <v>1.68</v>
       </c>
       <c r="I72" t="n">
-        <v>1.3181</v>
+        <v>1.3012</v>
       </c>
       <c r="J72" t="n">
-        <v>26.362</v>
+        <v>26.024</v>
       </c>
     </row>
     <row r="73">
@@ -4809,10 +4809,10 @@
         <v>1.51</v>
       </c>
       <c r="I73" t="n">
-        <v>1.1156</v>
+        <v>1.0841</v>
       </c>
       <c r="J73" t="n">
-        <v>22.312</v>
+        <v>21.682</v>
       </c>
     </row>
     <row r="74">
@@ -4849,10 +4849,10 @@
         <v>1.47</v>
       </c>
       <c r="I74" t="n">
-        <v>1.0673</v>
+        <v>1.0292</v>
       </c>
       <c r="J74" t="n">
-        <v>21.346</v>
+        <v>20.584</v>
       </c>
     </row>
     <row r="75">
@@ -4889,10 +4889,10 @@
         <v>1.22</v>
       </c>
       <c r="I75" t="n">
-        <v>0.5682</v>
+        <v>0.5608</v>
       </c>
       <c r="J75" t="n">
-        <v>11.364</v>
+        <v>11.216</v>
       </c>
     </row>
     <row r="76">
@@ -4929,10 +4929,10 @@
         <v>1.14</v>
       </c>
       <c r="I76" t="n">
-        <v>0.3656</v>
+        <v>0.3783</v>
       </c>
       <c r="J76" t="n">
-        <v>7.312</v>
+        <v>7.566</v>
       </c>
     </row>
     <row r="77">
@@ -4969,10 +4969,10 @@
         <v>1.17</v>
       </c>
       <c r="I77" t="n">
-        <v>0.4833</v>
+        <v>0.4558</v>
       </c>
       <c r="J77" t="n">
-        <v>9.666</v>
+        <v>9.116</v>
       </c>
     </row>
     <row r="78">
@@ -5009,10 +5009,10 @@
         <v>0.78</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.2324</v>
+        <v>-0.2516</v>
       </c>
       <c r="J78" t="n">
-        <v>-4.648</v>
+        <v>-5.032</v>
       </c>
     </row>
     <row r="79">
@@ -5049,10 +5049,10 @@
         <v>0.67</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.3357</v>
+        <v>-0.3525</v>
       </c>
       <c r="J79" t="n">
-        <v>-6.714</v>
+        <v>-7.05</v>
       </c>
     </row>
     <row r="80">
@@ -5089,10 +5089,10 @@
         <v>0.67</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.3357</v>
+        <v>-0.3525</v>
       </c>
       <c r="J80" t="n">
-        <v>-6.714</v>
+        <v>-7.05</v>
       </c>
     </row>
     <row r="81">
@@ -5129,10 +5129,10 @@
         <v>0.6</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4015</v>
+        <v>-0.4154</v>
       </c>
       <c r="J81" t="n">
-        <v>-8.029999999999999</v>
+        <v>-8.308</v>
       </c>
     </row>
     <row r="82">
@@ -5169,10 +5169,10 @@
         <v>1.74</v>
       </c>
       <c r="I82" t="n">
-        <v>1.3695</v>
+        <v>1.3592</v>
       </c>
       <c r="J82" t="n">
-        <v>24.651</v>
+        <v>24.4656</v>
       </c>
     </row>
     <row r="83">
@@ -5209,10 +5209,10 @@
         <v>1.57</v>
       </c>
       <c r="I83" t="n">
-        <v>1.174</v>
+        <v>1.1499</v>
       </c>
       <c r="J83" t="n">
-        <v>21.132</v>
+        <v>20.6982</v>
       </c>
     </row>
     <row r="84">
@@ -5249,10 +5249,10 @@
         <v>1.53</v>
       </c>
       <c r="I84" t="n">
-        <v>1.1278</v>
+        <v>1.0999</v>
       </c>
       <c r="J84" t="n">
-        <v>20.3004</v>
+        <v>19.7982</v>
       </c>
     </row>
     <row r="85">
@@ -5289,10 +5289,10 @@
         <v>1.43</v>
       </c>
       <c r="I85" t="n">
-        <v>1.0033</v>
+        <v>0.958</v>
       </c>
       <c r="J85" t="n">
-        <v>18.0594</v>
+        <v>17.244</v>
       </c>
     </row>
     <row r="86">
@@ -5329,10 +5329,10 @@
         <v>1.27</v>
       </c>
       <c r="I86" t="n">
-        <v>0.6655</v>
+        <v>0.6514</v>
       </c>
       <c r="J86" t="n">
-        <v>11.979</v>
+        <v>11.7252</v>
       </c>
     </row>
     <row r="87">
@@ -5369,10 +5369,10 @@
         <v>1.15</v>
       </c>
       <c r="I87" t="n">
-        <v>0.5228</v>
+        <v>0.4777</v>
       </c>
       <c r="J87" t="n">
-        <v>9.410399999999999</v>
+        <v>8.598599999999999</v>
       </c>
     </row>
     <row r="88">
@@ -5409,10 +5409,10 @@
         <v>0.85</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.1383</v>
+        <v>-0.163</v>
       </c>
       <c r="J88" t="n">
-        <v>-2.4894</v>
+        <v>-2.934</v>
       </c>
     </row>
     <row r="89">
@@ -5449,10 +5449,10 @@
         <v>0.78</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.2146</v>
+        <v>-0.2379</v>
       </c>
       <c r="J89" t="n">
-        <v>-3.8628</v>
+        <v>-4.2822</v>
       </c>
     </row>
     <row r="90">
@@ -5489,10 +5489,10 @@
         <v>0.33</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.6377</v>
+        <v>-0.6385</v>
       </c>
       <c r="J90" t="n">
-        <v>-11.4786</v>
+        <v>-11.493</v>
       </c>
     </row>
     <row r="91">
@@ -5529,10 +5529,10 @@
         <v>0.25</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.7128</v>
+        <v>-0.7073</v>
       </c>
       <c r="J91" t="n">
-        <v>-12.8304</v>
+        <v>-12.7314</v>
       </c>
     </row>
     <row r="92">
@@ -5569,10 +5569,10 @@
         <v>1.35</v>
       </c>
       <c r="I92" t="n">
-        <v>0.67</v>
+        <v>0.6508</v>
       </c>
       <c r="J92" t="n">
-        <v>20.1</v>
+        <v>19.524</v>
       </c>
     </row>
     <row r="93">
@@ -5609,10 +5609,10 @@
         <v>1.21</v>
       </c>
       <c r="I93" t="n">
-        <v>0.4313</v>
+        <v>0.4319</v>
       </c>
       <c r="J93" t="n">
-        <v>12.939</v>
+        <v>12.957</v>
       </c>
     </row>
     <row r="94">
@@ -5649,10 +5649,10 @@
         <v>1.2</v>
       </c>
       <c r="I94" t="n">
-        <v>0.4136</v>
+        <v>0.4154</v>
       </c>
       <c r="J94" t="n">
-        <v>12.408</v>
+        <v>12.462</v>
       </c>
     </row>
     <row r="95">
@@ -5689,10 +5689,10 @@
         <v>1.13</v>
       </c>
       <c r="I95" t="n">
-        <v>0.2859</v>
+        <v>0.2949</v>
       </c>
       <c r="J95" t="n">
-        <v>8.577</v>
+        <v>8.847</v>
       </c>
     </row>
     <row r="96">
@@ -5729,10 +5729,10 @@
         <v>0.57</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.465</v>
+        <v>-0.47</v>
       </c>
       <c r="J96" t="n">
-        <v>-13.95</v>
+        <v>-14.1</v>
       </c>
     </row>
     <row r="97">
@@ -5769,10 +5769,10 @@
         <v>1.23</v>
       </c>
       <c r="I97" t="n">
-        <v>0.4933</v>
+        <v>0.4842</v>
       </c>
       <c r="J97" t="n">
-        <v>14.799</v>
+        <v>14.526</v>
       </c>
     </row>
     <row r="98">
@@ -5809,10 +5809,10 @@
         <v>1.03</v>
       </c>
       <c r="I98" t="n">
-        <v>0.09180000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="J98" t="n">
-        <v>2.754</v>
+        <v>3</v>
       </c>
     </row>
     <row r="99">
@@ -5849,10 +5849,10 @@
         <v>1.01</v>
       </c>
       <c r="I99" t="n">
-        <v>0.0377</v>
+        <v>0.0433</v>
       </c>
       <c r="J99" t="n">
-        <v>1.131</v>
+        <v>1.299</v>
       </c>
     </row>
     <row r="100">
@@ -5889,10 +5889,10 @@
         <v>0.92</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.1117</v>
+        <v>-0.1236</v>
       </c>
       <c r="J100" t="n">
-        <v>-3.351</v>
+        <v>-3.708</v>
       </c>
     </row>
     <row r="101">
@@ -5929,10 +5929,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.229</v>
+        <v>-0.2425</v>
       </c>
       <c r="J101" t="n">
-        <v>-6.87</v>
+        <v>-7.275</v>
       </c>
     </row>
     <row r="102">
@@ -5969,10 +5969,10 @@
         <v>1.03</v>
       </c>
       <c r="I102" t="n">
-        <v>0.165</v>
+        <v>0.1534</v>
       </c>
       <c r="J102" t="n">
-        <v>3.96</v>
+        <v>3.6816</v>
       </c>
     </row>
     <row r="103">
@@ -6009,10 +6009,10 @@
         <v>0.89</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.1189</v>
+        <v>-0.138</v>
       </c>
       <c r="J103" t="n">
-        <v>-2.8536</v>
+        <v>-3.312</v>
       </c>
     </row>
     <row r="104">
@@ -6049,10 +6049,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.2039</v>
+        <v>-0.2232</v>
       </c>
       <c r="J104" t="n">
-        <v>-4.8936</v>
+        <v>-5.3568</v>
       </c>
     </row>
     <row r="105">
@@ -6089,10 +6089,10 @@
         <v>0.68</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.3266</v>
+        <v>-0.3436</v>
       </c>
       <c r="J105" t="n">
-        <v>-7.8384</v>
+        <v>-8.2464</v>
       </c>
     </row>
     <row r="106">
@@ -6129,10 +6129,10 @@
         <v>0.49</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.5039</v>
+        <v>-0.5121</v>
       </c>
       <c r="J106" t="n">
-        <v>-12.0936</v>
+        <v>-12.2904</v>
       </c>
     </row>
     <row r="107">
@@ -6169,10 +6169,10 @@
         <v>1.85</v>
       </c>
       <c r="I107" t="n">
-        <v>1.5514</v>
+        <v>1.5419</v>
       </c>
       <c r="J107" t="n">
-        <v>37.2336</v>
+        <v>37.0056</v>
       </c>
     </row>
     <row r="108">
@@ -6209,10 +6209,10 @@
         <v>1.35</v>
       </c>
       <c r="I108" t="n">
-        <v>0.8875999999999999</v>
+        <v>0.839</v>
       </c>
       <c r="J108" t="n">
-        <v>21.3024</v>
+        <v>20.136</v>
       </c>
     </row>
     <row r="109">
@@ -6249,10 +6249,10 @@
         <v>1.29</v>
       </c>
       <c r="I109" t="n">
-        <v>0.7547</v>
+        <v>0.7219</v>
       </c>
       <c r="J109" t="n">
-        <v>18.1128</v>
+        <v>17.3256</v>
       </c>
     </row>
     <row r="110">
@@ -6289,10 +6289,10 @@
         <v>1.2</v>
       </c>
       <c r="I110" t="n">
-        <v>0.5475</v>
+        <v>0.5366</v>
       </c>
       <c r="J110" t="n">
-        <v>13.14</v>
+        <v>12.8784</v>
       </c>
     </row>
     <row r="111">
@@ -6329,10 +6329,10 @@
         <v>0.67</v>
       </c>
       <c r="I111" t="n">
-        <v>-1.0113</v>
+        <v>-0.918</v>
       </c>
       <c r="J111" t="n">
-        <v>-24.2712</v>
+        <v>-22.032</v>
       </c>
     </row>
     <row r="112">
@@ -6369,10 +6369,10 @@
         <v>0.83</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.1478</v>
+        <v>-0.175</v>
       </c>
       <c r="J112" t="n">
-        <v>-2.956</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="113">
@@ -6409,10 +6409,10 @@
         <v>0.68</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.3056</v>
+        <v>-0.3276</v>
       </c>
       <c r="J113" t="n">
-        <v>-6.112</v>
+        <v>-6.552</v>
       </c>
     </row>
     <row r="114">
@@ -6449,10 +6449,10 @@
         <v>0.67</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.3152</v>
+        <v>-0.3367</v>
       </c>
       <c r="J114" t="n">
-        <v>-6.304</v>
+        <v>-6.734</v>
       </c>
     </row>
     <row r="115">
@@ -6489,10 +6489,10 @@
         <v>0.49</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.48</v>
+        <v>-0.4933</v>
       </c>
       <c r="J115" t="n">
-        <v>-9.6</v>
+        <v>-9.866</v>
       </c>
     </row>
     <row r="116">
@@ -6529,10 +6529,10 @@
         <v>0.48</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4895</v>
+        <v>-0.5021</v>
       </c>
       <c r="J116" t="n">
-        <v>-9.789999999999999</v>
+        <v>-10.042</v>
       </c>
     </row>
     <row r="117">
@@ -6569,10 +6569,10 @@
         <v>2.24</v>
       </c>
       <c r="I117" t="n">
-        <v>1.8338</v>
+        <v>1.9314</v>
       </c>
       <c r="J117" t="n">
-        <v>36.676</v>
+        <v>38.628</v>
       </c>
     </row>
     <row r="118">
@@ -6609,10 +6609,10 @@
         <v>1.6</v>
       </c>
       <c r="I118" t="n">
-        <v>1.2048</v>
+        <v>1.184</v>
       </c>
       <c r="J118" t="n">
-        <v>24.096</v>
+        <v>23.68</v>
       </c>
     </row>
     <row r="119">
@@ -6649,10 +6649,10 @@
         <v>1.54</v>
       </c>
       <c r="I119" t="n">
-        <v>1.137</v>
+        <v>1.1104</v>
       </c>
       <c r="J119" t="n">
-        <v>22.74</v>
+        <v>22.208</v>
       </c>
     </row>
     <row r="120">
@@ -6689,10 +6689,10 @@
         <v>1.33</v>
       </c>
       <c r="I120" t="n">
-        <v>0.7951</v>
+        <v>0.767</v>
       </c>
       <c r="J120" t="n">
-        <v>15.902</v>
+        <v>15.34</v>
       </c>
     </row>
     <row r="121">
@@ -6729,10 +6729,10 @@
         <v>1.01</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.0684</v>
+        <v>-0.0262</v>
       </c>
       <c r="J121" t="n">
-        <v>-1.368</v>
+        <v>-0.524</v>
       </c>
     </row>
     <row r="122">
@@ -6769,10 +6769,10 @@
         <v>1.33</v>
       </c>
       <c r="I122" t="n">
-        <v>0.6264</v>
+        <v>0.6131</v>
       </c>
       <c r="J122" t="n">
-        <v>18.1656</v>
+        <v>17.7799</v>
       </c>
     </row>
     <row r="123">
@@ -6809,10 +6809,10 @@
         <v>1.29</v>
       </c>
       <c r="I123" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5524</v>
       </c>
       <c r="J123" t="n">
-        <v>16.24</v>
+        <v>16.0196</v>
       </c>
     </row>
     <row r="124">
@@ -6849,10 +6849,10 @@
         <v>1.05</v>
       </c>
       <c r="I124" t="n">
-        <v>0.1201</v>
+        <v>0.1342</v>
       </c>
       <c r="J124" t="n">
-        <v>3.4829</v>
+        <v>3.8918</v>
       </c>
     </row>
     <row r="125">
@@ -6889,10 +6889,10 @@
         <v>1.04</v>
       </c>
       <c r="I125" t="n">
-        <v>0.0968</v>
+        <v>0.1109</v>
       </c>
       <c r="J125" t="n">
-        <v>2.8072</v>
+        <v>3.2161</v>
       </c>
     </row>
     <row r="126">
@@ -6929,10 +6929,10 @@
         <v>0.93</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.1136</v>
+        <v>-0.122</v>
       </c>
       <c r="J126" t="n">
-        <v>-3.2944</v>
+        <v>-3.538</v>
       </c>
     </row>
     <row r="127">
@@ -6969,10 +6969,10 @@
         <v>1.1</v>
       </c>
       <c r="I127" t="n">
-        <v>0.3409</v>
+        <v>0.3364</v>
       </c>
       <c r="J127" t="n">
-        <v>9.886100000000001</v>
+        <v>9.755599999999999</v>
       </c>
     </row>
     <row r="128">
@@ -7009,10 +7009,10 @@
         <v>1.07</v>
       </c>
       <c r="I128" t="n">
-        <v>0.2529</v>
+        <v>0.2547</v>
       </c>
       <c r="J128" t="n">
-        <v>7.3341</v>
+        <v>7.3863</v>
       </c>
     </row>
     <row r="129">
@@ -7049,10 +7049,10 @@
         <v>1.06</v>
       </c>
       <c r="I129" t="n">
-        <v>0.2224</v>
+        <v>0.2259</v>
       </c>
       <c r="J129" t="n">
-        <v>6.4496</v>
+        <v>6.5511</v>
       </c>
     </row>
     <row r="130">
@@ -7089,10 +7089,10 @@
         <v>0.95</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2036</v>
+        <v>-0.2046</v>
       </c>
       <c r="J130" t="n">
-        <v>-5.9044</v>
+        <v>-5.9334</v>
       </c>
     </row>
     <row r="131">
@@ -7129,10 +7129,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.2355</v>
+        <v>-0.2349</v>
       </c>
       <c r="J131" t="n">
-        <v>-6.8295</v>
+        <v>-6.8121</v>
       </c>
     </row>
     <row r="132">
@@ -7169,10 +7169,10 @@
         <v>1.85</v>
       </c>
       <c r="I132" t="n">
-        <v>1.5215</v>
+        <v>1.5153</v>
       </c>
       <c r="J132" t="n">
-        <v>31.9515</v>
+        <v>31.8213</v>
       </c>
     </row>
     <row r="133">
@@ -7209,10 +7209,10 @@
         <v>1.52</v>
       </c>
       <c r="I133" t="n">
-        <v>1.1312</v>
+        <v>1.1002</v>
       </c>
       <c r="J133" t="n">
-        <v>23.7552</v>
+        <v>23.1042</v>
       </c>
     </row>
     <row r="134">
@@ -7249,10 +7249,10 @@
         <v>1.3</v>
       </c>
       <c r="I134" t="n">
-        <v>0.7599</v>
+        <v>0.73</v>
       </c>
       <c r="J134" t="n">
-        <v>15.9579</v>
+        <v>15.33</v>
       </c>
     </row>
     <row r="135">
@@ -7289,10 +7289,10 @@
         <v>1.26</v>
       </c>
       <c r="I135" t="n">
-        <v>0.6683</v>
+        <v>0.6489</v>
       </c>
       <c r="J135" t="n">
-        <v>14.0343</v>
+        <v>13.6269</v>
       </c>
     </row>
     <row r="136">
@@ -7329,10 +7329,10 @@
         <v>0.97</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.2238</v>
+        <v>-0.2009</v>
       </c>
       <c r="J136" t="n">
-        <v>-4.6998</v>
+        <v>-4.2189</v>
       </c>
     </row>
     <row r="137">
@@ -7369,10 +7369,10 @@
         <v>1.03</v>
       </c>
       <c r="I137" t="n">
-        <v>0.1702</v>
+        <v>0.1572</v>
       </c>
       <c r="J137" t="n">
-        <v>3.5742</v>
+        <v>3.3012</v>
       </c>
     </row>
     <row r="138">
@@ -7409,10 +7409,10 @@
         <v>0.77</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.2409</v>
+        <v>-0.2602</v>
       </c>
       <c r="J138" t="n">
-        <v>-5.0589</v>
+        <v>-5.4642</v>
       </c>
     </row>
     <row r="139">
@@ -7449,10 +7449,10 @@
         <v>0.76</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.2499</v>
+        <v>-0.2692</v>
       </c>
       <c r="J139" t="n">
-        <v>-5.2479</v>
+        <v>-5.6532</v>
       </c>
     </row>
     <row r="140">
@@ -7489,10 +7489,10 @@
         <v>0.74</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2686</v>
+        <v>-0.2875</v>
       </c>
       <c r="J140" t="n">
-        <v>-5.6406</v>
+        <v>-6.0375</v>
       </c>
     </row>
     <row r="141">
@@ -7529,10 +7529,10 @@
         <v>0.55</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4469</v>
+        <v>-0.4587</v>
       </c>
       <c r="J141" t="n">
-        <v>-9.3849</v>
+        <v>-9.6327</v>
       </c>
     </row>
     <row r="142">
@@ -7569,10 +7569,10 @@
         <v>1.53</v>
       </c>
       <c r="I142" t="n">
-        <v>1.1409</v>
+        <v>1.1111</v>
       </c>
       <c r="J142" t="n">
-        <v>27.3816</v>
+        <v>26.6664</v>
       </c>
     </row>
     <row r="143">
@@ -7609,10 +7609,10 @@
         <v>1.44</v>
       </c>
       <c r="I143" t="n">
-        <v>1.0294</v>
+        <v>0.9842</v>
       </c>
       <c r="J143" t="n">
-        <v>24.7056</v>
+        <v>23.6208</v>
       </c>
     </row>
     <row r="144">
@@ -7649,10 +7649,10 @@
         <v>1.43</v>
       </c>
       <c r="I144" t="n">
-        <v>1.015</v>
+        <v>0.968</v>
       </c>
       <c r="J144" t="n">
-        <v>24.36</v>
+        <v>23.232</v>
       </c>
     </row>
     <row r="145">
@@ -7689,10 +7689,10 @@
         <v>1.37</v>
       </c>
       <c r="I145" t="n">
-        <v>0.9094</v>
+        <v>0.8625</v>
       </c>
       <c r="J145" t="n">
-        <v>21.8256</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="146">
@@ -7729,10 +7729,10 @@
         <v>1.21</v>
       </c>
       <c r="I146" t="n">
-        <v>0.5455</v>
+        <v>0.5402</v>
       </c>
       <c r="J146" t="n">
-        <v>13.092</v>
+        <v>12.9648</v>
       </c>
     </row>
     <row r="147">
@@ -7769,10 +7769,10 @@
         <v>0.76</v>
       </c>
       <c r="I147" t="n">
-        <v>-0.245</v>
+        <v>-0.2654</v>
       </c>
       <c r="J147" t="n">
-        <v>-5.88</v>
+        <v>-6.3696</v>
       </c>
     </row>
     <row r="148">
@@ -7809,10 +7809,10 @@
         <v>0.76</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.245</v>
+        <v>-0.2654</v>
       </c>
       <c r="J148" t="n">
-        <v>-5.88</v>
+        <v>-6.3696</v>
       </c>
     </row>
     <row r="149">
@@ -7849,10 +7849,10 @@
         <v>0.71</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.2908</v>
+        <v>-0.3105</v>
       </c>
       <c r="J149" t="n">
-        <v>-6.9792</v>
+        <v>-7.452</v>
       </c>
     </row>
     <row r="150">
@@ -7889,10 +7889,10 @@
         <v>0.7</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.3</v>
+        <v>-0.3194</v>
       </c>
       <c r="J150" t="n">
-        <v>-7.2</v>
+        <v>-7.6656</v>
       </c>
     </row>
     <row r="151">
@@ -7929,10 +7929,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.3092</v>
+        <v>-0.3284</v>
       </c>
       <c r="J151" t="n">
-        <v>-7.4208</v>
+        <v>-7.8816</v>
       </c>
     </row>
     <row r="152">
@@ -7969,10 +7969,10 @@
         <v>1.16</v>
       </c>
       <c r="I152" t="n">
-        <v>0.3595</v>
+        <v>0.3608</v>
       </c>
       <c r="J152" t="n">
-        <v>10.785</v>
+        <v>10.824</v>
       </c>
     </row>
     <row r="153">
@@ -8009,10 +8009,10 @@
         <v>1.13</v>
       </c>
       <c r="I153" t="n">
-        <v>0.302</v>
+        <v>0.3066</v>
       </c>
       <c r="J153" t="n">
-        <v>9.06</v>
+        <v>9.198</v>
       </c>
     </row>
     <row r="154">
@@ -8049,10 +8049,10 @@
         <v>1.05</v>
       </c>
       <c r="I154" t="n">
-        <v>0.1363</v>
+        <v>0.1457</v>
       </c>
       <c r="J154" t="n">
-        <v>4.089</v>
+        <v>4.371</v>
       </c>
     </row>
     <row r="155">
@@ -8089,10 +8089,10 @@
         <v>0.89</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.1471</v>
+        <v>-0.1596</v>
       </c>
       <c r="J155" t="n">
-        <v>-4.413</v>
+        <v>-4.788</v>
       </c>
     </row>
     <row r="156">
@@ -8129,10 +8129,10 @@
         <v>0.85</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.1898</v>
+        <v>-0.2029</v>
       </c>
       <c r="J156" t="n">
-        <v>-5.694</v>
+        <v>-6.087</v>
       </c>
     </row>
     <row r="157">
@@ -8169,10 +8169,10 @@
         <v>1.19</v>
       </c>
       <c r="I157" t="n">
-        <v>0.4125</v>
+        <v>0.4109</v>
       </c>
       <c r="J157" t="n">
-        <v>12.375</v>
+        <v>12.327</v>
       </c>
     </row>
     <row r="158">
@@ -8209,10 +8209,10 @@
         <v>1.17</v>
       </c>
       <c r="I158" t="n">
-        <v>0.3755</v>
+        <v>0.3764</v>
       </c>
       <c r="J158" t="n">
-        <v>11.265</v>
+        <v>11.292</v>
       </c>
     </row>
     <row r="159">
@@ -8249,10 +8249,10 @@
         <v>1.16</v>
       </c>
       <c r="I159" t="n">
-        <v>0.3568</v>
+        <v>0.3588</v>
       </c>
       <c r="J159" t="n">
-        <v>10.704</v>
+        <v>10.764</v>
       </c>
     </row>
     <row r="160">
@@ -8289,10 +8289,10 @@
         <v>0.82</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.2218</v>
+        <v>-0.2347</v>
       </c>
       <c r="J160" t="n">
-        <v>-6.654</v>
+        <v>-7.041</v>
       </c>
     </row>
     <row r="161">
@@ -8329,10 +8329,10 @@
         <v>0.79</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.252</v>
+        <v>-0.2646</v>
       </c>
       <c r="J161" t="n">
-        <v>-7.56</v>
+        <v>-7.938</v>
       </c>
     </row>
     <row r="162">
@@ -8369,10 +8369,10 @@
         <v>1.33</v>
       </c>
       <c r="I162" t="n">
-        <v>0.6518</v>
+        <v>0.6317</v>
       </c>
       <c r="J162" t="n">
-        <v>19.554</v>
+        <v>18.951</v>
       </c>
     </row>
     <row r="163">
@@ -8409,10 +8409,10 @@
         <v>1.24</v>
       </c>
       <c r="I163" t="n">
-        <v>0.4965</v>
+        <v>0.4899</v>
       </c>
       <c r="J163" t="n">
-        <v>14.895</v>
+        <v>14.697</v>
       </c>
     </row>
     <row r="164">
@@ -8449,10 +8449,10 @@
         <v>1.02</v>
       </c>
       <c r="I164" t="n">
-        <v>0.0603</v>
+        <v>0.0694</v>
       </c>
       <c r="J164" t="n">
-        <v>1.809</v>
+        <v>2.082</v>
       </c>
     </row>
     <row r="165">
@@ -8489,10 +8489,10 @@
         <v>0.96</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.0678</v>
+        <v>-0.0761</v>
       </c>
       <c r="J165" t="n">
-        <v>-2.034</v>
+        <v>-2.283</v>
       </c>
     </row>
     <row r="166">
@@ -8529,10 +8529,10 @@
         <v>0.68</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.36</v>
+        <v>-0.3698</v>
       </c>
       <c r="J166" t="n">
-        <v>-10.8</v>
+        <v>-11.094</v>
       </c>
     </row>
     <row r="167">
@@ -8569,10 +8569,10 @@
         <v>1.4</v>
       </c>
       <c r="I167" t="n">
-        <v>0.7687</v>
+        <v>0.7372</v>
       </c>
       <c r="J167" t="n">
-        <v>23.061</v>
+        <v>22.116</v>
       </c>
     </row>
     <row r="168">
@@ -8609,10 +8609,10 @@
         <v>1.03</v>
       </c>
       <c r="I168" t="n">
-        <v>0.0859</v>
+        <v>0.0959</v>
       </c>
       <c r="J168" t="n">
-        <v>2.577</v>
+        <v>2.877</v>
       </c>
     </row>
     <row r="169">
@@ -8649,10 +8649,10 @@
         <v>0.97</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.0545</v>
+        <v>-0.0616</v>
       </c>
       <c r="J169" t="n">
-        <v>-1.635</v>
+        <v>-1.848</v>
       </c>
     </row>
     <row r="170">
@@ -8689,10 +8689,10 @@
         <v>0.93</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.1049</v>
+        <v>-0.1153</v>
       </c>
       <c r="J170" t="n">
-        <v>-3.147</v>
+        <v>-3.459</v>
       </c>
     </row>
     <row r="171">
@@ -8729,10 +8729,10 @@
         <v>0.9</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.1393</v>
+        <v>-0.1509</v>
       </c>
       <c r="J171" t="n">
-        <v>-4.179</v>
+        <v>-4.527</v>
       </c>
     </row>
     <row r="172">
@@ -8769,10 +8769,10 @@
         <v>1.78</v>
       </c>
       <c r="I172" t="n">
-        <v>1.4177</v>
+        <v>1.4099</v>
       </c>
       <c r="J172" t="n">
-        <v>26.9363</v>
+        <v>26.7881</v>
       </c>
     </row>
     <row r="173">
@@ -8809,10 +8809,10 @@
         <v>1.73</v>
       </c>
       <c r="I173" t="n">
-        <v>1.3606</v>
+        <v>1.3493</v>
       </c>
       <c r="J173" t="n">
-        <v>25.8514</v>
+        <v>25.6367</v>
       </c>
     </row>
     <row r="174">
@@ -8849,10 +8849,10 @@
         <v>1.69</v>
       </c>
       <c r="I174" t="n">
-        <v>1.3147</v>
+        <v>1.3004</v>
       </c>
       <c r="J174" t="n">
-        <v>24.9793</v>
+        <v>24.7076</v>
       </c>
     </row>
     <row r="175">
@@ -8889,10 +8889,10 @@
         <v>1.38</v>
       </c>
       <c r="I175" t="n">
-        <v>0.914</v>
+        <v>0.8698</v>
       </c>
       <c r="J175" t="n">
-        <v>17.366</v>
+        <v>16.5262</v>
       </c>
     </row>
     <row r="176">
@@ -8929,10 +8929,10 @@
         <v>0.88</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.5221</v>
+        <v>-0.4757</v>
       </c>
       <c r="J176" t="n">
-        <v>-9.9199</v>
+        <v>-9.0383</v>
       </c>
     </row>
     <row r="177">
@@ -8969,10 +8969,10 @@
         <v>1.06</v>
       </c>
       <c r="I177" t="n">
-        <v>0.3655</v>
+        <v>0.3206</v>
       </c>
       <c r="J177" t="n">
-        <v>6.9445</v>
+        <v>6.0914</v>
       </c>
     </row>
     <row r="178">
@@ -9009,10 +9009,10 @@
         <v>0.66</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.3216</v>
+        <v>-0.3435</v>
       </c>
       <c r="J178" t="n">
-        <v>-6.1104</v>
+        <v>-6.5265</v>
       </c>
     </row>
     <row r="179">
@@ -9049,10 +9049,10 @@
         <v>0.66</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.3216</v>
+        <v>-0.3435</v>
       </c>
       <c r="J179" t="n">
-        <v>-6.1104</v>
+        <v>-6.5265</v>
       </c>
     </row>
     <row r="180">
@@ -9089,10 +9089,10 @@
         <v>0.38</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.5816</v>
+        <v>-0.5879</v>
       </c>
       <c r="J180" t="n">
-        <v>-11.0504</v>
+        <v>-11.1701</v>
       </c>
     </row>
     <row r="181">
@@ -9129,10 +9129,10 @@
         <v>0.31</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.6485</v>
+        <v>-0.6494</v>
       </c>
       <c r="J181" t="n">
-        <v>-12.3215</v>
+        <v>-12.3386</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2998/event_2998_evp_summary.xlsx
+++ b/database/event/2998/event_2998_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.823</v>
+        <v>3.8622</v>
       </c>
       <c r="C2" t="n">
-        <v>1.4339</v>
+        <v>1.4487</v>
       </c>
       <c r="D2" t="n">
-        <v>1.1161</v>
+        <v>1.1536</v>
       </c>
       <c r="E2" t="n">
-        <v>3.823</v>
+        <v>3.8622</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1791</v>
+        <v>0.1238</v>
       </c>
       <c r="G2" t="n">
-        <v>3.6439</v>
+        <v>3.7384</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1791</v>
+        <v>0.1238</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1791</v>
+        <v>0.1238</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6439</v>
+        <v>3.7384</v>
       </c>
       <c r="K2" t="n">
         <v>115</v>
@@ -529,7 +529,7 @@
         <v>86</v>
       </c>
       <c r="M2" t="n">
-        <v>3.823</v>
+        <v>3.8622</v>
       </c>
       <c r="N2" t="n">
         <v>201</v>
@@ -538,81 +538,81 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.7022</v>
+        <v>3.6227</v>
       </c>
       <c r="C3" t="n">
-        <v>1.3886</v>
+        <v>1.3588</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0611</v>
+        <v>1.0445</v>
       </c>
       <c r="E3" t="n">
-        <v>3.7022</v>
+        <v>3.6227</v>
       </c>
       <c r="F3" t="n">
-        <v>3.3459</v>
+        <v>3.1175</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3563</v>
+        <v>0.5052</v>
       </c>
       <c r="H3" t="n">
-        <v>4.5982</v>
+        <v>4.1944</v>
       </c>
       <c r="I3" t="n">
-        <v>4.7167</v>
+        <v>4.1944</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3563</v>
+        <v>0.5052</v>
       </c>
       <c r="K3" t="n">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="L3" t="n">
         <v>86</v>
       </c>
       <c r="M3" t="n">
-        <v>5.073</v>
+        <v>4.6996</v>
       </c>
       <c r="N3" t="n">
-        <v>206</v>
+        <v>201</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>boltz</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.6901</v>
+        <v>3.5784</v>
       </c>
       <c r="C4" t="n">
-        <v>1.3841</v>
+        <v>1.3422</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0556</v>
+        <v>1.0243</v>
       </c>
       <c r="E4" t="n">
-        <v>3.6901</v>
+        <v>3.5784</v>
       </c>
       <c r="F4" t="n">
-        <v>3.1393</v>
+        <v>1.9647</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5508</v>
+        <v>1.6137</v>
       </c>
       <c r="H4" t="n">
-        <v>4.1459</v>
+        <v>1.9647</v>
       </c>
       <c r="I4" t="n">
-        <v>4.1459</v>
+        <v>1.9647</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5508</v>
+        <v>1.6137</v>
       </c>
       <c r="K4" t="n">
         <v>115</v>
@@ -621,7 +621,7 @@
         <v>86</v>
       </c>
       <c r="M4" t="n">
-        <v>4.6967</v>
+        <v>3.5784</v>
       </c>
       <c r="N4" t="n">
         <v>201</v>
@@ -630,47 +630,47 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>boltz</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.6021</v>
+        <v>3.5372</v>
       </c>
       <c r="C5" t="n">
-        <v>1.3511</v>
+        <v>1.3267</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0155</v>
+        <v>1.0056</v>
       </c>
       <c r="E5" t="n">
-        <v>3.6021</v>
+        <v>3.5372</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9793</v>
+        <v>3.2682</v>
       </c>
       <c r="G5" t="n">
-        <v>1.6228</v>
+        <v>0.269</v>
       </c>
       <c r="H5" t="n">
-        <v>1.9793</v>
+        <v>4.5396</v>
       </c>
       <c r="I5" t="n">
-        <v>1.9793</v>
+        <v>4.6609</v>
       </c>
       <c r="J5" t="n">
-        <v>1.6228</v>
+        <v>0.269</v>
       </c>
       <c r="K5" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="L5" t="n">
         <v>86</v>
       </c>
       <c r="M5" t="n">
-        <v>3.6021</v>
+        <v>4.9299</v>
       </c>
       <c r="N5" t="n">
-        <v>201</v>
+        <v>206</v>
       </c>
     </row>
     <row r="6">
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.0132</v>
+        <v>2.9574</v>
       </c>
       <c r="C6" t="n">
-        <v>1.1302</v>
+        <v>1.1093</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7475000000000001</v>
+        <v>0.7413999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>3.0132</v>
+        <v>2.9574</v>
       </c>
       <c r="F6" t="n">
-        <v>3.1078</v>
+        <v>3.0742</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0946</v>
+        <v>-0.1168</v>
       </c>
       <c r="H6" t="n">
-        <v>4.0771</v>
+        <v>4.095</v>
       </c>
       <c r="I6" t="n">
-        <v>4.1822</v>
+        <v>4.2044</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.0946</v>
+        <v>-0.1168</v>
       </c>
       <c r="K6" t="n">
         <v>120</v>
@@ -726,28 +726,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.9216</v>
+        <v>2.8707</v>
       </c>
       <c r="C7" t="n">
-        <v>1.0958</v>
+        <v>1.0768</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7058</v>
+        <v>0.702</v>
       </c>
       <c r="E7" t="n">
-        <v>2.9216</v>
+        <v>2.8707</v>
       </c>
       <c r="F7" t="n">
-        <v>2.9216</v>
+        <v>2.8707</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>3.6695</v>
+        <v>3.6287</v>
       </c>
       <c r="I7" t="n">
-        <v>3.6695</v>
+        <v>3.6287</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -759,7 +759,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.6695</v>
+        <v>3.6287</v>
       </c>
       <c r="N7" t="n">
         <v>137</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.7546</v>
+        <v>2.6543</v>
       </c>
       <c r="C8" t="n">
-        <v>1.0332</v>
+        <v>0.9956</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6297</v>
+        <v>0.6034</v>
       </c>
       <c r="E8" t="n">
-        <v>2.7546</v>
+        <v>2.6543</v>
       </c>
       <c r="F8" t="n">
-        <v>2.9227</v>
+        <v>2.8564</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1681</v>
+        <v>-0.2021</v>
       </c>
       <c r="H8" t="n">
-        <v>3.6719</v>
+        <v>3.5958</v>
       </c>
       <c r="I8" t="n">
-        <v>3.7665</v>
+        <v>3.6919</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1681</v>
+        <v>-0.2021</v>
       </c>
       <c r="K8" t="n">
         <v>120</v>
@@ -805,7 +805,7 @@
         <v>86</v>
       </c>
       <c r="M8" t="n">
-        <v>3.5984</v>
+        <v>3.4898</v>
       </c>
       <c r="N8" t="n">
         <v>206</v>
@@ -818,28 +818,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.6412</v>
+        <v>2.5802</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9907</v>
+        <v>0.9678</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5780999999999999</v>
+        <v>0.5696</v>
       </c>
       <c r="E9" t="n">
-        <v>2.6412</v>
+        <v>2.5802</v>
       </c>
       <c r="F9" t="n">
-        <v>2.6412</v>
+        <v>2.5802</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>3.0558</v>
+        <v>2.9628</v>
       </c>
       <c r="I9" t="n">
-        <v>3.0558</v>
+        <v>2.9628</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.0558</v>
+        <v>2.9628</v>
       </c>
       <c r="N9" t="n">
         <v>137</v>
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.2654</v>
+        <v>2.0798</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8497</v>
+        <v>0.7801</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4071</v>
+        <v>0.3417</v>
       </c>
       <c r="E10" t="n">
-        <v>2.2654</v>
+        <v>2.0798</v>
       </c>
       <c r="F10" t="n">
-        <v>2.2654</v>
+        <v>2.0798</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2.2654</v>
+        <v>2.0798</v>
       </c>
       <c r="I10" t="n">
-        <v>2.2654</v>
+        <v>2.0798</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.2654</v>
+        <v>2.0798</v>
       </c>
       <c r="N10" t="n">
         <v>137</v>
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.8584</v>
+        <v>1.8079</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6971000000000001</v>
+        <v>0.6781</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2218</v>
+        <v>0.2178</v>
       </c>
       <c r="E11" t="n">
-        <v>1.8584</v>
+        <v>1.8079</v>
       </c>
       <c r="F11" t="n">
-        <v>1.8584</v>
+        <v>1.8079</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1.8584</v>
+        <v>1.8079</v>
       </c>
       <c r="I11" t="n">
-        <v>1.8584</v>
+        <v>1.8079</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1.8584</v>
+        <v>1.8079</v>
       </c>
       <c r="N11" t="n">
         <v>112</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.6797</v>
+        <v>1.5608</v>
       </c>
       <c r="C12" t="n">
-        <v>0.63</v>
+        <v>0.5854</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1404</v>
+        <v>0.1052</v>
       </c>
       <c r="E12" t="n">
-        <v>1.6797</v>
+        <v>1.5608</v>
       </c>
       <c r="F12" t="n">
-        <v>1.7737</v>
+        <v>1.7015</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.094</v>
+        <v>-0.1407</v>
       </c>
       <c r="H12" t="n">
-        <v>1.7737</v>
+        <v>1.7015</v>
       </c>
       <c r="I12" t="n">
-        <v>1.8194</v>
+        <v>1.747</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.094</v>
+        <v>-0.1407</v>
       </c>
       <c r="K12" t="n">
         <v>120</v>
@@ -989,7 +989,7 @@
         <v>86</v>
       </c>
       <c r="M12" t="n">
-        <v>1.7254</v>
+        <v>1.6063</v>
       </c>
       <c r="N12" t="n">
         <v>206</v>
@@ -1002,28 +1002,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.2372</v>
+        <v>1.1651</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4641</v>
+        <v>0.437</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.061</v>
+        <v>-0.075</v>
       </c>
       <c r="E13" t="n">
-        <v>1.2372</v>
+        <v>1.1651</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2372</v>
+        <v>1.1651</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1.2372</v>
+        <v>1.1651</v>
       </c>
       <c r="I13" t="n">
-        <v>1.2372</v>
+        <v>1.1651</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.2372</v>
+        <v>1.1651</v>
       </c>
       <c r="N13" t="n">
         <v>137</v>
@@ -1044,93 +1044,93 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9496</v>
+        <v>0.9593</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3562</v>
+        <v>0.3598</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1919</v>
+        <v>-0.1688</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9496</v>
+        <v>0.9593</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9496</v>
+        <v>1.2151</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-0.2558</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9496</v>
+        <v>1.2151</v>
       </c>
       <c r="I14" t="n">
-        <v>0.9496</v>
+        <v>1.2151</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-0.2558</v>
       </c>
       <c r="K14" t="n">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="M14" t="n">
-        <v>0.9496</v>
+        <v>0.9593</v>
       </c>
       <c r="N14" t="n">
-        <v>121</v>
+        <v>201</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8541</v>
+        <v>0.8982</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3204</v>
+        <v>0.3369</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2354</v>
+        <v>-0.1966</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8541</v>
+        <v>0.8982</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1365</v>
+        <v>0.8982</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.2824</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.1365</v>
+        <v>0.8982</v>
       </c>
       <c r="I15" t="n">
-        <v>1.1365</v>
+        <v>0.8982</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.2824</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="L15" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.8541000000000001</v>
+        <v>0.8982</v>
       </c>
       <c r="N15" t="n">
-        <v>201</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16">
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8486</v>
+        <v>0.791</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3183</v>
+        <v>0.2967</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2379</v>
+        <v>-0.2454</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8486</v>
+        <v>0.791</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8486</v>
+        <v>0.791</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8486</v>
+        <v>0.791</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8486</v>
+        <v>0.791</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.8486</v>
+        <v>0.791</v>
       </c>
       <c r="N16" t="n">
         <v>135</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7348</v>
+        <v>0.7507</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2756</v>
+        <v>0.2816</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2897</v>
+        <v>-0.2638</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7348</v>
+        <v>0.7507</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7348</v>
+        <v>0.7507</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7348</v>
+        <v>0.7507</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7348</v>
+        <v>0.7507</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7348</v>
+        <v>0.7507</v>
       </c>
       <c r="N17" t="n">
         <v>121</v>
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.5588</v>
+        <v>0.5538</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2096</v>
+        <v>0.2077</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3698</v>
+        <v>-0.3535</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5588</v>
+        <v>0.5538</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5588</v>
+        <v>0.5538</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5588</v>
+        <v>0.5538</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5588</v>
+        <v>0.5538</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5588</v>
+        <v>0.5538</v>
       </c>
       <c r="N18" t="n">
         <v>121</v>
@@ -1274,93 +1274,93 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>valde</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.5115</v>
+        <v>0.5471</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1919</v>
+        <v>0.2052</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3914</v>
+        <v>-0.3566</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5115</v>
+        <v>0.5471</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5115</v>
+        <v>0.7542</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>-0.2071</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5115</v>
+        <v>0.7542</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5115</v>
+        <v>0.7542</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>-0.2071</v>
       </c>
       <c r="K19" t="n">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5115</v>
+        <v>0.5470999999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>135</v>
+        <v>201</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>valde</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.4932</v>
+        <v>0.448</v>
       </c>
       <c r="C20" t="n">
-        <v>0.185</v>
+        <v>0.168</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3997</v>
+        <v>-0.4017</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4932</v>
+        <v>0.448</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7272</v>
+        <v>0.448</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.234</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7272</v>
+        <v>0.448</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7272</v>
+        <v>0.448</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.234</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="L20" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4932</v>
+        <v>0.448</v>
       </c>
       <c r="N20" t="n">
-        <v>201</v>
+        <v>135</v>
       </c>
     </row>
     <row r="21">
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.1551</v>
+        <v>0.2347</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0582</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5536</v>
+        <v>-0.4989</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1551</v>
+        <v>0.2347</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1551</v>
+        <v>0.2347</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1551</v>
+        <v>0.2347</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1551</v>
+        <v>0.2347</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1551</v>
+        <v>0.2347</v>
       </c>
       <c r="N21" t="n">
         <v>112</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.0828</v>
+        <v>0.1521</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0311</v>
+        <v>0.0571</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5865</v>
+        <v>-0.5365</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0828</v>
+        <v>0.1521</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0828</v>
+        <v>0.1521</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0828</v>
+        <v>0.1521</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0828</v>
+        <v>0.1521</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0828</v>
+        <v>0.1521</v>
       </c>
       <c r="N22" t="n">
         <v>112</v>
@@ -1462,31 +1462,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.0747</v>
+        <v>0.058</v>
       </c>
       <c r="C23" t="n">
-        <v>0.028</v>
+        <v>0.0218</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.5901999999999999</v>
+        <v>-0.5794</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0747</v>
+        <v>0.058</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5505</v>
+        <v>0.5447</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.4758</v>
+        <v>-0.4867</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5505</v>
+        <v>0.5447</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5647</v>
+        <v>0.5593</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.4758</v>
+        <v>-0.4867</v>
       </c>
       <c r="K23" t="n">
         <v>120</v>
@@ -1495,7 +1495,7 @@
         <v>86</v>
       </c>
       <c r="M23" t="n">
-        <v>0.08889999999999998</v>
+        <v>0.0726</v>
       </c>
       <c r="N23" t="n">
         <v>206</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.0143</v>
+        <v>0.0004</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.0054</v>
+        <v>0.0002</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.6307</v>
+        <v>-0.6056</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.0143</v>
+        <v>0.0004</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.0143</v>
+        <v>0.0004</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.0143</v>
+        <v>0.0004</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.0143</v>
+        <v>0.0004</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.0143</v>
+        <v>0.0004</v>
       </c>
       <c r="N24" t="n">
         <v>112</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.1959</v>
+        <v>-0.1579</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.0735</v>
+        <v>-0.0592</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.7134</v>
+        <v>-0.6777</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.1959</v>
+        <v>-0.1579</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.1959</v>
+        <v>-0.1579</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.1959</v>
+        <v>-0.1579</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1959</v>
+        <v>-0.1579</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.1959</v>
+        <v>-0.1579</v>
       </c>
       <c r="N25" t="n">
         <v>112</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.2983</v>
+        <v>-0.3908</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.1119</v>
+        <v>-0.1466</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.76</v>
+        <v>-0.7838000000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.2983</v>
+        <v>-0.3908</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.2983</v>
+        <v>-0.3908</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.2983</v>
+        <v>-0.3908</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.2983</v>
+        <v>-0.3908</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.2983</v>
+        <v>-0.3908</v>
       </c>
       <c r="N26" t="n">
         <v>135</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.4391</v>
+        <v>-0.4018</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.1647</v>
+        <v>-0.1507</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.8241000000000001</v>
+        <v>-0.7887999999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.4391</v>
+        <v>-0.4018</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.4391</v>
+        <v>-0.4018</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.4391</v>
+        <v>-0.4018</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.4391</v>
+        <v>-0.4018</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.4391</v>
+        <v>-0.4018</v>
       </c>
       <c r="N27" t="n">
         <v>121</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.4937</v>
+        <v>-0.5854</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.1852</v>
+        <v>-0.2196</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.8489</v>
+        <v>-0.8725000000000001</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.4937</v>
+        <v>-0.5854</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.4937</v>
+        <v>-0.5854</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.4937</v>
+        <v>-0.5854</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.4937</v>
+        <v>-0.5854</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.4937</v>
+        <v>-0.5854</v>
       </c>
       <c r="N28" t="n">
         <v>135</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.7482</v>
+        <v>-0.6803</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.2806</v>
+        <v>-0.2552</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.9648</v>
+        <v>-0.9157</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.7482</v>
+        <v>-0.6803</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.7482</v>
+        <v>-0.6803</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.7482</v>
+        <v>-0.6803</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.7482</v>
+        <v>-0.6803</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.7482</v>
+        <v>-0.6803</v>
       </c>
       <c r="N29" t="n">
         <v>135</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-1.0624</v>
+        <v>-1.0623</v>
       </c>
       <c r="C30" t="n">
         <v>-0.3985</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.1078</v>
+        <v>-1.0897</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.0624</v>
+        <v>-1.0623</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.0624</v>
+        <v>-1.0623</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-1.0624</v>
+        <v>-1.0623</v>
       </c>
       <c r="I30" t="n">
-        <v>-1.0624</v>
+        <v>-1.0623</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-1.0624</v>
+        <v>-1.0623</v>
       </c>
       <c r="N30" t="n">
         <v>121</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-1.7389</v>
+        <v>-1.69</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.6522</v>
+        <v>-0.6339</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.4158</v>
+        <v>-1.3757</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.7389</v>
+        <v>-1.69</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.7389</v>
+        <v>-1.69</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-1.7389</v>
+        <v>-1.69</v>
       </c>
       <c r="I31" t="n">
-        <v>-1.7389</v>
+        <v>-1.69</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-1.7389</v>
+        <v>-1.69</v>
       </c>
       <c r="N31" t="n">
         <v>137</v>
@@ -1969,10 +1969,10 @@
         <v>1.42</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5481</v>
+        <v>0.478</v>
       </c>
       <c r="J2" t="n">
-        <v>14.7987</v>
+        <v>12.906</v>
       </c>
     </row>
     <row r="3">
@@ -2009,10 +2009,10 @@
         <v>1.35</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4728</v>
+        <v>0.4057</v>
       </c>
       <c r="J3" t="n">
-        <v>12.7656</v>
+        <v>10.9539</v>
       </c>
     </row>
     <row r="4">
@@ -2049,10 +2049,10 @@
         <v>1.3</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4174</v>
+        <v>0.3536</v>
       </c>
       <c r="J4" t="n">
-        <v>11.2698</v>
+        <v>9.5472</v>
       </c>
     </row>
     <row r="5">
@@ -2089,10 +2089,10 @@
         <v>1.04</v>
       </c>
       <c r="I5" t="n">
-        <v>0.07920000000000001</v>
+        <v>0.058</v>
       </c>
       <c r="J5" t="n">
-        <v>2.1384</v>
+        <v>1.566</v>
       </c>
     </row>
     <row r="6">
@@ -2129,10 +2129,10 @@
         <v>0.7</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3605</v>
+        <v>-0.3484</v>
       </c>
       <c r="J6" t="n">
-        <v>-9.733499999999999</v>
+        <v>-9.4068</v>
       </c>
     </row>
     <row r="7">
@@ -2169,10 +2169,10 @@
         <v>1.42</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6118</v>
+        <v>0.6405999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>16.5186</v>
+        <v>17.2962</v>
       </c>
     </row>
     <row r="8">
@@ -2209,10 +2209,10 @@
         <v>0.92</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1236</v>
+        <v>-0.1051</v>
       </c>
       <c r="J8" t="n">
-        <v>-3.3372</v>
+        <v>-2.8377</v>
       </c>
     </row>
     <row r="9">
@@ -2249,10 +2249,10 @@
         <v>0.9</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1469</v>
+        <v>-0.1273</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.9663</v>
+        <v>-3.4371</v>
       </c>
     </row>
     <row r="10">
@@ -2289,10 +2289,10 @@
         <v>0.89</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1582</v>
+        <v>-0.1382</v>
       </c>
       <c r="J10" t="n">
-        <v>-4.2714</v>
+        <v>-3.7314</v>
       </c>
     </row>
     <row r="11">
@@ -2329,10 +2329,10 @@
         <v>0.87</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1802</v>
+        <v>-0.1597</v>
       </c>
       <c r="J11" t="n">
-        <v>-4.8654</v>
+        <v>-4.3119</v>
       </c>
     </row>
     <row r="12">
@@ -2369,10 +2369,10 @@
         <v>1.06</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2149</v>
+        <v>0.1757</v>
       </c>
       <c r="J12" t="n">
-        <v>5.1576</v>
+        <v>4.2168</v>
       </c>
     </row>
     <row r="13">
@@ -2409,10 +2409,10 @@
         <v>1.01</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0813</v>
+        <v>0.062</v>
       </c>
       <c r="J13" t="n">
-        <v>1.9512</v>
+        <v>1.488</v>
       </c>
     </row>
     <row r="14">
@@ -2449,10 +2449,10 @@
         <v>0.76</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2733</v>
+        <v>-0.2554</v>
       </c>
       <c r="J14" t="n">
-        <v>-6.5592</v>
+        <v>-6.1296</v>
       </c>
     </row>
     <row r="15">
@@ -2489,10 +2489,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3385</v>
+        <v>-0.3228</v>
       </c>
       <c r="J15" t="n">
-        <v>-8.124000000000001</v>
+        <v>-7.7472</v>
       </c>
     </row>
     <row r="16">
@@ -2529,10 +2529,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.455</v>
+        <v>-0.4489</v>
       </c>
       <c r="J16" t="n">
-        <v>-10.92</v>
+        <v>-10.7736</v>
       </c>
     </row>
     <row r="17">
@@ -2569,10 +2569,10 @@
         <v>1.67</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4338</v>
+        <v>1.4701</v>
       </c>
       <c r="J17" t="n">
-        <v>34.4112</v>
+        <v>35.2824</v>
       </c>
     </row>
     <row r="18">
@@ -2609,10 +2609,10 @@
         <v>1.43</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9989</v>
+        <v>0.9915</v>
       </c>
       <c r="J18" t="n">
-        <v>23.9736</v>
+        <v>23.796</v>
       </c>
     </row>
     <row r="19">
@@ -2649,10 +2649,10 @@
         <v>1.12</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3555</v>
+        <v>0.3225</v>
       </c>
       <c r="J19" t="n">
-        <v>8.532</v>
+        <v>7.74</v>
       </c>
     </row>
     <row r="20">
@@ -2689,10 +2689,10 @@
         <v>1.09</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2779</v>
+        <v>0.2465</v>
       </c>
       <c r="J20" t="n">
-        <v>6.6696</v>
+        <v>5.916</v>
       </c>
     </row>
     <row r="21">
@@ -2729,10 +2729,10 @@
         <v>0.87</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4638</v>
+        <v>-0.4244</v>
       </c>
       <c r="J21" t="n">
-        <v>-11.1312</v>
+        <v>-10.1856</v>
       </c>
     </row>
     <row r="22">
@@ -2769,10 +2769,10 @@
         <v>1.06</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2122</v>
+        <v>0.1727</v>
       </c>
       <c r="J22" t="n">
-        <v>7.427</v>
+        <v>6.0445</v>
       </c>
     </row>
     <row r="23">
@@ -2809,10 +2809,10 @@
         <v>0.85</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1871</v>
+        <v>-0.1698</v>
       </c>
       <c r="J23" t="n">
-        <v>-6.5485</v>
+        <v>-5.943</v>
       </c>
     </row>
     <row r="24">
@@ -2849,10 +2849,10 @@
         <v>0.78</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2551</v>
+        <v>-0.2368</v>
       </c>
       <c r="J24" t="n">
-        <v>-8.9285</v>
+        <v>-8.288</v>
       </c>
     </row>
     <row r="25">
@@ -2889,10 +2889,10 @@
         <v>0.73</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3024</v>
+        <v>-0.285</v>
       </c>
       <c r="J25" t="n">
-        <v>-10.584</v>
+        <v>-9.975</v>
       </c>
     </row>
     <row r="26">
@@ -2929,10 +2929,10 @@
         <v>0.7</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3302</v>
+        <v>-0.314</v>
       </c>
       <c r="J26" t="n">
-        <v>-11.557</v>
+        <v>-10.99</v>
       </c>
     </row>
     <row r="27">
@@ -2969,10 +2969,10 @@
         <v>1.78</v>
       </c>
       <c r="I27" t="n">
-        <v>1.5983</v>
+        <v>1.6277</v>
       </c>
       <c r="J27" t="n">
-        <v>55.9405</v>
+        <v>56.9695</v>
       </c>
     </row>
     <row r="28">
@@ -3009,10 +3009,10 @@
         <v>1.33</v>
       </c>
       <c r="I28" t="n">
-        <v>0.8041</v>
+        <v>0.7819</v>
       </c>
       <c r="J28" t="n">
-        <v>28.1435</v>
+        <v>27.3665</v>
       </c>
     </row>
     <row r="29">
@@ -3049,10 +3049,10 @@
         <v>1.12</v>
       </c>
       <c r="I29" t="n">
-        <v>0.3535</v>
+        <v>0.3209</v>
       </c>
       <c r="J29" t="n">
-        <v>12.3725</v>
+        <v>11.2315</v>
       </c>
     </row>
     <row r="30">
@@ -3089,10 +3089,10 @@
         <v>1.11</v>
       </c>
       <c r="I30" t="n">
-        <v>0.3283</v>
+        <v>0.2959</v>
       </c>
       <c r="J30" t="n">
-        <v>11.4905</v>
+        <v>10.3565</v>
       </c>
     </row>
     <row r="31">
@@ -3129,10 +3129,10 @@
         <v>0.9</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3883</v>
+        <v>-0.3485</v>
       </c>
       <c r="J31" t="n">
-        <v>-13.5905</v>
+        <v>-12.1975</v>
       </c>
     </row>
     <row r="32">
@@ -3169,10 +3169,10 @@
         <v>1.33</v>
       </c>
       <c r="I32" t="n">
-        <v>0.8437</v>
+        <v>0.8206</v>
       </c>
       <c r="J32" t="n">
-        <v>25.311</v>
+        <v>24.618</v>
       </c>
     </row>
     <row r="33">
@@ -3209,10 +3209,10 @@
         <v>1.06</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2187</v>
+        <v>0.1867</v>
       </c>
       <c r="J33" t="n">
-        <v>6.561</v>
+        <v>5.601</v>
       </c>
     </row>
     <row r="34">
@@ -3249,10 +3249,10 @@
         <v>1.02</v>
       </c>
       <c r="I34" t="n">
-        <v>0.0883</v>
+        <v>0.0698</v>
       </c>
       <c r="J34" t="n">
-        <v>2.649</v>
+        <v>2.094</v>
       </c>
     </row>
     <row r="35">
@@ -3289,10 +3289,10 @@
         <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.0125</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.375</v>
+        <v>-0.252</v>
       </c>
     </row>
     <row r="36">
@@ -3329,10 +3329,10 @@
         <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.0125</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.375</v>
+        <v>-0.252</v>
       </c>
     </row>
     <row r="37">
@@ -3369,10 +3369,10 @@
         <v>1.11</v>
       </c>
       <c r="I37" t="n">
-        <v>0.273</v>
+        <v>0.2246</v>
       </c>
       <c r="J37" t="n">
-        <v>8.19</v>
+        <v>6.738</v>
       </c>
     </row>
     <row r="38">
@@ -3409,10 +3409,10 @@
         <v>1.08</v>
       </c>
       <c r="I38" t="n">
-        <v>0.2134</v>
+        <v>0.1708</v>
       </c>
       <c r="J38" t="n">
-        <v>6.402</v>
+        <v>5.124</v>
       </c>
     </row>
     <row r="39">
@@ -3449,10 +3449,10 @@
         <v>1.03</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1007</v>
+        <v>0.0743</v>
       </c>
       <c r="J39" t="n">
-        <v>3.021</v>
+        <v>2.229</v>
       </c>
     </row>
     <row r="40">
@@ -3489,10 +3489,10 @@
         <v>0.88</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.1688</v>
+        <v>-0.1485</v>
       </c>
       <c r="J40" t="n">
-        <v>-5.064</v>
+        <v>-4.455</v>
       </c>
     </row>
     <row r="41">
@@ -3529,10 +3529,10 @@
         <v>0.87</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.1797</v>
+        <v>-0.1592</v>
       </c>
       <c r="J41" t="n">
-        <v>-5.391</v>
+        <v>-4.776</v>
       </c>
     </row>
     <row r="42">
@@ -3569,10 +3569,10 @@
         <v>1.52</v>
       </c>
       <c r="I42" t="n">
-        <v>0.9481000000000001</v>
+        <v>0.9139</v>
       </c>
       <c r="J42" t="n">
-        <v>26.5468</v>
+        <v>25.5892</v>
       </c>
     </row>
     <row r="43">
@@ -3609,10 +3609,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.0953</v>
+        <v>-0.0798</v>
       </c>
       <c r="J43" t="n">
-        <v>-2.6684</v>
+        <v>-2.2344</v>
       </c>
     </row>
     <row r="44">
@@ -3649,10 +3649,10 @@
         <v>0.88</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.1646</v>
+        <v>-0.145</v>
       </c>
       <c r="J44" t="n">
-        <v>-4.6088</v>
+        <v>-4.06</v>
       </c>
     </row>
     <row r="45">
@@ -3689,10 +3689,10 @@
         <v>0.8</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.2474</v>
+        <v>-0.2274</v>
       </c>
       <c r="J45" t="n">
-        <v>-6.9272</v>
+        <v>-6.3672</v>
       </c>
     </row>
     <row r="46">
@@ -3729,10 +3729,10 @@
         <v>0.59</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.4414</v>
+        <v>-0.435</v>
       </c>
       <c r="J46" t="n">
-        <v>-12.3592</v>
+        <v>-12.18</v>
       </c>
     </row>
     <row r="47">
@@ -3769,10 +3769,10 @@
         <v>1.53</v>
       </c>
       <c r="I47" t="n">
-        <v>1.1568</v>
+        <v>1.1708</v>
       </c>
       <c r="J47" t="n">
-        <v>32.3904</v>
+        <v>32.7824</v>
       </c>
     </row>
     <row r="48">
@@ -3809,10 +3809,10 @@
         <v>1.42</v>
       </c>
       <c r="I48" t="n">
-        <v>0.9958</v>
+        <v>0.9918</v>
       </c>
       <c r="J48" t="n">
-        <v>27.8824</v>
+        <v>27.7704</v>
       </c>
     </row>
     <row r="49">
@@ -3849,10 +3849,10 @@
         <v>1.09</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2915</v>
+        <v>0.2581</v>
       </c>
       <c r="J49" t="n">
-        <v>8.162000000000001</v>
+        <v>7.2268</v>
       </c>
     </row>
     <row r="50">
@@ -3889,10 +3889,10 @@
         <v>0.98</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1263</v>
+        <v>-0.099</v>
       </c>
       <c r="J50" t="n">
-        <v>-3.5364</v>
+        <v>-2.772</v>
       </c>
     </row>
     <row r="51">
@@ -3929,10 +3929,10 @@
         <v>0.74</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.7513</v>
+        <v>-0.7252</v>
       </c>
       <c r="J51" t="n">
-        <v>-21.0364</v>
+        <v>-20.3056</v>
       </c>
     </row>
     <row r="52">
@@ -3969,10 +3969,10 @@
         <v>1.59</v>
       </c>
       <c r="I52" t="n">
-        <v>1.1977</v>
+        <v>1.213</v>
       </c>
       <c r="J52" t="n">
-        <v>27.5471</v>
+        <v>27.899</v>
       </c>
     </row>
     <row r="53">
@@ -4009,10 +4009,10 @@
         <v>1.48</v>
       </c>
       <c r="I53" t="n">
-        <v>1.052</v>
+        <v>1.0603</v>
       </c>
       <c r="J53" t="n">
-        <v>24.196</v>
+        <v>24.3869</v>
       </c>
     </row>
     <row r="54">
@@ -4049,10 +4049,10 @@
         <v>1.47</v>
       </c>
       <c r="I54" t="n">
-        <v>1.0377</v>
+        <v>1.044</v>
       </c>
       <c r="J54" t="n">
-        <v>23.8671</v>
+        <v>24.012</v>
       </c>
     </row>
     <row r="55">
@@ -4089,10 +4089,10 @@
         <v>1.19</v>
       </c>
       <c r="I55" t="n">
-        <v>0.5046</v>
+        <v>0.4748</v>
       </c>
       <c r="J55" t="n">
-        <v>11.6058</v>
+        <v>10.9204</v>
       </c>
     </row>
     <row r="56">
@@ -4129,10 +4129,10 @@
         <v>0.96</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.2283</v>
+        <v>-0.1966</v>
       </c>
       <c r="J56" t="n">
-        <v>-5.2509</v>
+        <v>-4.5218</v>
       </c>
     </row>
     <row r="57">
@@ -4169,10 +4169,10 @@
         <v>0.99</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.0109</v>
+        <v>-0.0066</v>
       </c>
       <c r="J57" t="n">
-        <v>-0.2507</v>
+        <v>-0.1518</v>
       </c>
     </row>
     <row r="58">
@@ -4209,10 +4209,10 @@
         <v>0.92</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.1122</v>
+        <v>-0.0973</v>
       </c>
       <c r="J58" t="n">
-        <v>-2.5806</v>
+        <v>-2.2379</v>
       </c>
     </row>
     <row r="59">
@@ -4249,10 +4249,10 @@
         <v>0.85</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1889</v>
+        <v>-0.1707</v>
       </c>
       <c r="J59" t="n">
-        <v>-4.3447</v>
+        <v>-3.9261</v>
       </c>
     </row>
     <row r="60">
@@ -4289,10 +4289,10 @@
         <v>0.78</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2578</v>
+        <v>-0.239</v>
       </c>
       <c r="J60" t="n">
-        <v>-5.9294</v>
+        <v>-5.497</v>
       </c>
     </row>
     <row r="61">
@@ -4329,10 +4329,10 @@
         <v>0.72</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3147</v>
+        <v>-0.2975</v>
       </c>
       <c r="J61" t="n">
-        <v>-7.2381</v>
+        <v>-6.8425</v>
       </c>
     </row>
     <row r="62">
@@ -4369,10 +4369,10 @@
         <v>0.99</v>
       </c>
       <c r="I62" t="n">
-        <v>0.0098</v>
+        <v>0.0186</v>
       </c>
       <c r="J62" t="n">
-        <v>0.2352</v>
+        <v>0.4464</v>
       </c>
     </row>
     <row r="63">
@@ -4409,10 +4409,10 @@
         <v>0.93</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.0858</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="J63" t="n">
-        <v>-2.0592</v>
+        <v>-1.728</v>
       </c>
     </row>
     <row r="64">
@@ -4449,10 +4449,10 @@
         <v>0.87</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.1576</v>
+        <v>-0.142</v>
       </c>
       <c r="J64" t="n">
-        <v>-3.7824</v>
+        <v>-3.408</v>
       </c>
     </row>
     <row r="65">
@@ -4489,10 +4489,10 @@
         <v>0.54</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.4663</v>
+        <v>-0.461</v>
       </c>
       <c r="J65" t="n">
-        <v>-11.1912</v>
+        <v>-11.064</v>
       </c>
     </row>
     <row r="66">
@@ -4529,10 +4529,10 @@
         <v>0.47</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.5272</v>
+        <v>-0.5296</v>
       </c>
       <c r="J66" t="n">
-        <v>-12.6528</v>
+        <v>-12.7104</v>
       </c>
     </row>
     <row r="67">
@@ -4569,10 +4569,10 @@
         <v>1.93</v>
       </c>
       <c r="I67" t="n">
-        <v>1.6114</v>
+        <v>1.6523</v>
       </c>
       <c r="J67" t="n">
-        <v>38.6736</v>
+        <v>39.6552</v>
       </c>
     </row>
     <row r="68">
@@ -4609,10 +4609,10 @@
         <v>1.69</v>
       </c>
       <c r="I68" t="n">
-        <v>1.3176</v>
+        <v>1.3379</v>
       </c>
       <c r="J68" t="n">
-        <v>31.6224</v>
+        <v>32.1096</v>
       </c>
     </row>
     <row r="69">
@@ -4649,10 +4649,10 @@
         <v>1.31</v>
       </c>
       <c r="I69" t="n">
-        <v>0.7495000000000001</v>
+        <v>0.7311</v>
       </c>
       <c r="J69" t="n">
-        <v>17.988</v>
+        <v>17.5464</v>
       </c>
     </row>
     <row r="70">
@@ -4689,10 +4689,10 @@
         <v>1.07</v>
       </c>
       <c r="I70" t="n">
-        <v>0.1991</v>
+        <v>0.1691</v>
       </c>
       <c r="J70" t="n">
-        <v>4.7784</v>
+        <v>4.0584</v>
       </c>
     </row>
     <row r="71">
@@ -4729,10 +4729,10 @@
         <v>0.91</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.3823</v>
+        <v>-0.3466</v>
       </c>
       <c r="J71" t="n">
-        <v>-9.1752</v>
+        <v>-8.3184</v>
       </c>
     </row>
     <row r="72">
@@ -4769,10 +4769,10 @@
         <v>1.68</v>
       </c>
       <c r="I72" t="n">
-        <v>1.3012</v>
+        <v>1.3211</v>
       </c>
       <c r="J72" t="n">
-        <v>26.024</v>
+        <v>26.422</v>
       </c>
     </row>
     <row r="73">
@@ -4809,10 +4809,10 @@
         <v>1.51</v>
       </c>
       <c r="I73" t="n">
-        <v>1.0841</v>
+        <v>1.0976</v>
       </c>
       <c r="J73" t="n">
-        <v>21.682</v>
+        <v>21.952</v>
       </c>
     </row>
     <row r="74">
@@ -4849,10 +4849,10 @@
         <v>1.47</v>
       </c>
       <c r="I74" t="n">
-        <v>1.0292</v>
+        <v>1.0368</v>
       </c>
       <c r="J74" t="n">
-        <v>20.584</v>
+        <v>20.736</v>
       </c>
     </row>
     <row r="75">
@@ -4889,10 +4889,10 @@
         <v>1.22</v>
       </c>
       <c r="I75" t="n">
-        <v>0.5608</v>
+        <v>0.5339</v>
       </c>
       <c r="J75" t="n">
-        <v>11.216</v>
+        <v>10.678</v>
       </c>
     </row>
     <row r="76">
@@ -4929,10 +4929,10 @@
         <v>1.14</v>
       </c>
       <c r="I76" t="n">
-        <v>0.3783</v>
+        <v>0.3463</v>
       </c>
       <c r="J76" t="n">
-        <v>7.566</v>
+        <v>6.926</v>
       </c>
     </row>
     <row r="77">
@@ -4969,10 +4969,10 @@
         <v>1.17</v>
       </c>
       <c r="I77" t="n">
-        <v>0.4558</v>
+        <v>0.41</v>
       </c>
       <c r="J77" t="n">
-        <v>9.116</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="78">
@@ -5009,10 +5009,10 @@
         <v>0.78</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.2516</v>
+        <v>-0.2347</v>
       </c>
       <c r="J78" t="n">
-        <v>-5.032</v>
+        <v>-4.694</v>
       </c>
     </row>
     <row r="79">
@@ -5049,10 +5049,10 @@
         <v>0.67</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.3525</v>
+        <v>-0.3379</v>
       </c>
       <c r="J79" t="n">
-        <v>-7.05</v>
+        <v>-6.758</v>
       </c>
     </row>
     <row r="80">
@@ -5089,10 +5089,10 @@
         <v>0.67</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.3525</v>
+        <v>-0.3379</v>
       </c>
       <c r="J80" t="n">
-        <v>-7.05</v>
+        <v>-6.758</v>
       </c>
     </row>
     <row r="81">
@@ -5129,10 +5129,10 @@
         <v>0.6</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4154</v>
+        <v>-0.4052</v>
       </c>
       <c r="J81" t="n">
-        <v>-8.308</v>
+        <v>-8.103999999999999</v>
       </c>
     </row>
     <row r="82">
@@ -5169,10 +5169,10 @@
         <v>1.74</v>
       </c>
       <c r="I82" t="n">
-        <v>1.3592</v>
+        <v>1.3833</v>
       </c>
       <c r="J82" t="n">
-        <v>24.4656</v>
+        <v>24.8994</v>
       </c>
     </row>
     <row r="83">
@@ -5209,10 +5209,10 @@
         <v>1.57</v>
       </c>
       <c r="I83" t="n">
-        <v>1.1499</v>
+        <v>1.1684</v>
       </c>
       <c r="J83" t="n">
-        <v>20.6982</v>
+        <v>21.0312</v>
       </c>
     </row>
     <row r="84">
@@ -5249,10 +5249,10 @@
         <v>1.53</v>
       </c>
       <c r="I84" t="n">
-        <v>1.0999</v>
+        <v>1.1178</v>
       </c>
       <c r="J84" t="n">
-        <v>19.7982</v>
+        <v>20.1204</v>
       </c>
     </row>
     <row r="85">
@@ -5289,10 +5289,10 @@
         <v>1.43</v>
       </c>
       <c r="I85" t="n">
-        <v>0.958</v>
+        <v>0.9608</v>
       </c>
       <c r="J85" t="n">
-        <v>17.244</v>
+        <v>17.2944</v>
       </c>
     </row>
     <row r="86">
@@ -5329,10 +5329,10 @@
         <v>1.27</v>
       </c>
       <c r="I86" t="n">
-        <v>0.6514</v>
+        <v>0.6302</v>
       </c>
       <c r="J86" t="n">
-        <v>11.7252</v>
+        <v>11.3436</v>
       </c>
     </row>
     <row r="87">
@@ -5369,10 +5369,10 @@
         <v>1.15</v>
       </c>
       <c r="I87" t="n">
-        <v>0.4777</v>
+        <v>0.4512</v>
       </c>
       <c r="J87" t="n">
-        <v>8.598599999999999</v>
+        <v>8.121600000000001</v>
       </c>
     </row>
     <row r="88">
@@ -5409,10 +5409,10 @@
         <v>0.85</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.163</v>
+        <v>-0.1467</v>
       </c>
       <c r="J88" t="n">
-        <v>-2.934</v>
+        <v>-2.6406</v>
       </c>
     </row>
     <row r="89">
@@ -5449,10 +5449,10 @@
         <v>0.78</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.2379</v>
+        <v>-0.2235</v>
       </c>
       <c r="J89" t="n">
-        <v>-4.2822</v>
+        <v>-4.023</v>
       </c>
     </row>
     <row r="90">
@@ -5489,10 +5489,10 @@
         <v>0.33</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.6385</v>
+        <v>-0.6576</v>
       </c>
       <c r="J90" t="n">
-        <v>-11.493</v>
+        <v>-11.8368</v>
       </c>
     </row>
     <row r="91">
@@ -5529,10 +5529,10 @@
         <v>0.25</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.7073</v>
+        <v>-0.7403999999999999</v>
       </c>
       <c r="J91" t="n">
-        <v>-12.7314</v>
+        <v>-13.3272</v>
       </c>
     </row>
     <row r="92">
@@ -5569,10 +5569,10 @@
         <v>1.35</v>
       </c>
       <c r="I92" t="n">
-        <v>0.6508</v>
+        <v>0.5914</v>
       </c>
       <c r="J92" t="n">
-        <v>19.524</v>
+        <v>17.742</v>
       </c>
     </row>
     <row r="93">
@@ -5609,10 +5609,10 @@
         <v>1.21</v>
       </c>
       <c r="I93" t="n">
-        <v>0.4319</v>
+        <v>0.3753</v>
       </c>
       <c r="J93" t="n">
-        <v>12.957</v>
+        <v>11.259</v>
       </c>
     </row>
     <row r="94">
@@ -5649,10 +5649,10 @@
         <v>1.2</v>
       </c>
       <c r="I94" t="n">
-        <v>0.4154</v>
+        <v>0.3595</v>
       </c>
       <c r="J94" t="n">
-        <v>12.462</v>
+        <v>10.785</v>
       </c>
     </row>
     <row r="95">
@@ -5689,10 +5689,10 @@
         <v>1.13</v>
       </c>
       <c r="I95" t="n">
-        <v>0.2949</v>
+        <v>0.247</v>
       </c>
       <c r="J95" t="n">
-        <v>8.847</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="96">
@@ -5729,10 +5729,10 @@
         <v>0.57</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.47</v>
+        <v>-0.4689</v>
       </c>
       <c r="J96" t="n">
-        <v>-14.1</v>
+        <v>-14.067</v>
       </c>
     </row>
     <row r="97">
@@ -5769,10 +5769,10 @@
         <v>1.23</v>
       </c>
       <c r="I97" t="n">
-        <v>0.4842</v>
+        <v>0.4254</v>
       </c>
       <c r="J97" t="n">
-        <v>14.526</v>
+        <v>12.762</v>
       </c>
     </row>
     <row r="98">
@@ -5809,10 +5809,10 @@
         <v>1.03</v>
       </c>
       <c r="I98" t="n">
-        <v>0.1</v>
+        <v>0.0738</v>
       </c>
       <c r="J98" t="n">
-        <v>3</v>
+        <v>2.214</v>
       </c>
     </row>
     <row r="99">
@@ -5849,10 +5849,10 @@
         <v>1.01</v>
       </c>
       <c r="I99" t="n">
-        <v>0.0433</v>
+        <v>0.0293</v>
       </c>
       <c r="J99" t="n">
-        <v>1.299</v>
+        <v>0.879</v>
       </c>
     </row>
     <row r="100">
@@ -5889,10 +5889,10 @@
         <v>0.92</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.1236</v>
+        <v>-0.1051</v>
       </c>
       <c r="J100" t="n">
-        <v>-3.708</v>
+        <v>-3.153</v>
       </c>
     </row>
     <row r="101">
@@ -5929,10 +5929,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.2425</v>
+        <v>-0.2223</v>
       </c>
       <c r="J101" t="n">
-        <v>-7.275</v>
+        <v>-6.669</v>
       </c>
     </row>
     <row r="102">
@@ -5969,10 +5969,10 @@
         <v>1.03</v>
       </c>
       <c r="I102" t="n">
-        <v>0.1534</v>
+        <v>0.1244</v>
       </c>
       <c r="J102" t="n">
-        <v>3.6816</v>
+        <v>2.9856</v>
       </c>
     </row>
     <row r="103">
@@ -6009,10 +6009,10 @@
         <v>0.89</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.138</v>
+        <v>-0.1227</v>
       </c>
       <c r="J103" t="n">
-        <v>-3.312</v>
+        <v>-2.9448</v>
       </c>
     </row>
     <row r="104">
@@ -6049,10 +6049,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.2232</v>
+        <v>-0.2065</v>
       </c>
       <c r="J104" t="n">
-        <v>-5.3568</v>
+        <v>-4.956</v>
       </c>
     </row>
     <row r="105">
@@ -6089,10 +6089,10 @@
         <v>0.68</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.3436</v>
+        <v>-0.3285</v>
       </c>
       <c r="J105" t="n">
-        <v>-8.2464</v>
+        <v>-7.884</v>
       </c>
     </row>
     <row r="106">
@@ -6129,10 +6129,10 @@
         <v>0.49</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.5121</v>
+        <v>-0.5125999999999999</v>
       </c>
       <c r="J106" t="n">
-        <v>-12.2904</v>
+        <v>-12.3024</v>
       </c>
     </row>
     <row r="107">
@@ -6169,10 +6169,10 @@
         <v>1.85</v>
       </c>
       <c r="I107" t="n">
-        <v>1.5419</v>
+        <v>1.5791</v>
       </c>
       <c r="J107" t="n">
-        <v>37.0056</v>
+        <v>37.8984</v>
       </c>
     </row>
     <row r="108">
@@ -6209,10 +6209,10 @@
         <v>1.35</v>
       </c>
       <c r="I108" t="n">
-        <v>0.839</v>
+        <v>0.8201000000000001</v>
       </c>
       <c r="J108" t="n">
-        <v>20.136</v>
+        <v>19.6824</v>
       </c>
     </row>
     <row r="109">
@@ -6249,10 +6249,10 @@
         <v>1.29</v>
       </c>
       <c r="I109" t="n">
-        <v>0.7219</v>
+        <v>0.6968</v>
       </c>
       <c r="J109" t="n">
-        <v>17.3256</v>
+        <v>16.7232</v>
       </c>
     </row>
     <row r="110">
@@ -6289,10 +6289,10 @@
         <v>1.2</v>
       </c>
       <c r="I110" t="n">
-        <v>0.5366</v>
+        <v>0.5057</v>
       </c>
       <c r="J110" t="n">
-        <v>12.8784</v>
+        <v>12.1368</v>
       </c>
     </row>
     <row r="111">
@@ -6329,10 +6329,10 @@
         <v>0.67</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.918</v>
+        <v>-0.9123</v>
       </c>
       <c r="J111" t="n">
-        <v>-22.032</v>
+        <v>-21.8952</v>
       </c>
     </row>
     <row r="112">
@@ -6369,10 +6369,10 @@
         <v>0.83</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.175</v>
+        <v>-0.1578</v>
       </c>
       <c r="J112" t="n">
-        <v>-3.5</v>
+        <v>-3.156</v>
       </c>
     </row>
     <row r="113">
@@ -6409,10 +6409,10 @@
         <v>0.68</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.3276</v>
+        <v>-0.3167</v>
       </c>
       <c r="J113" t="n">
-        <v>-6.552</v>
+        <v>-6.334</v>
       </c>
     </row>
     <row r="114">
@@ -6449,10 +6449,10 @@
         <v>0.67</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.3367</v>
+        <v>-0.3261</v>
       </c>
       <c r="J114" t="n">
-        <v>-6.734</v>
+        <v>-6.522</v>
       </c>
     </row>
     <row r="115">
@@ -6489,10 +6489,10 @@
         <v>0.49</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.4933</v>
+        <v>-0.4907</v>
       </c>
       <c r="J115" t="n">
-        <v>-9.866</v>
+        <v>-9.814</v>
       </c>
     </row>
     <row r="116">
@@ -6529,10 +6529,10 @@
         <v>0.48</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.5021</v>
+        <v>-0.5004</v>
       </c>
       <c r="J116" t="n">
-        <v>-10.042</v>
+        <v>-10.008</v>
       </c>
     </row>
     <row r="117">
@@ -6569,10 +6569,10 @@
         <v>2.24</v>
       </c>
       <c r="I117" t="n">
-        <v>1.9314</v>
+        <v>1.9818</v>
       </c>
       <c r="J117" t="n">
-        <v>38.628</v>
+        <v>39.636</v>
       </c>
     </row>
     <row r="118">
@@ -6609,10 +6609,10 @@
         <v>1.6</v>
       </c>
       <c r="I118" t="n">
-        <v>1.184</v>
+        <v>1.204</v>
       </c>
       <c r="J118" t="n">
-        <v>23.68</v>
+        <v>24.08</v>
       </c>
     </row>
     <row r="119">
@@ -6649,10 +6649,10 @@
         <v>1.54</v>
       </c>
       <c r="I119" t="n">
-        <v>1.1104</v>
+        <v>1.1297</v>
       </c>
       <c r="J119" t="n">
-        <v>22.208</v>
+        <v>22.594</v>
       </c>
     </row>
     <row r="120">
@@ -6689,10 +6689,10 @@
         <v>1.33</v>
       </c>
       <c r="I120" t="n">
-        <v>0.767</v>
+        <v>0.754</v>
       </c>
       <c r="J120" t="n">
-        <v>15.34</v>
+        <v>15.08</v>
       </c>
     </row>
     <row r="121">
@@ -6729,10 +6729,10 @@
         <v>1.01</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.0262</v>
+        <v>-0.0427</v>
       </c>
       <c r="J121" t="n">
-        <v>-0.524</v>
+        <v>-0.854</v>
       </c>
     </row>
     <row r="122">
@@ -6769,10 +6769,10 @@
         <v>1.33</v>
       </c>
       <c r="I122" t="n">
-        <v>0.6131</v>
+        <v>0.5534</v>
       </c>
       <c r="J122" t="n">
-        <v>17.7799</v>
+        <v>16.0486</v>
       </c>
     </row>
     <row r="123">
@@ -6809,10 +6809,10 @@
         <v>1.29</v>
       </c>
       <c r="I123" t="n">
-        <v>0.5524</v>
+        <v>0.4931</v>
       </c>
       <c r="J123" t="n">
-        <v>16.0196</v>
+        <v>14.2999</v>
       </c>
     </row>
     <row r="124">
@@ -6849,10 +6849,10 @@
         <v>1.05</v>
       </c>
       <c r="I124" t="n">
-        <v>0.1342</v>
+        <v>0.1057</v>
       </c>
       <c r="J124" t="n">
-        <v>3.8918</v>
+        <v>3.0653</v>
       </c>
     </row>
     <row r="125">
@@ -6889,10 +6889,10 @@
         <v>1.04</v>
       </c>
       <c r="I125" t="n">
-        <v>0.1109</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="J125" t="n">
-        <v>3.2161</v>
+        <v>2.494</v>
       </c>
     </row>
     <row r="126">
@@ -6929,10 +6929,10 @@
         <v>0.93</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.122</v>
+        <v>-0.1034</v>
       </c>
       <c r="J126" t="n">
-        <v>-3.538</v>
+        <v>-2.9986</v>
       </c>
     </row>
     <row r="127">
@@ -6969,10 +6969,10 @@
         <v>1.1</v>
       </c>
       <c r="I127" t="n">
-        <v>0.3364</v>
+        <v>0.2954</v>
       </c>
       <c r="J127" t="n">
-        <v>9.755599999999999</v>
+        <v>8.566599999999999</v>
       </c>
     </row>
     <row r="128">
@@ -7009,10 +7009,10 @@
         <v>1.07</v>
       </c>
       <c r="I128" t="n">
-        <v>0.2547</v>
+        <v>0.2173</v>
       </c>
       <c r="J128" t="n">
-        <v>7.3863</v>
+        <v>6.3017</v>
       </c>
     </row>
     <row r="129">
@@ -7049,10 +7049,10 @@
         <v>1.06</v>
       </c>
       <c r="I129" t="n">
-        <v>0.2259</v>
+        <v>0.1904</v>
       </c>
       <c r="J129" t="n">
-        <v>6.5511</v>
+        <v>5.5216</v>
       </c>
     </row>
     <row r="130">
@@ -7089,10 +7089,10 @@
         <v>0.95</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2046</v>
+        <v>-0.1692</v>
       </c>
       <c r="J130" t="n">
-        <v>-5.9334</v>
+        <v>-4.9068</v>
       </c>
     </row>
     <row r="131">
@@ -7129,10 +7129,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.2349</v>
+        <v>-0.1973</v>
       </c>
       <c r="J131" t="n">
-        <v>-6.8121</v>
+        <v>-5.7217</v>
       </c>
     </row>
     <row r="132">
@@ -7169,10 +7169,10 @@
         <v>1.85</v>
       </c>
       <c r="I132" t="n">
-        <v>1.5153</v>
+        <v>1.5481</v>
       </c>
       <c r="J132" t="n">
-        <v>31.8213</v>
+        <v>32.5101</v>
       </c>
     </row>
     <row r="133">
@@ -7209,10 +7209,10 @@
         <v>1.52</v>
       </c>
       <c r="I133" t="n">
-        <v>1.1002</v>
+        <v>1.1139</v>
       </c>
       <c r="J133" t="n">
-        <v>23.1042</v>
+        <v>23.3919</v>
       </c>
     </row>
     <row r="134">
@@ -7249,10 +7249,10 @@
         <v>1.3</v>
       </c>
       <c r="I134" t="n">
-        <v>0.73</v>
+        <v>0.7104</v>
       </c>
       <c r="J134" t="n">
-        <v>15.33</v>
+        <v>14.9184</v>
       </c>
     </row>
     <row r="135">
@@ -7289,10 +7289,10 @@
         <v>1.26</v>
       </c>
       <c r="I135" t="n">
-        <v>0.6489</v>
+        <v>0.6253</v>
       </c>
       <c r="J135" t="n">
-        <v>13.6269</v>
+        <v>13.1313</v>
       </c>
     </row>
     <row r="136">
@@ -7329,10 +7329,10 @@
         <v>0.97</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.2009</v>
+        <v>-0.173</v>
       </c>
       <c r="J136" t="n">
-        <v>-4.2189</v>
+        <v>-3.633</v>
       </c>
     </row>
     <row r="137">
@@ -7369,10 +7369,10 @@
         <v>1.03</v>
       </c>
       <c r="I137" t="n">
-        <v>0.1572</v>
+        <v>0.1287</v>
       </c>
       <c r="J137" t="n">
-        <v>3.3012</v>
+        <v>2.7027</v>
       </c>
     </row>
     <row r="138">
@@ -7409,10 +7409,10 @@
         <v>0.77</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.2602</v>
+        <v>-0.2436</v>
       </c>
       <c r="J138" t="n">
-        <v>-5.4642</v>
+        <v>-5.1156</v>
       </c>
     </row>
     <row r="139">
@@ -7449,10 +7449,10 @@
         <v>0.76</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.2692</v>
+        <v>-0.2526</v>
       </c>
       <c r="J139" t="n">
-        <v>-5.6532</v>
+        <v>-5.3046</v>
       </c>
     </row>
     <row r="140">
@@ -7489,10 +7489,10 @@
         <v>0.74</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2875</v>
+        <v>-0.271</v>
       </c>
       <c r="J140" t="n">
-        <v>-6.0375</v>
+        <v>-5.691</v>
       </c>
     </row>
     <row r="141">
@@ -7529,10 +7529,10 @@
         <v>0.55</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4587</v>
+        <v>-0.4526</v>
       </c>
       <c r="J141" t="n">
-        <v>-9.6327</v>
+        <v>-9.5046</v>
       </c>
     </row>
     <row r="142">
@@ -7569,10 +7569,10 @@
         <v>1.53</v>
       </c>
       <c r="I142" t="n">
-        <v>1.1111</v>
+        <v>1.1257</v>
       </c>
       <c r="J142" t="n">
-        <v>26.6664</v>
+        <v>27.0168</v>
       </c>
     </row>
     <row r="143">
@@ -7609,10 +7609,10 @@
         <v>1.44</v>
       </c>
       <c r="I143" t="n">
-        <v>0.9842</v>
+        <v>0.9853</v>
       </c>
       <c r="J143" t="n">
-        <v>23.6208</v>
+        <v>23.6472</v>
       </c>
     </row>
     <row r="144">
@@ -7649,10 +7649,10 @@
         <v>1.43</v>
       </c>
       <c r="I144" t="n">
-        <v>0.968</v>
+        <v>0.9668</v>
       </c>
       <c r="J144" t="n">
-        <v>23.232</v>
+        <v>23.2032</v>
       </c>
     </row>
     <row r="145">
@@ -7689,10 +7689,10 @@
         <v>1.37</v>
       </c>
       <c r="I145" t="n">
-        <v>0.8625</v>
+        <v>0.8515</v>
       </c>
       <c r="J145" t="n">
-        <v>20.7</v>
+        <v>20.436</v>
       </c>
     </row>
     <row r="146">
@@ -7729,10 +7729,10 @@
         <v>1.21</v>
       </c>
       <c r="I146" t="n">
-        <v>0.5402</v>
+        <v>0.5124</v>
       </c>
       <c r="J146" t="n">
-        <v>12.9648</v>
+        <v>12.2976</v>
       </c>
     </row>
     <row r="147">
@@ -7769,10 +7769,10 @@
         <v>0.76</v>
       </c>
       <c r="I147" t="n">
-        <v>-0.2654</v>
+        <v>-0.2505</v>
       </c>
       <c r="J147" t="n">
-        <v>-6.3696</v>
+        <v>-6.012</v>
       </c>
     </row>
     <row r="148">
@@ -7809,10 +7809,10 @@
         <v>0.76</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.2654</v>
+        <v>-0.2505</v>
       </c>
       <c r="J148" t="n">
-        <v>-6.3696</v>
+        <v>-6.012</v>
       </c>
     </row>
     <row r="149">
@@ -7849,10 +7849,10 @@
         <v>0.71</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.3105</v>
+        <v>-0.2958</v>
       </c>
       <c r="J149" t="n">
-        <v>-7.452</v>
+        <v>-7.0992</v>
       </c>
     </row>
     <row r="150">
@@ -7889,10 +7889,10 @@
         <v>0.7</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.3194</v>
+        <v>-0.3048</v>
       </c>
       <c r="J150" t="n">
-        <v>-7.6656</v>
+        <v>-7.3152</v>
       </c>
     </row>
     <row r="151">
@@ -7929,10 +7929,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.3284</v>
+        <v>-0.3139</v>
       </c>
       <c r="J151" t="n">
-        <v>-7.8816</v>
+        <v>-7.5336</v>
       </c>
     </row>
     <row r="152">
@@ -7969,10 +7969,10 @@
         <v>1.16</v>
       </c>
       <c r="I152" t="n">
-        <v>0.3608</v>
+        <v>0.3064</v>
       </c>
       <c r="J152" t="n">
-        <v>10.824</v>
+        <v>9.192</v>
       </c>
     </row>
     <row r="153">
@@ -8009,10 +8009,10 @@
         <v>1.13</v>
       </c>
       <c r="I153" t="n">
-        <v>0.3066</v>
+        <v>0.2557</v>
       </c>
       <c r="J153" t="n">
-        <v>9.198</v>
+        <v>7.671</v>
       </c>
     </row>
     <row r="154">
@@ -8049,10 +8049,10 @@
         <v>1.05</v>
       </c>
       <c r="I154" t="n">
-        <v>0.1457</v>
+        <v>0.1124</v>
       </c>
       <c r="J154" t="n">
-        <v>4.371</v>
+        <v>3.372</v>
       </c>
     </row>
     <row r="155">
@@ -8089,10 +8089,10 @@
         <v>0.89</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.1596</v>
+        <v>-0.1395</v>
       </c>
       <c r="J155" t="n">
-        <v>-4.788</v>
+        <v>-4.185</v>
       </c>
     </row>
     <row r="156">
@@ -8129,10 +8129,10 @@
         <v>0.85</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.2029</v>
+        <v>-0.1822</v>
       </c>
       <c r="J156" t="n">
-        <v>-6.087</v>
+        <v>-5.466</v>
       </c>
     </row>
     <row r="157">
@@ -8169,10 +8169,10 @@
         <v>1.19</v>
       </c>
       <c r="I157" t="n">
-        <v>0.4109</v>
+        <v>0.3542</v>
       </c>
       <c r="J157" t="n">
-        <v>12.327</v>
+        <v>10.626</v>
       </c>
     </row>
     <row r="158">
@@ -8209,10 +8209,10 @@
         <v>1.17</v>
       </c>
       <c r="I158" t="n">
-        <v>0.3764</v>
+        <v>0.3213</v>
       </c>
       <c r="J158" t="n">
-        <v>11.292</v>
+        <v>9.638999999999999</v>
       </c>
     </row>
     <row r="159">
@@ -8249,10 +8249,10 @@
         <v>1.16</v>
       </c>
       <c r="I159" t="n">
-        <v>0.3588</v>
+        <v>0.3047</v>
       </c>
       <c r="J159" t="n">
-        <v>10.764</v>
+        <v>9.141</v>
       </c>
     </row>
     <row r="160">
@@ -8289,10 +8289,10 @@
         <v>0.82</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.2347</v>
+        <v>-0.2144</v>
       </c>
       <c r="J160" t="n">
-        <v>-7.041</v>
+        <v>-6.432</v>
       </c>
     </row>
     <row r="161">
@@ -8329,10 +8329,10 @@
         <v>0.79</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.2646</v>
+        <v>-0.2452</v>
       </c>
       <c r="J161" t="n">
-        <v>-7.938</v>
+        <v>-7.356</v>
       </c>
     </row>
     <row r="162">
@@ -8369,10 +8369,10 @@
         <v>1.33</v>
       </c>
       <c r="I162" t="n">
-        <v>0.6317</v>
+        <v>0.5724</v>
       </c>
       <c r="J162" t="n">
-        <v>18.951</v>
+        <v>17.172</v>
       </c>
     </row>
     <row r="163">
@@ -8409,10 +8409,10 @@
         <v>1.24</v>
       </c>
       <c r="I163" t="n">
-        <v>0.4899</v>
+        <v>0.4308</v>
       </c>
       <c r="J163" t="n">
-        <v>14.697</v>
+        <v>12.924</v>
       </c>
     </row>
     <row r="164">
@@ -8449,10 +8449,10 @@
         <v>1.02</v>
       </c>
       <c r="I164" t="n">
-        <v>0.0694</v>
+        <v>0.0506</v>
       </c>
       <c r="J164" t="n">
-        <v>2.082</v>
+        <v>1.518</v>
       </c>
     </row>
     <row r="165">
@@ -8489,10 +8489,10 @@
         <v>0.96</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.0761</v>
+        <v>-0.0609</v>
       </c>
       <c r="J165" t="n">
-        <v>-2.283</v>
+        <v>-1.827</v>
       </c>
     </row>
     <row r="166">
@@ -8529,10 +8529,10 @@
         <v>0.68</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.3698</v>
+        <v>-0.3573</v>
       </c>
       <c r="J166" t="n">
-        <v>-11.094</v>
+        <v>-10.719</v>
       </c>
     </row>
     <row r="167">
@@ -8569,10 +8569,10 @@
         <v>1.4</v>
       </c>
       <c r="I167" t="n">
-        <v>0.7372</v>
+        <v>0.6808</v>
       </c>
       <c r="J167" t="n">
-        <v>22.116</v>
+        <v>20.424</v>
       </c>
     </row>
     <row r="168">
@@ -8609,10 +8609,10 @@
         <v>1.03</v>
       </c>
       <c r="I168" t="n">
-        <v>0.0959</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="J168" t="n">
-        <v>2.877</v>
+        <v>2.157</v>
       </c>
     </row>
     <row r="169">
@@ -8649,10 +8649,10 @@
         <v>0.97</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.0616</v>
+        <v>-0.0481</v>
       </c>
       <c r="J169" t="n">
-        <v>-1.848</v>
+        <v>-1.443</v>
       </c>
     </row>
     <row r="170">
@@ -8689,10 +8689,10 @@
         <v>0.93</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.1153</v>
+        <v>-0.097</v>
       </c>
       <c r="J170" t="n">
-        <v>-3.459</v>
+        <v>-2.91</v>
       </c>
     </row>
     <row r="171">
@@ -8729,10 +8729,10 @@
         <v>0.9</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.1509</v>
+        <v>-0.1309</v>
       </c>
       <c r="J171" t="n">
-        <v>-4.527</v>
+        <v>-3.927</v>
       </c>
     </row>
     <row r="172">
@@ -8769,10 +8769,10 @@
         <v>1.78</v>
       </c>
       <c r="I172" t="n">
-        <v>1.4099</v>
+        <v>1.4361</v>
       </c>
       <c r="J172" t="n">
-        <v>26.7881</v>
+        <v>27.2859</v>
       </c>
     </row>
     <row r="173">
@@ -8809,10 +8809,10 @@
         <v>1.73</v>
       </c>
       <c r="I173" t="n">
-        <v>1.3493</v>
+        <v>1.3727</v>
       </c>
       <c r="J173" t="n">
-        <v>25.6367</v>
+        <v>26.0813</v>
       </c>
     </row>
     <row r="174">
@@ -8849,10 +8849,10 @@
         <v>1.69</v>
       </c>
       <c r="I174" t="n">
-        <v>1.3004</v>
+        <v>1.3218</v>
       </c>
       <c r="J174" t="n">
-        <v>24.7076</v>
+        <v>25.1142</v>
       </c>
     </row>
     <row r="175">
@@ -8889,10 +8889,10 @@
         <v>1.38</v>
       </c>
       <c r="I175" t="n">
-        <v>0.8698</v>
+        <v>0.8633</v>
       </c>
       <c r="J175" t="n">
-        <v>16.5262</v>
+        <v>16.4027</v>
       </c>
     </row>
     <row r="176">
@@ -8929,10 +8929,10 @@
         <v>0.88</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.4757</v>
+        <v>-0.4445</v>
       </c>
       <c r="J176" t="n">
-        <v>-9.0383</v>
+        <v>-8.445499999999999</v>
       </c>
     </row>
     <row r="177">
@@ -8969,10 +8969,10 @@
         <v>1.06</v>
       </c>
       <c r="I177" t="n">
-        <v>0.3206</v>
+        <v>0.3096</v>
       </c>
       <c r="J177" t="n">
-        <v>6.0914</v>
+        <v>5.8824</v>
       </c>
     </row>
     <row r="178">
@@ -9009,10 +9009,10 @@
         <v>0.66</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.3435</v>
+        <v>-0.3336</v>
       </c>
       <c r="J178" t="n">
-        <v>-6.5265</v>
+        <v>-6.3384</v>
       </c>
     </row>
     <row r="179">
@@ -9049,10 +9049,10 @@
         <v>0.66</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.3435</v>
+        <v>-0.3336</v>
       </c>
       <c r="J179" t="n">
-        <v>-6.5265</v>
+        <v>-6.3384</v>
       </c>
     </row>
     <row r="180">
@@ -9089,10 +9089,10 @@
         <v>0.38</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.5879</v>
+        <v>-0.5974</v>
       </c>
       <c r="J180" t="n">
-        <v>-11.1701</v>
+        <v>-11.3506</v>
       </c>
     </row>
     <row r="181">
@@ -9129,10 +9129,10 @@
         <v>0.31</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.6494</v>
+        <v>-0.6696</v>
       </c>
       <c r="J181" t="n">
-        <v>-12.3386</v>
+        <v>-12.7224</v>
       </c>
     </row>
   </sheetData>
